--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Vital Signs: BP</t>
+    <t>Vital Signs BP</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Vital Signs BP</t>
+    <t>Vital Signs: BP</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1790,10 +1790,7 @@
     <t>666: transform using Split_rate_value.Systolic on GMRV VITAL MEASUREMENT - RATE (#120.5-1.2) case VUID = 4500634</t>
   </si>
   <si>
-    <t>Vital.VitalSign.Diastolic
-Vital.VitalSign.Systolic
-Vital.VitalSign.VitalResult
-Vital.VitalSign.VitalResultNumeric</t>
+    <t>Vital.VitalSign.Diastolic,Vital.VitalSign.Systolic,Vital.VitalSign.VitalResult,Vital.VitalSign.VitalResultNumeric</t>
   </si>
   <si>
     <t>Observation.component:systolic.value[x].comparator</t>
@@ -2344,7 +2341,7 @@
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
     <col min="43" max="43" width="113.26171875" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="98.75" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,12 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -253,12 +259,6 @@
   </si>
   <si>
     <t>Mapping: SNOMED CT Attribute Binding</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t>Vital Signs
@@ -1781,16 +1781,16 @@
     <t>Quantity.value</t>
   </si>
   <si>
+    <t>666: transform using Split_rate_value.Systolic on GMRV VITAL MEASUREMENT - RATE (#120.5-1.2) case VUID = 4500634</t>
+  </si>
+  <si>
+    <t>Vital.VitalSign.Diastolic,Vital.VitalSign.Systolic,Vital.VitalSign.VitalResult,Vital.VitalSign.VitalResultNumeric</t>
+  </si>
+  <si>
     <t>SN.2  / CQ - N/A</t>
   </si>
   <si>
     <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
-  </si>
-  <si>
-    <t>666: transform using Split_rate_value.Systolic on GMRV VITAL MEASUREMENT - RATE (#120.5-1.2) case VUID = 4500634</t>
-  </si>
-  <si>
-    <t>Vital.VitalSign.Diastolic,Vital.VitalSign.Systolic,Vital.VitalSign.VitalResult,Vital.VitalSign.VitalResultNumeric</t>
   </si>
   <si>
     <t>Observation.component:systolic.value[x].comparator</t>
@@ -2334,14 +2334,14 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="113.26171875" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="98.75" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="113.26171875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="98.75" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="107.01953125" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="42.34375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2580,22 +2580,22 @@
         <v>88</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="AM2" t="s" s="2">
+      <c r="AO2" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="AN2" t="s" s="2">
+      <c r="AP2" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="AO2" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP2" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ2" t="s" s="2">
         <v>84</v>
@@ -3217,13 +3217,13 @@
         <v>84</v>
       </c>
       <c r="AN7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP7" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP7" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ7" t="s" s="2">
         <v>84</v>
@@ -3343,13 +3343,13 @@
         <v>84</v>
       </c>
       <c r="AN8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP8" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP8" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ8" t="s" s="2">
         <v>84</v>
@@ -3469,13 +3469,13 @@
         <v>84</v>
       </c>
       <c r="AN9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP9" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP9" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ9" t="s" s="2">
         <v>84</v>
@@ -3597,13 +3597,13 @@
         <v>84</v>
       </c>
       <c r="AN10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP10" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP10" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ10" t="s" s="2">
         <v>84</v>
@@ -3714,25 +3714,25 @@
         <v>106</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="AL11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO11" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="AO11" t="s" s="2">
+      <c r="AQ11" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ11" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR11" t="s" s="2">
         <v>84</v>
@@ -3840,22 +3840,22 @@
         <v>106</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="AL12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM12" t="s" s="2">
+      <c r="AN12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO12" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="AN12" t="s" s="2">
+      <c r="AP12" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP12" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ12" t="s" s="2">
         <v>84</v>
@@ -3966,22 +3966,22 @@
         <v>106</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="AL13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO13" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AN13" t="s" s="2">
+      <c r="AP13" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP13" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ13" t="s" s="2">
         <v>84</v>
@@ -4092,25 +4092,25 @@
         <v>106</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="AN14" t="s" s="2">
+      <c r="AP14" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="AO14" t="s" s="2">
+      <c r="AQ14" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="AP14" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ14" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR14" t="s" s="2">
         <v>84</v>
@@ -4227,16 +4227,16 @@
         <v>84</v>
       </c>
       <c r="AN15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP15" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="AO15" t="s" s="2">
+      <c r="AQ15" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AP15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ15" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR15" t="s" s="2">
         <v>84</v>
@@ -4357,16 +4357,16 @@
         <v>84</v>
       </c>
       <c r="AN16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP16" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="AO16" t="s" s="2">
+      <c r="AQ16" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ16" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR16" t="s" s="2">
         <v>84</v>
@@ -4481,13 +4481,13 @@
         <v>84</v>
       </c>
       <c r="AN17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP17" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ17" t="s" s="2">
         <v>84</v>
@@ -4607,13 +4607,13 @@
         <v>84</v>
       </c>
       <c r="AN18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP18" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP18" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ18" t="s" s="2">
         <v>84</v>
@@ -4732,16 +4732,16 @@
         <v>84</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO19" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="AN19" t="s" s="2">
+      <c r="AP19" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP19" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>84</v>
@@ -4859,13 +4859,13 @@
         <v>84</v>
       </c>
       <c r="AN20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP20" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>84</v>
@@ -4985,13 +4985,13 @@
         <v>84</v>
       </c>
       <c r="AN21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP21" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ21" t="s" s="2">
         <v>84</v>
@@ -5110,16 +5110,16 @@
         <v>84</v>
       </c>
       <c r="AM22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO22" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AP22" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ22" t="s" s="2">
         <v>84</v>
@@ -5236,16 +5236,16 @@
         <v>84</v>
       </c>
       <c r="AM23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO23" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AP23" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ23" t="s" s="2">
         <v>84</v>
@@ -5362,16 +5362,16 @@
         <v>84</v>
       </c>
       <c r="AM24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO24" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AP24" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ24" t="s" s="2">
         <v>84</v>
@@ -5488,16 +5488,16 @@
         <v>84</v>
       </c>
       <c r="AM25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO25" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AP25" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ25" t="s" s="2">
         <v>84</v>
@@ -5616,16 +5616,16 @@
         <v>84</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AP26" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>84</v>
@@ -5744,16 +5744,16 @@
         <v>84</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AP27" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>84</v>
@@ -5866,28 +5866,28 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="AN28" t="s" s="2">
+      <c r="AP28" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="AO28" t="s" s="2">
+      <c r="AQ28" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="AP28" t="s" s="2">
+      <c r="AR28" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AQ28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR28" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="29" hidden="true">
@@ -5994,25 +5994,25 @@
         <v>106</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="AL29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO29" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AN29" t="s" s="2">
+      <c r="AP29" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AO29" t="s" s="2">
+      <c r="AQ29" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ29" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR29" t="s" s="2">
         <v>84</v>
@@ -6126,19 +6126,19 @@
         <v>84</v>
       </c>
       <c r="AM30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO30" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AP30" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="AO30" t="s" s="2">
+      <c r="AQ30" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ30" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>84</v>
@@ -6248,25 +6248,25 @@
         <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="AL31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO31" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="AN31" t="s" s="2">
+      <c r="AP31" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="AO31" t="s" s="2">
+      <c r="AQ31" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ31" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>84</v>
@@ -6376,25 +6376,25 @@
         <v>336</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="AL32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO32" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AN32" t="s" s="2">
+      <c r="AP32" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AO32" t="s" s="2">
+      <c r="AQ32" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ32" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>84</v>
@@ -6508,19 +6508,19 @@
         <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO33" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AP33" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="AO33" t="s" s="2">
+      <c r="AQ33" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ33" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>84</v>
@@ -6628,25 +6628,25 @@
         <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AL34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AN34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO34" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AP34" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AO34" t="s" s="2">
+      <c r="AQ34" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ34" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>84</v>
@@ -6759,25 +6759,25 @@
         <v>84</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AP35" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AO35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP35" t="s" s="2">
+      <c r="AQ35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR35" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AQ35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR35" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="36" hidden="true">
@@ -6890,16 +6890,16 @@
         <v>84</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO36" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AN36" t="s" s="2">
+      <c r="AP36" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP36" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
@@ -7015,25 +7015,25 @@
         <v>84</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AP37" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="AO37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP37" t="s" s="2">
+      <c r="AQ37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR37" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AQ37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR37" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="38" hidden="true">
@@ -7146,16 +7146,16 @@
         <v>84</v>
       </c>
       <c r="AM38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO38" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AP38" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
@@ -7269,25 +7269,25 @@
         <v>84</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AP39" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="AO39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP39" t="s" s="2">
+      <c r="AQ39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR39" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="AQ39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR39" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="40" hidden="true">
@@ -7400,16 +7400,16 @@
         <v>84</v>
       </c>
       <c r="AM40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO40" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AN40" t="s" s="2">
+      <c r="AP40" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -7523,25 +7523,25 @@
         <v>84</v>
       </c>
       <c r="AL41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AO41" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AN41" t="s" s="2">
+      <c r="AP41" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="AO41" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP41" t="s" s="2">
+      <c r="AQ41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR41" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AQ41" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR41" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="42" hidden="true">
@@ -7649,25 +7649,25 @@
         <v>84</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="AM42" t="s" s="2">
+      <c r="AO42" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="AN42" t="s" s="2">
+      <c r="AP42" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="AO42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP42" t="s" s="2">
+      <c r="AQ42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR42" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AQ42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR42" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="43" hidden="true">
@@ -7780,16 +7780,16 @@
         <v>84</v>
       </c>
       <c r="AM43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO43" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="AN43" t="s" s="2">
+      <c r="AP43" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
@@ -7907,13 +7907,13 @@
         <v>84</v>
       </c>
       <c r="AN44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP44" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -8033,13 +8033,13 @@
         <v>84</v>
       </c>
       <c r="AN45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP45" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -8161,13 +8161,13 @@
         <v>84</v>
       </c>
       <c r="AN46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP46" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -8282,16 +8282,16 @@
         <v>84</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO47" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="AN47" t="s" s="2">
+      <c r="AP47" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -8406,16 +8406,16 @@
         <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AP48" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8531,19 +8531,19 @@
         <v>84</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AP49" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8659,19 +8659,19 @@
         <v>84</v>
       </c>
       <c r="AL50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="AM50" t="s" s="2">
+      <c r="AO50" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="AN50" t="s" s="2">
+      <c r="AP50" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -8791,13 +8791,13 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8912,16 +8912,16 @@
         <v>84</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO52" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="AN52" t="s" s="2">
+      <c r="AP52" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -9038,16 +9038,16 @@
         <v>84</v>
       </c>
       <c r="AM53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO53" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="AN53" t="s" s="2">
+      <c r="AP53" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -9164,16 +9164,16 @@
         <v>84</v>
       </c>
       <c r="AM54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO54" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="AN54" t="s" s="2">
+      <c r="AP54" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
@@ -9290,16 +9290,16 @@
         <v>84</v>
       </c>
       <c r="AM55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO55" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="AN55" t="s" s="2">
+      <c r="AP55" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9417,13 +9417,13 @@
         <v>84</v>
       </c>
       <c r="AN56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP56" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9543,13 +9543,13 @@
         <v>84</v>
       </c>
       <c r="AN57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP57" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP57" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9671,13 +9671,13 @@
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP58" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9793,22 +9793,22 @@
         <v>84</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AO59" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="AN59" t="s" s="2">
+      <c r="AP59" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="AO59" t="s" s="2">
+      <c r="AQ59" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ59" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>84</v>
@@ -9921,25 +9921,25 @@
         <v>84</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="AM60" t="s" s="2">
+      <c r="AO60" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AN60" t="s" s="2">
+      <c r="AP60" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AO60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP60" t="s" s="2">
+      <c r="AQ60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR60" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AQ60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR60" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="61" hidden="true">
@@ -10052,16 +10052,16 @@
         <v>84</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO61" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AN61" t="s" s="2">
+      <c r="AP61" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -10177,25 +10177,25 @@
         <v>84</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="AM62" t="s" s="2">
+      <c r="AO62" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="AN62" t="s" s="2">
+      <c r="AP62" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="AO62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP62" t="s" s="2">
+      <c r="AQ62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR62" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AQ62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR62" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="63" hidden="true">
@@ -10308,16 +10308,16 @@
         <v>84</v>
       </c>
       <c r="AM63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO63" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="AN63" t="s" s="2">
+      <c r="AP63" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10438,16 +10438,16 @@
         <v>84</v>
       </c>
       <c r="AM64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO64" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="AN64" t="s" s="2">
+      <c r="AP64" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
@@ -10565,13 +10565,13 @@
         <v>84</v>
       </c>
       <c r="AN65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP65" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
@@ -10691,13 +10691,13 @@
         <v>84</v>
       </c>
       <c r="AN66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP66" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
@@ -10819,13 +10819,13 @@
         <v>84</v>
       </c>
       <c r="AN67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP67" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>84</v>
@@ -10941,22 +10941,22 @@
         <v>84</v>
       </c>
       <c r="AL68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="AM68" t="s" s="2">
+      <c r="AO68" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="AN68" t="s" s="2">
+      <c r="AP68" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="AO68" t="s" s="2">
+      <c r="AQ68" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ68" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>84</v>
@@ -11069,25 +11069,25 @@
         <v>84</v>
       </c>
       <c r="AL69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="AM69" t="s" s="2">
+      <c r="AO69" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AN69" t="s" s="2">
+      <c r="AP69" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AO69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP69" t="s" s="2">
+      <c r="AQ69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR69" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AQ69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR69" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="70" hidden="true">
@@ -11199,13 +11199,13 @@
         <v>84</v>
       </c>
       <c r="AN70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP70" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11325,13 +11325,13 @@
         <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP71" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP71" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
@@ -11444,28 +11444,28 @@
         <v>106</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>84</v>
+        <v>561</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>84</v>
+        <v>562</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>561</v>
+        <v>84</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>562</v>
+        <v>84</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>84</v>
+        <v>563</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>84</v>
+        <v>564</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>563</v>
+        <v>84</v>
       </c>
       <c r="AR72" t="s" s="2">
-        <v>564</v>
+        <v>84</v>
       </c>
     </row>
     <row r="73" hidden="true">
@@ -11578,16 +11578,16 @@
         <v>84</v>
       </c>
       <c r="AM73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO73" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="AN73" t="s" s="2">
+      <c r="AP73" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP73" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>84</v>
@@ -11704,16 +11704,16 @@
         <v>84</v>
       </c>
       <c r="AM74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO74" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="AN74" t="s" s="2">
+      <c r="AP74" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ74" t="s" s="2">
         <v>84</v>
@@ -11830,16 +11830,16 @@
         <v>84</v>
       </c>
       <c r="AM75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO75" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="AN75" t="s" s="2">
+      <c r="AP75" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP75" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>84</v>
@@ -11958,16 +11958,16 @@
         <v>84</v>
       </c>
       <c r="AM76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO76" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="AN76" t="s" s="2">
+      <c r="AP76" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>84</v>
@@ -12086,16 +12086,16 @@
         <v>84</v>
       </c>
       <c r="AM77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO77" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AN77" t="s" s="2">
+      <c r="AP77" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP77" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
@@ -12211,25 +12211,25 @@
         <v>84</v>
       </c>
       <c r="AL78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN78" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="AM78" t="s" s="2">
+      <c r="AO78" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="AN78" t="s" s="2">
+      <c r="AP78" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="AO78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP78" t="s" s="2">
+      <c r="AQ78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR78" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AQ78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR78" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="79" hidden="true">
@@ -12342,16 +12342,16 @@
         <v>84</v>
       </c>
       <c r="AM79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO79" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="AN79" t="s" s="2">
+      <c r="AP79" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AO79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP79" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>84</v>
@@ -12472,16 +12472,16 @@
         <v>84</v>
       </c>
       <c r="AM80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO80" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="AN80" t="s" s="2">
+      <c r="AP80" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="AO80" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP80" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ80" t="s" s="2">
         <v>84</v>
@@ -12599,13 +12599,13 @@
         <v>84</v>
       </c>
       <c r="AN81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP81" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP81" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>84</v>
@@ -12725,13 +12725,13 @@
         <v>84</v>
       </c>
       <c r="AN82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP82" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP82" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>84</v>
@@ -12853,13 +12853,13 @@
         <v>84</v>
       </c>
       <c r="AN83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP83" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP83" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ83" t="s" s="2">
         <v>84</v>
@@ -12975,22 +12975,22 @@
         <v>84</v>
       </c>
       <c r="AL84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN84" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="AM84" t="s" s="2">
+      <c r="AO84" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="AN84" t="s" s="2">
+      <c r="AP84" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="AO84" t="s" s="2">
+      <c r="AQ84" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="AP84" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ84" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR84" t="s" s="2">
         <v>84</v>
@@ -13103,25 +13103,25 @@
         <v>84</v>
       </c>
       <c r="AL85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN85" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="AM85" t="s" s="2">
+      <c r="AO85" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AN85" t="s" s="2">
+      <c r="AP85" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AO85" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP85" t="s" s="2">
+      <c r="AQ85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR85" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AQ85" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR85" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="86" hidden="true">
@@ -13233,13 +13233,13 @@
         <v>84</v>
       </c>
       <c r="AN86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP86" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AO86" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP86" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>84</v>
@@ -13359,13 +13359,13 @@
         <v>84</v>
       </c>
       <c r="AN87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP87" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP87" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>84</v>
@@ -13478,28 +13478,28 @@
         <v>106</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>84</v>
+        <v>618</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>84</v>
+        <v>562</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>561</v>
+        <v>84</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>562</v>
+        <v>84</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>84</v>
+        <v>563</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>84</v>
+        <v>564</v>
       </c>
       <c r="AQ88" t="s" s="2">
-        <v>618</v>
+        <v>84</v>
       </c>
       <c r="AR88" t="s" s="2">
-        <v>564</v>
+        <v>84</v>
       </c>
     </row>
     <row r="89" hidden="true">
@@ -13612,16 +13612,16 @@
         <v>84</v>
       </c>
       <c r="AM89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO89" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="AN89" t="s" s="2">
+      <c r="AP89" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="AO89" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP89" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>84</v>
@@ -13738,16 +13738,16 @@
         <v>84</v>
       </c>
       <c r="AM90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO90" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="AN90" t="s" s="2">
+      <c r="AP90" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="AO90" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP90" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ90" t="s" s="2">
         <v>84</v>
@@ -13864,16 +13864,16 @@
         <v>84</v>
       </c>
       <c r="AM91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO91" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="AN91" t="s" s="2">
+      <c r="AP91" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP91" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ91" t="s" s="2">
         <v>84</v>
@@ -13992,16 +13992,16 @@
         <v>84</v>
       </c>
       <c r="AM92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO92" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="AN92" t="s" s="2">
+      <c r="AP92" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP92" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ92" t="s" s="2">
         <v>84</v>
@@ -14120,16 +14120,16 @@
         <v>84</v>
       </c>
       <c r="AM93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO93" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AN93" t="s" s="2">
+      <c r="AP93" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP93" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ93" t="s" s="2">
         <v>84</v>
@@ -14245,25 +14245,25 @@
         <v>84</v>
       </c>
       <c r="AL94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN94" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="AM94" t="s" s="2">
+      <c r="AO94" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="AN94" t="s" s="2">
+      <c r="AP94" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="AO94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP94" t="s" s="2">
+      <c r="AQ94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR94" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AQ94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR94" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="95" hidden="true">
@@ -14376,16 +14376,16 @@
         <v>84</v>
       </c>
       <c r="AM95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO95" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="AN95" t="s" s="2">
+      <c r="AP95" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP95" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ95" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1277,7 +1277,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2600,6 +2600,78 @@
     <t>Observation.component:diastolic.referenceRange</t>
   </si>
   <si>
+    <t>Observation.component:va-cuff-size</t>
+  </si>
+  <si>
+    <t>va-cuff-size</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.id</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.modifierExtension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.code</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="8358-4"/&gt;
+    &lt;display value="Blood pressure device cuff size"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>1805-1: fixed value = http://loinc.org#8358-4 Blood pressure device cuff size</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept.id</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].coding</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFVitalsCuffSize</t>
+  </si>
+  <si>
+    <t>1805: terminologyMaps using VF_VitalsCuffSize on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept.text</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].text</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.dataAbsentReason</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.interpretation</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.referenceRange</t>
+  </si>
+  <si>
     <t>Observation.component:va-pre-condition</t>
   </si>
   <si>
@@ -2636,9 +2708,6 @@
     <t>Observation.component:va-pre-condition.value[x]:valueCodeableConcept</t>
   </si>
   <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
     <t>Observation.component:va-pre-condition.value[x]:valueCodeableConcept.id</t>
   </si>
   <si>
@@ -2648,9 +2717,6 @@
     <t>Observation.component:va-pre-condition.value[x]:valueCodeableConcept.coding</t>
   </si>
   <si>
-    <t>Observation.component.value[x].coding</t>
-  </si>
-  <si>
     <t>http://va.gov/fhir/ValueSet/VSVFVitalsPrecondition</t>
   </si>
   <si>
@@ -2660,9 +2726,6 @@
     <t>Observation.component:va-pre-condition.value[x]:valueCodeableConcept.text</t>
   </si>
   <si>
-    <t>Observation.component.value[x].text</t>
-  </si>
-  <si>
     <t>Observation.component:va-pre-condition.dataAbsentReason</t>
   </si>
   <si>
@@ -2724,69 +2787,6 @@
   </si>
   <si>
     <t>Observation.component:va-pre-condition-device.referenceRange</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size</t>
-  </si>
-  <si>
-    <t>va-cuff-size</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.id</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.modifierExtension</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.code</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://loinc.org"/&gt;
-    &lt;code value="8358-4"/&gt;
-    &lt;display value="Blood pressure device cuff size"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>1805-1: fixed value = http://loinc.org#8358-4 Blood pressure device cuff size</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.value[x]</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept.id</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFVitalsCuffSize</t>
-  </si>
-  <si>
-    <t>1805: terminologyMaps using VF_VitalsCuffSize on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept.text</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.dataAbsentReason</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.interpretation</t>
-  </si>
-  <si>
-    <t>Observation.component:va-cuff-size.referenceRange</t>
   </si>
 </sst>
 </file>
@@ -25207,7 +25207,7 @@
         <v>84</v>
       </c>
       <c r="S175" t="s" s="2">
-        <v>833</v>
+        <v>855</v>
       </c>
       <c r="T175" t="s" s="2">
         <v>84</v>
@@ -25261,7 +25261,7 @@
         <v>106</v>
       </c>
       <c r="AK175" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="AL175" t="s" s="2">
         <v>84</v>
@@ -25287,7 +25287,7 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B176" t="s" s="2">
         <v>721</v>
@@ -25413,7 +25413,7 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B177" t="s" s="2">
         <v>721</v>
@@ -25543,7 +25543,7 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B178" t="s" s="2">
         <v>772</v>
@@ -25667,7 +25667,7 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B179" t="s" s="2">
         <v>774</v>
@@ -25793,7 +25793,7 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B180" t="s" s="2">
         <v>841</v>
@@ -25860,7 +25860,7 @@
       </c>
       <c r="Y180" s="2"/>
       <c r="Z180" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>84</v>
@@ -25893,7 +25893,7 @@
         <v>106</v>
       </c>
       <c r="AK180" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="AL180" t="s" s="2">
         <v>84</v>
@@ -25919,7 +25919,7 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B181" t="s" s="2">
         <v>845</v>
@@ -26047,7 +26047,7 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B182" t="s" s="2">
         <v>727</v>
@@ -26175,7 +26175,7 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B183" t="s" s="2">
         <v>733</v>
@@ -26303,7 +26303,7 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B184" t="s" s="2">
         <v>734</v>
@@ -26431,13 +26431,13 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B185" t="s" s="2">
         <v>702</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="D185" t="s" s="2">
         <v>84</v>
@@ -26561,7 +26561,7 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B186" t="s" s="2">
         <v>712</v>
@@ -26685,7 +26685,7 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B187" t="s" s="2">
         <v>713</v>
@@ -26811,7 +26811,7 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B188" t="s" s="2">
         <v>714</v>
@@ -26939,7 +26939,7 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B189" t="s" s="2">
         <v>715</v>
@@ -26987,7 +26987,7 @@
         <v>84</v>
       </c>
       <c r="S189" t="s" s="2">
-        <v>873</v>
+        <v>855</v>
       </c>
       <c r="T189" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -561,7 +561,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFVitalsMeasurementDevice</t>
+    <t>http://va.gov/fhir/ValueSet/VitalsMeasurementDevice</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -605,7 +605,7 @@
     <t>Observation.extension:observation-bodyPosition.value[x]</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFVitalsBodyPosition</t>
+    <t>http://va.gov/fhir/ValueSet/VitalsBodyPosition</t>
   </si>
   <si>
     <t>1804: terminologyMaps using VF_VitalsBodyPosition on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
@@ -1262,7 +1262,7 @@
     <t>Observation.code.coding</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFVitalsCodes</t>
+    <t>http://va.gov/fhir/ValueSet/VitalsCodes</t>
   </si>
   <si>
     <t>661: terminologyMaps using VF_VitalsCodes on GMRV VITAL MEASUREMENT - VITAL TYPE (120.5-.03)</t>
@@ -1770,7 +1770,7 @@
 </t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ConceptMap/CMVFVitalsUnits</t>
+    <t>http://va.gov/fhir/ConceptMap/VitalsUnits</t>
   </si>
   <si>
     <t>Observation.value[x]:valueQuantity.code.value</t>
@@ -1892,7 +1892,7 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFVitalsBodySite</t>
+    <t>http://va.gov/fhir/ValueSet/VitalsBodySite</t>
   </si>
   <si>
     <t>662: terminologyMaps using VF_VitalsBodySite on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
@@ -1925,7 +1925,7 @@
     <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFVitalsMethod</t>
+    <t>http://va.gov/fhir/ValueSet/VitalsMethod</t>
   </si>
   <si>
     <t>867: terminologyMaps using VF_VitalsMethod on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
@@ -2651,7 +2651,7 @@
     <t>Observation.component.value[x].coding</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFVitalsCuffSize</t>
+    <t>http://va.gov/fhir/ValueSet/VitalsCuffSize</t>
   </si>
   <si>
     <t>1805: terminologyMaps using VF_VitalsCuffSize on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
@@ -2717,7 +2717,7 @@
     <t>Observation.component:va-pre-condition.value[x]:valueCodeableConcept.coding</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFVitalsPrecondition</t>
+    <t>http://va.gov/fhir/ValueSet/VitalsPrecondition</t>
   </si>
   <si>
     <t>1802: terminologyMaps using VF_VitalsPrecondition on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
@@ -2771,7 +2771,7 @@
     <t>Observation.component:va-pre-condition-device.value[x]:valueCodeableConcept.coding</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFVitalsQualifyingDevice</t>
+    <t>http://va.gov/fhir/ValueSet/VitalsQualifyingDevice</t>
   </si>
   <si>
     <t>1803: terminologyMaps using VF_VitalsQualifyingDevice on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
@@ -3131,7 +3131,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="54.625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.83984375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8012" uniqueCount="886">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8012" uniqueCount="893">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -916,6 +916,10 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+VitalSignsBP-655:if null then fixed value #final {null}VitalSignsBP-656:if not null then fixed value #entered-in-error {null}</t>
   </si>
   <si>
     <t>656: fixed value = #entered-in-error when GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (120.5-4) case not null</t>
@@ -2388,6 +2392,10 @@
     <t>Observation.component.code.coding.system</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+VitalSignsBP-666-2:if VUID = 4500634 then fixed value http://loinc.org {null}</t>
+  </si>
+  <si>
     <t>666-2: fixed value = http://loinc.org case VUID = 4500634</t>
   </si>
   <si>
@@ -2403,6 +2411,10 @@
     <t>Observation.component.code.coding.code</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+VitalSignsBP-666-3:if VUID = 4500634 then fixed value 8480-6 {null}</t>
+  </si>
+  <si>
     <t>666-3: fixed value = 8480-6 case VUID = 4500634</t>
   </si>
   <si>
@@ -2476,6 +2488,10 @@
   </si>
   <si>
     <t>mm[Hg]</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+VitalSignsBP-666-1:if VUID = 4500634 then fixed value mm[Hg] {null}</t>
   </si>
   <si>
     <t>666-1: fixed value = mm[Hg] case VUID = 4500634</t>
@@ -2540,6 +2556,10 @@
     <t>Observation.component:diastolic.code.coding.system</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+VitalSignsBP-667-2:if VUID = 4500634 then fixed value http://loinc.org {null}</t>
+  </si>
+  <si>
     <t>667-2: fixed value = http://loinc.org case VUID = 4500634</t>
   </si>
   <si>
@@ -2549,6 +2569,10 @@
     <t>Observation.component:diastolic.code.coding.code</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+VitalSignsBP-667-3:if VUID = 4500634 then fixed value 8462-4 {null}</t>
+  </si>
+  <si>
     <t>667-3: fixed value = 8462-4 case VUID = 4500634</t>
   </si>
   <si>
@@ -2586,6 +2610,10 @@
   </si>
   <si>
     <t>Observation.component:diastolic.value[x].code</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+VitalSignsBP-667-1:if VUID = 4500634 then fixed value mm[Hg] {null}</t>
   </si>
   <si>
     <t>667-1: fixed value = mm[Hg] case VUID = 4500634</t>
@@ -2627,7 +2655,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>1805-1: fixed value = http://loinc.org#8358-4 Blood pressure device cuff size</t>
+    <t>1805-1: fixed value = http://loinc.org#8358-4 "Blood pressure device cuff size"</t>
   </si>
   <si>
     <t>Observation.component:va-cuff-size.value[x]</t>
@@ -2699,7 +2727,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>1802-1: fixed value = http://loinc.org#104158-1 Associated precondition - Reported</t>
+    <t>1802-1: fixed value = http://loinc.org#104158-1 "Associated precondition - Reported"</t>
   </si>
   <si>
     <t>Observation.component:va-pre-condition.value[x]</t>
@@ -2753,7 +2781,7 @@
     <t>Observation.component:va-pre-condition-device.code</t>
   </si>
   <si>
-    <t>1803-1: fixed value = http://loinc.org#104158-1 Associated precondition - Reported</t>
+    <t>1803-1: fixed value = http://loinc.org#104158-1 "Associated precondition - Reported"</t>
   </si>
   <si>
     <t>Observation.component:va-pre-condition-device.value[x]</t>
@@ -7146,28 +7174,28 @@
         <v>84</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>106</v>
+        <v>290</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>84</v>
@@ -7175,10 +7203,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -7204,16 +7232,16 @@
         <v>171</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -7223,7 +7251,7 @@
         <v>84</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>84</v>
@@ -7241,16 +7269,16 @@
         <v>118</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
@@ -7260,7 +7288,7 @@
         <v>143</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -7275,7 +7303,7 @@
         <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>84</v>
@@ -7290,10 +7318,10 @@
         <v>84</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>84</v>
@@ -7301,13 +7329,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>84</v>
@@ -7332,16 +7360,16 @@
         <v>171</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -7369,10 +7397,10 @@
         <v>118</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>84</v>
@@ -7390,7 +7418,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -7420,10 +7448,10 @@
         <v>84</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>84</v>
@@ -7431,10 +7459,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7555,10 +7583,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7681,10 +7709,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7707,19 +7735,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -7768,7 +7796,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -7795,10 +7823,10 @@
         <v>84</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -7809,10 +7837,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7933,10 +7961,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -8059,10 +8087,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -8088,23 +8116,23 @@
         <v>108</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>84</v>
@@ -8146,7 +8174,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -8173,10 +8201,10 @@
         <v>84</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -8187,10 +8215,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -8216,13 +8244,13 @@
         <v>208</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -8272,7 +8300,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -8299,10 +8327,10 @@
         <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -8313,10 +8341,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -8342,21 +8370,21 @@
         <v>114</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>84</v>
@@ -8398,7 +8426,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -8425,10 +8453,10 @@
         <v>84</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -8439,10 +8467,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8468,14 +8496,14 @@
         <v>208</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
@@ -8524,7 +8552,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -8551,10 +8579,10 @@
         <v>84</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
@@ -8565,10 +8593,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8591,19 +8619,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -8652,7 +8680,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8679,10 +8707,10 @@
         <v>84</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -8693,10 +8721,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8722,16 +8750,16 @@
         <v>208</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -8780,7 +8808,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8807,10 +8835,10 @@
         <v>84</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -8821,14 +8849,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -8850,16 +8878,16 @@
         <v>171</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -8869,7 +8897,7 @@
         <v>84</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>84</v>
@@ -8887,10 +8915,10 @@
         <v>226</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
@@ -8908,7 +8936,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>94</v>
@@ -8929,30 +8957,30 @@
         <v>84</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -9073,10 +9101,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -9199,10 +9227,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -9225,19 +9253,19 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -9266,7 +9294,7 @@
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -9284,7 +9312,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -9299,10 +9327,10 @@
         <v>106</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>84</v>
@@ -9311,10 +9339,10 @@
         <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -9325,10 +9353,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9354,16 +9382,16 @@
         <v>208</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -9412,7 +9440,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -9439,10 +9467,10 @@
         <v>84</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -9453,10 +9481,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9479,19 +9507,19 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -9540,7 +9568,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9555,25 +9583,25 @@
         <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>84</v>
@@ -9581,10 +9609,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9607,16 +9635,16 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -9666,7 +9694,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9693,13 +9721,13 @@
         <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>84</v>
@@ -9707,14 +9735,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -9733,19 +9761,19 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
@@ -9794,7 +9822,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9815,19 +9843,19 @@
         <v>84</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>84</v>
@@ -9835,14 +9863,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -9861,19 +9889,19 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
@@ -9910,7 +9938,7 @@
         <v>84</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AC54" s="2"/>
       <c r="AD54" t="s" s="2">
@@ -9920,7 +9948,7 @@
         <v>143</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9929,10 +9957,10 @@
         <v>94</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>84</v>
@@ -9941,19 +9969,19 @@
         <v>84</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>84</v>
@@ -9961,16 +9989,16 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -9989,19 +10017,19 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -10050,7 +10078,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -10059,31 +10087,31 @@
         <v>94</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>84</v>
@@ -10091,10 +10119,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -10117,16 +10145,16 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -10176,7 +10204,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -10191,10 +10219,10 @@
         <v>106</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>84</v>
@@ -10203,13 +10231,13 @@
         <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>84</v>
@@ -10217,10 +10245,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -10243,17 +10271,17 @@
         <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>84</v>
@@ -10302,7 +10330,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -10317,25 +10345,25 @@
         <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>84</v>
@@ -10343,10 +10371,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10369,19 +10397,19 @@
         <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -10409,16 +10437,16 @@
         <v>226</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
@@ -10428,7 +10456,7 @@
         <v>143</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -10437,7 +10465,7 @@
         <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
@@ -10452,30 +10480,30 @@
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR58" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>84</v>
@@ -10497,19 +10525,19 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -10537,10 +10565,10 @@
         <v>226</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>84</v>
@@ -10558,7 +10586,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10567,7 +10595,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -10582,27 +10610,27 @@
         <v>84</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10723,10 +10751,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10849,10 +10877,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10875,19 +10903,19 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>84</v>
@@ -10936,7 +10964,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10951,10 +10979,10 @@
         <v>106</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>84</v>
@@ -10963,10 +10991,10 @@
         <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10977,10 +11005,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -11006,20 +11034,20 @@
         <v>114</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q63" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="R63" t="s" s="2">
         <v>84</v>
@@ -11043,10 +11071,10 @@
         <v>174</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>84</v>
@@ -11064,7 +11092,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -11091,10 +11119,10 @@
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -11105,10 +11133,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -11134,14 +11162,14 @@
         <v>208</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -11190,7 +11218,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -11217,10 +11245,10 @@
         <v>84</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
@@ -11231,10 +11259,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -11260,14 +11288,14 @@
         <v>108</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
@@ -11316,7 +11344,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -11325,7 +11353,7 @@
         <v>94</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>106</v>
@@ -11343,10 +11371,10 @@
         <v>84</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
@@ -11357,10 +11385,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11386,16 +11414,16 @@
         <v>114</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>84</v>
@@ -11444,7 +11472,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -11459,10 +11487,10 @@
         <v>106</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>84</v>
@@ -11471,10 +11499,10 @@
         <v>84</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
@@ -11485,10 +11513,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11514,10 +11542,10 @@
         <v>208</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -11609,10 +11637,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11731,13 +11759,13 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="B69" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="B69" t="s" s="2">
-        <v>546</v>
-      </c>
       <c r="C69" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>84</v>
@@ -11759,16 +11787,16 @@
         <v>84</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -11859,10 +11887,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11983,10 +12011,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -12107,10 +12135,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -12150,7 +12178,7 @@
       </c>
       <c r="Q72" s="2"/>
       <c r="R72" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="S72" t="s" s="2">
         <v>84</v>
@@ -12233,10 +12261,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12259,7 +12287,7 @@
         <v>84</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="L73" t="s" s="2">
         <v>172</v>
@@ -12277,7 +12305,7 @@
         <v>84</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="T73" t="s" s="2">
         <v>84</v>
@@ -12357,10 +12385,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12386,10 +12414,10 @@
         <v>208</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -12440,7 +12468,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -12481,10 +12509,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12510,16 +12538,16 @@
         <v>171</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>84</v>
@@ -12547,10 +12575,10 @@
         <v>226</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>84</v>
@@ -12568,7 +12596,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12577,13 +12605,13 @@
         <v>94</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>84</v>
@@ -12598,7 +12626,7 @@
         <v>137</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>84</v>
@@ -12609,14 +12637,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -12638,16 +12666,16 @@
         <v>171</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>84</v>
@@ -12675,10 +12703,10 @@
         <v>226</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>84</v>
@@ -12696,7 +12724,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12720,27 +12748,27 @@
         <v>84</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12763,19 +12791,19 @@
         <v>84</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>84</v>
@@ -12824,7 +12852,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12851,10 +12879,10 @@
         <v>84</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
@@ -12865,10 +12893,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12894,13 +12922,13 @@
         <v>171</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -12930,7 +12958,7 @@
       </c>
       <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>84</v>
@@ -12948,7 +12976,7 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12963,7 +12991,7 @@
         <v>106</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>84</v>
@@ -12972,27 +13000,27 @@
         <v>84</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR78" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -13018,16 +13046,16 @@
         <v>171</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>84</v>
@@ -13056,7 +13084,7 @@
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>84</v>
@@ -13074,7 +13102,7 @@
         <v>84</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -13089,7 +13117,7 @@
         <v>106</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>84</v>
@@ -13101,10 +13129,10 @@
         <v>84</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>84</v>
@@ -13115,10 +13143,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -13141,16 +13169,16 @@
         <v>84</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -13200,7 +13228,7 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -13224,27 +13252,27 @@
         <v>84</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AQ80" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR80" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -13267,16 +13295,16 @@
         <v>84</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -13326,7 +13354,7 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -13350,27 +13378,27 @@
         <v>84</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR81" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13393,19 +13421,19 @@
         <v>84</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>84</v>
@@ -13454,7 +13482,7 @@
         <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -13466,7 +13494,7 @@
         <v>84</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>84</v>
@@ -13481,10 +13509,10 @@
         <v>84</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>84</v>
@@ -13495,10 +13523,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13619,10 +13647,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13745,14 +13773,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -13774,10 +13802,10 @@
         <v>139</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>195</v>
@@ -13832,7 +13860,7 @@
         <v>84</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13873,10 +13901,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13899,13 +13927,13 @@
         <v>84</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -13956,7 +13984,7 @@
         <v>84</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -13965,7 +13993,7 @@
         <v>94</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>106</v>
@@ -13983,10 +14011,10 @@
         <v>84</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>84</v>
@@ -13997,10 +14025,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -14023,13 +14051,13 @@
         <v>84</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -14080,7 +14108,7 @@
         <v>84</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -14089,7 +14117,7 @@
         <v>94</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>106</v>
@@ -14107,10 +14135,10 @@
         <v>84</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>84</v>
@@ -14121,10 +14149,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -14150,16 +14178,16 @@
         <v>171</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>84</v>
@@ -14187,10 +14215,10 @@
         <v>118</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>84</v>
@@ -14208,7 +14236,7 @@
         <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -14232,13 +14260,13 @@
         <v>84</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AQ88" t="s" s="2">
         <v>84</v>
@@ -14249,10 +14277,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -14278,16 +14306,16 @@
         <v>171</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>84</v>
@@ -14312,13 +14340,13 @@
         <v>84</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>84</v>
@@ -14336,7 +14364,7 @@
         <v>84</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -14360,13 +14388,13 @@
         <v>84</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>84</v>
@@ -14377,10 +14405,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14403,17 +14431,17 @@
         <v>84</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>84</v>
@@ -14462,7 +14490,7 @@
         <v>84</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -14492,7 +14520,7 @@
         <v>84</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AQ90" t="s" s="2">
         <v>84</v>
@@ -14503,10 +14531,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14532,10 +14560,10 @@
         <v>208</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -14586,7 +14614,7 @@
         <v>84</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14613,10 +14641,10 @@
         <v>84</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AQ91" t="s" s="2">
         <v>84</v>
@@ -14627,10 +14655,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14653,16 +14681,16 @@
         <v>95</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -14712,7 +14740,7 @@
         <v>84</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14739,10 +14767,10 @@
         <v>84</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AQ92" t="s" s="2">
         <v>84</v>
@@ -14753,10 +14781,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14779,16 +14807,16 @@
         <v>95</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -14838,7 +14866,7 @@
         <v>84</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14865,10 +14893,10 @@
         <v>84</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AQ93" t="s" s="2">
         <v>84</v>
@@ -14879,10 +14907,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14890,7 +14918,7 @@
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="G94" t="s" s="2">
         <v>83</v>
@@ -14905,19 +14933,19 @@
         <v>95</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>84</v>
@@ -14954,7 +14982,7 @@
         <v>84</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AC94" s="2"/>
       <c r="AD94" t="s" s="2">
@@ -14964,7 +14992,7 @@
         <v>143</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14976,7 +15004,7 @@
         <v>84</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>84</v>
@@ -14991,10 +15019,10 @@
         <v>84</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AQ94" t="s" s="2">
         <v>84</v>
@@ -15005,10 +15033,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -15129,10 +15157,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -15255,14 +15283,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -15284,10 +15312,10 @@
         <v>139</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>195</v>
@@ -15342,7 +15370,7 @@
         <v>84</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
@@ -15383,10 +15411,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15412,16 +15440,16 @@
         <v>171</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>84</v>
@@ -15449,10 +15477,10 @@
         <v>226</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>84</v>
@@ -15470,7 +15498,7 @@
         <v>84</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>94</v>
@@ -15494,16 +15522,16 @@
         <v>84</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AQ98" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AR98" t="s" s="2">
         <v>84</v>
@@ -15511,10 +15539,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15537,19 +15565,19 @@
         <v>95</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>84</v>
@@ -15577,10 +15605,10 @@
         <v>226</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>84</v>
@@ -15598,7 +15626,7 @@
         <v>84</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15607,7 +15635,7 @@
         <v>94</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>106</v>
@@ -15622,27 +15650,27 @@
         <v>84</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AQ99" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR99" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15668,16 +15696,16 @@
         <v>171</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>84</v>
@@ -15705,10 +15733,10 @@
         <v>226</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>84</v>
@@ -15726,7 +15754,7 @@
         <v>84</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>82</v>
@@ -15735,13 +15763,13 @@
         <v>94</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>84</v>
@@ -15756,7 +15784,7 @@
         <v>137</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AQ100" t="s" s="2">
         <v>84</v>
@@ -15767,14 +15795,14 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -15796,16 +15824,16 @@
         <v>171</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>84</v>
@@ -15833,10 +15861,10 @@
         <v>226</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>84</v>
@@ -15854,7 +15882,7 @@
         <v>84</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15878,27 +15906,27 @@
         <v>84</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AQ101" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15924,16 +15952,16 @@
         <v>85</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>84</v>
@@ -15982,7 +16010,7 @@
         <v>84</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -16009,10 +16037,10 @@
         <v>84</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AQ102" t="s" s="2">
         <v>84</v>
@@ -16023,13 +16051,13 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>84</v>
@@ -16051,19 +16079,19 @@
         <v>95</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>84</v>
@@ -16112,7 +16140,7 @@
         <v>84</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -16124,7 +16152,7 @@
         <v>84</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>84</v>
@@ -16139,10 +16167,10 @@
         <v>84</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AQ103" t="s" s="2">
         <v>84</v>
@@ -16153,10 +16181,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -16277,10 +16305,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -16403,14 +16431,14 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -16432,10 +16460,10 @@
         <v>139</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>195</v>
@@ -16490,7 +16518,7 @@
         <v>84</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>82</v>
@@ -16531,10 +16559,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16560,16 +16588,16 @@
         <v>171</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>84</v>
@@ -16579,7 +16607,7 @@
         <v>84</v>
       </c>
       <c r="S107" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="T107" t="s" s="2">
         <v>84</v>
@@ -16597,10 +16625,10 @@
         <v>226</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>84</v>
@@ -16618,7 +16646,7 @@
         <v>84</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>94</v>
@@ -16642,16 +16670,16 @@
         <v>84</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AQ107" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AR107" t="s" s="2">
         <v>84</v>
@@ -16659,10 +16687,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16783,10 +16811,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16909,10 +16937,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16935,19 +16963,19 @@
         <v>95</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>84</v>
@@ -16996,7 +17024,7 @@
         <v>84</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>82</v>
@@ -17023,10 +17051,10 @@
         <v>84</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AQ110" t="s" s="2">
         <v>84</v>
@@ -17037,10 +17065,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -17161,10 +17189,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -17287,10 +17315,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17316,16 +17344,16 @@
         <v>108</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>84</v>
@@ -17374,7 +17402,7 @@
         <v>84</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>82</v>
@@ -17386,10 +17414,10 @@
         <v>84</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>106</v>
+        <v>759</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>84</v>
@@ -17401,10 +17429,10 @@
         <v>84</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AQ113" t="s" s="2">
         <v>84</v>
@@ -17415,10 +17443,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17444,13 +17472,13 @@
         <v>208</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -17500,7 +17528,7 @@
         <v>84</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>82</v>
@@ -17527,10 +17555,10 @@
         <v>84</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AQ114" t="s" s="2">
         <v>84</v>
@@ -17541,10 +17569,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -17570,14 +17598,14 @@
         <v>114</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>84</v>
@@ -17626,7 +17654,7 @@
         <v>84</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>82</v>
@@ -17638,10 +17666,10 @@
         <v>84</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>106</v>
+        <v>765</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="AL115" t="s" s="2">
         <v>84</v>
@@ -17653,10 +17681,10 @@
         <v>84</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AQ115" t="s" s="2">
         <v>84</v>
@@ -17667,10 +17695,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17696,14 +17724,14 @@
         <v>208</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>84</v>
@@ -17752,7 +17780,7 @@
         <v>84</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>82</v>
@@ -17779,10 +17807,10 @@
         <v>84</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AQ116" t="s" s="2">
         <v>84</v>
@@ -17793,10 +17821,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17819,19 +17847,19 @@
         <v>95</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>84</v>
@@ -17880,7 +17908,7 @@
         <v>84</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>82</v>
@@ -17907,10 +17935,10 @@
         <v>84</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AQ117" t="s" s="2">
         <v>84</v>
@@ -17921,10 +17949,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17950,16 +17978,16 @@
         <v>208</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>84</v>
@@ -18008,7 +18036,7 @@
         <v>84</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>82</v>
@@ -18035,10 +18063,10 @@
         <v>84</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AQ118" t="s" s="2">
         <v>84</v>
@@ -18049,10 +18077,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -18075,19 +18103,19 @@
         <v>95</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>84</v>
@@ -18115,10 +18143,10 @@
         <v>226</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>84</v>
@@ -18136,7 +18164,7 @@
         <v>84</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>82</v>
@@ -18145,7 +18173,7 @@
         <v>94</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AJ119" t="s" s="2">
         <v>106</v>
@@ -18160,27 +18188,27 @@
         <v>84</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AP119" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AQ119" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR119" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -18301,10 +18329,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -18427,10 +18455,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18453,19 +18481,19 @@
         <v>95</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>84</v>
@@ -18514,7 +18542,7 @@
         <v>84</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>82</v>
@@ -18529,10 +18557,10 @@
         <v>106</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>84</v>
@@ -18541,10 +18569,10 @@
         <v>84</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AQ122" t="s" s="2">
         <v>84</v>
@@ -18555,10 +18583,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18584,20 +18612,20 @@
         <v>114</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q123" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="R123" t="s" s="2">
         <v>84</v>
@@ -18621,10 +18649,10 @@
         <v>174</v>
       </c>
       <c r="Y123" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="Z123" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>84</v>
@@ -18642,7 +18670,7 @@
         <v>84</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>82</v>
@@ -18669,10 +18697,10 @@
         <v>84</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AP123" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AQ123" t="s" s="2">
         <v>84</v>
@@ -18683,10 +18711,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18712,14 +18740,14 @@
         <v>208</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>84</v>
@@ -18768,7 +18796,7 @@
         <v>84</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>82</v>
@@ -18795,10 +18823,10 @@
         <v>84</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AP124" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AQ124" t="s" s="2">
         <v>84</v>
@@ -18809,10 +18837,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18838,21 +18866,21 @@
         <v>108</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q125" s="2"/>
       <c r="R125" t="s" s="2">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="S125" t="s" s="2">
         <v>84</v>
@@ -18894,7 +18922,7 @@
         <v>84</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>82</v>
@@ -18903,7 +18931,7 @@
         <v>94</v>
       </c>
       <c r="AI125" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AJ125" t="s" s="2">
         <v>106</v>
@@ -18921,10 +18949,10 @@
         <v>84</v>
       </c>
       <c r="AO125" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AP125" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AQ125" t="s" s="2">
         <v>84</v>
@@ -18935,10 +18963,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18964,23 +18992,23 @@
         <v>114</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q126" s="2"/>
       <c r="R126" t="s" s="2">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="S126" t="s" s="2">
         <v>84</v>
@@ -19022,7 +19050,7 @@
         <v>84</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>82</v>
@@ -19034,10 +19062,10 @@
         <v>84</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>106</v>
+        <v>791</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>84</v>
@@ -19049,10 +19077,10 @@
         <v>84</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AQ126" t="s" s="2">
         <v>84</v>
@@ -19063,10 +19091,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -19092,16 +19120,16 @@
         <v>171</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>84</v>
@@ -19129,10 +19157,10 @@
         <v>226</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>84</v>
@@ -19150,7 +19178,7 @@
         <v>84</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>82</v>
@@ -19159,7 +19187,7 @@
         <v>94</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>106</v>
@@ -19180,7 +19208,7 @@
         <v>137</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AQ127" t="s" s="2">
         <v>84</v>
@@ -19191,14 +19219,14 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -19220,16 +19248,16 @@
         <v>171</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>84</v>
@@ -19257,10 +19285,10 @@
         <v>226</v>
       </c>
       <c r="Y128" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z128" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>84</v>
@@ -19278,7 +19306,7 @@
         <v>84</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>82</v>
@@ -19302,27 +19330,27 @@
         <v>84</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AO128" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AP128" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AQ128" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR128" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -19348,16 +19376,16 @@
         <v>85</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>84</v>
@@ -19406,7 +19434,7 @@
         <v>84</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>82</v>
@@ -19433,10 +19461,10 @@
         <v>84</v>
       </c>
       <c r="AO129" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AP129" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AQ129" t="s" s="2">
         <v>84</v>
@@ -19447,13 +19475,13 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="D130" t="s" s="2">
         <v>84</v>
@@ -19475,19 +19503,19 @@
         <v>95</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>84</v>
@@ -19536,7 +19564,7 @@
         <v>84</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>82</v>
@@ -19548,7 +19576,7 @@
         <v>84</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AK130" t="s" s="2">
         <v>84</v>
@@ -19563,10 +19591,10 @@
         <v>84</v>
       </c>
       <c r="AO130" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AP130" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AQ130" t="s" s="2">
         <v>84</v>
@@ -19577,10 +19605,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -19701,10 +19729,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -19827,14 +19855,14 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -19856,10 +19884,10 @@
         <v>139</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="N133" t="s" s="2">
         <v>195</v>
@@ -19914,7 +19942,7 @@
         <v>84</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>82</v>
@@ -19955,10 +19983,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -19984,16 +20012,16 @@
         <v>171</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>84</v>
@@ -20003,7 +20031,7 @@
         <v>84</v>
       </c>
       <c r="S134" t="s" s="2">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="T134" t="s" s="2">
         <v>84</v>
@@ -20021,10 +20049,10 @@
         <v>226</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>84</v>
@@ -20042,7 +20070,7 @@
         <v>84</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>94</v>
@@ -20066,16 +20094,16 @@
         <v>84</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AO134" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AP134" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AQ134" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AR134" t="s" s="2">
         <v>84</v>
@@ -20083,10 +20111,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -20207,10 +20235,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -20333,10 +20361,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -20359,19 +20387,19 @@
         <v>95</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>84</v>
@@ -20420,7 +20448,7 @@
         <v>84</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>82</v>
@@ -20447,10 +20475,10 @@
         <v>84</v>
       </c>
       <c r="AO137" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AP137" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AQ137" t="s" s="2">
         <v>84</v>
@@ -20461,10 +20489,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -20585,10 +20613,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -20711,10 +20739,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -20740,16 +20768,16 @@
         <v>108</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>84</v>
@@ -20798,7 +20826,7 @@
         <v>84</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>82</v>
@@ -20810,10 +20838,10 @@
         <v>84</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>106</v>
+        <v>811</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>807</v>
+        <v>812</v>
       </c>
       <c r="AL140" t="s" s="2">
         <v>84</v>
@@ -20825,10 +20853,10 @@
         <v>84</v>
       </c>
       <c r="AO140" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AP140" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AQ140" t="s" s="2">
         <v>84</v>
@@ -20839,10 +20867,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -20868,13 +20896,13 @@
         <v>208</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -20924,7 +20952,7 @@
         <v>84</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>82</v>
@@ -20951,10 +20979,10 @@
         <v>84</v>
       </c>
       <c r="AO141" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AP141" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AQ141" t="s" s="2">
         <v>84</v>
@@ -20965,10 +20993,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>809</v>
+        <v>814</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -20994,14 +21022,14 @@
         <v>114</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>84</v>
@@ -21050,7 +21078,7 @@
         <v>84</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>82</v>
@@ -21062,10 +21090,10 @@
         <v>84</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>106</v>
+        <v>815</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>84</v>
@@ -21077,10 +21105,10 @@
         <v>84</v>
       </c>
       <c r="AO142" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AP142" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AQ142" t="s" s="2">
         <v>84</v>
@@ -21091,10 +21119,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -21120,14 +21148,14 @@
         <v>208</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>84</v>
@@ -21176,7 +21204,7 @@
         <v>84</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>82</v>
@@ -21203,10 +21231,10 @@
         <v>84</v>
       </c>
       <c r="AO143" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AP143" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AQ143" t="s" s="2">
         <v>84</v>
@@ -21217,10 +21245,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>812</v>
+        <v>818</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -21243,19 +21271,19 @@
         <v>95</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O144" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>84</v>
@@ -21304,7 +21332,7 @@
         <v>84</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>82</v>
@@ -21331,10 +21359,10 @@
         <v>84</v>
       </c>
       <c r="AO144" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AP144" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AQ144" t="s" s="2">
         <v>84</v>
@@ -21345,10 +21373,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>813</v>
+        <v>819</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -21374,16 +21402,16 @@
         <v>208</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>84</v>
@@ -21432,7 +21460,7 @@
         <v>84</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>82</v>
@@ -21459,10 +21487,10 @@
         <v>84</v>
       </c>
       <c r="AO145" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP145" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AQ145" t="s" s="2">
         <v>84</v>
@@ -21473,10 +21501,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>814</v>
+        <v>820</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -21499,19 +21527,19 @@
         <v>95</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>84</v>
@@ -21539,10 +21567,10 @@
         <v>226</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>84</v>
@@ -21560,7 +21588,7 @@
         <v>84</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>82</v>
@@ -21569,7 +21597,7 @@
         <v>94</v>
       </c>
       <c r="AI146" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AJ146" t="s" s="2">
         <v>106</v>
@@ -21584,27 +21612,27 @@
         <v>84</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AO146" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AP146" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AQ146" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR146" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>815</v>
+        <v>821</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -21725,10 +21753,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>816</v>
+        <v>822</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -21851,10 +21879,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -21877,19 +21905,19 @@
         <v>95</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>84</v>
@@ -21938,7 +21966,7 @@
         <v>84</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>82</v>
@@ -21953,10 +21981,10 @@
         <v>106</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>818</v>
+        <v>824</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AM149" t="s" s="2">
         <v>84</v>
@@ -21965,10 +21993,10 @@
         <v>84</v>
       </c>
       <c r="AO149" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AP149" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AQ149" t="s" s="2">
         <v>84</v>
@@ -21979,10 +22007,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -22008,20 +22036,20 @@
         <v>114</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q150" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="R150" t="s" s="2">
         <v>84</v>
@@ -22045,10 +22073,10 @@
         <v>174</v>
       </c>
       <c r="Y150" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="Z150" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>84</v>
@@ -22066,7 +22094,7 @@
         <v>84</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>82</v>
@@ -22093,10 +22121,10 @@
         <v>84</v>
       </c>
       <c r="AO150" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AP150" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AQ150" t="s" s="2">
         <v>84</v>
@@ -22107,10 +22135,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -22136,14 +22164,14 @@
         <v>208</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>84</v>
@@ -22192,7 +22220,7 @@
         <v>84</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>82</v>
@@ -22219,10 +22247,10 @@
         <v>84</v>
       </c>
       <c r="AO151" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AP151" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AQ151" t="s" s="2">
         <v>84</v>
@@ -22233,10 +22261,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -22262,21 +22290,21 @@
         <v>108</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q152" s="2"/>
       <c r="R152" t="s" s="2">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="S152" t="s" s="2">
         <v>84</v>
@@ -22318,7 +22346,7 @@
         <v>84</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>82</v>
@@ -22327,7 +22355,7 @@
         <v>94</v>
       </c>
       <c r="AI152" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AJ152" t="s" s="2">
         <v>106</v>
@@ -22345,10 +22373,10 @@
         <v>84</v>
       </c>
       <c r="AO152" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AP152" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AQ152" t="s" s="2">
         <v>84</v>
@@ -22359,10 +22387,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>822</v>
+        <v>828</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -22388,23 +22416,23 @@
         <v>114</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="O153" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q153" s="2"/>
       <c r="R153" t="s" s="2">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="S153" t="s" s="2">
         <v>84</v>
@@ -22446,7 +22474,7 @@
         <v>84</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>82</v>
@@ -22458,10 +22486,10 @@
         <v>84</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>106</v>
+        <v>829</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>823</v>
+        <v>830</v>
       </c>
       <c r="AL153" t="s" s="2">
         <v>84</v>
@@ -22473,10 +22501,10 @@
         <v>84</v>
       </c>
       <c r="AO153" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AP153" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AQ153" t="s" s="2">
         <v>84</v>
@@ -22487,10 +22515,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>824</v>
+        <v>831</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -22516,16 +22544,16 @@
         <v>171</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>84</v>
@@ -22553,10 +22581,10 @@
         <v>226</v>
       </c>
       <c r="Y154" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="Z154" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>84</v>
@@ -22574,7 +22602,7 @@
         <v>84</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>82</v>
@@ -22583,7 +22611,7 @@
         <v>94</v>
       </c>
       <c r="AI154" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AJ154" t="s" s="2">
         <v>106</v>
@@ -22604,7 +22632,7 @@
         <v>137</v>
       </c>
       <c r="AP154" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AQ154" t="s" s="2">
         <v>84</v>
@@ -22615,14 +22643,14 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>825</v>
+        <v>832</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
@@ -22644,16 +22672,16 @@
         <v>171</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>84</v>
@@ -22681,10 +22709,10 @@
         <v>226</v>
       </c>
       <c r="Y155" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z155" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AA155" t="s" s="2">
         <v>84</v>
@@ -22702,7 +22730,7 @@
         <v>84</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>82</v>
@@ -22726,27 +22754,27 @@
         <v>84</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AO155" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AP155" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AQ155" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR155" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>826</v>
+        <v>833</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -22772,16 +22800,16 @@
         <v>85</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>84</v>
@@ -22830,7 +22858,7 @@
         <v>84</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>82</v>
@@ -22857,10 +22885,10 @@
         <v>84</v>
       </c>
       <c r="AO156" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AP156" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AQ156" t="s" s="2">
         <v>84</v>
@@ -22871,13 +22899,13 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>827</v>
+        <v>834</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>828</v>
+        <v>835</v>
       </c>
       <c r="D157" t="s" s="2">
         <v>84</v>
@@ -22899,19 +22927,19 @@
         <v>95</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>84</v>
@@ -22960,7 +22988,7 @@
         <v>84</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>82</v>
@@ -22972,7 +23000,7 @@
         <v>84</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AK157" t="s" s="2">
         <v>84</v>
@@ -22987,10 +23015,10 @@
         <v>84</v>
       </c>
       <c r="AO157" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AP157" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AQ157" t="s" s="2">
         <v>84</v>
@@ -23001,10 +23029,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>829</v>
+        <v>836</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -23125,10 +23153,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>830</v>
+        <v>837</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -23251,14 +23279,14 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>831</v>
+        <v>838</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
@@ -23280,10 +23308,10 @@
         <v>139</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="N160" t="s" s="2">
         <v>195</v>
@@ -23338,7 +23366,7 @@
         <v>84</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>82</v>
@@ -23379,10 +23407,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>832</v>
+        <v>839</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -23408,16 +23436,16 @@
         <v>171</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>84</v>
@@ -23427,7 +23455,7 @@
         <v>84</v>
       </c>
       <c r="S161" t="s" s="2">
-        <v>833</v>
+        <v>840</v>
       </c>
       <c r="T161" t="s" s="2">
         <v>84</v>
@@ -23445,10 +23473,10 @@
         <v>226</v>
       </c>
       <c r="Y161" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Z161" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AA161" t="s" s="2">
         <v>84</v>
@@ -23466,7 +23494,7 @@
         <v>84</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>94</v>
@@ -23481,7 +23509,7 @@
         <v>106</v>
       </c>
       <c r="AK161" t="s" s="2">
-        <v>834</v>
+        <v>841</v>
       </c>
       <c r="AL161" t="s" s="2">
         <v>84</v>
@@ -23490,16 +23518,16 @@
         <v>84</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AO161" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AP161" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AQ161" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AR161" t="s" s="2">
         <v>84</v>
@@ -23507,10 +23535,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>835</v>
+        <v>842</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -23533,19 +23561,19 @@
         <v>95</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="O162" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>84</v>
@@ -23573,16 +23601,16 @@
         <v>226</v>
       </c>
       <c r="Y162" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Z162" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AA162" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB162" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AC162" s="2"/>
       <c r="AD162" t="s" s="2">
@@ -23592,7 +23620,7 @@
         <v>143</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>82</v>
@@ -23601,7 +23629,7 @@
         <v>94</v>
       </c>
       <c r="AI162" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AJ162" t="s" s="2">
         <v>106</v>
@@ -23616,30 +23644,30 @@
         <v>84</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AO162" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AP162" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AQ162" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR162" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>836</v>
+        <v>843</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>837</v>
+        <v>844</v>
       </c>
       <c r="D163" t="s" s="2">
         <v>84</v>
@@ -23664,16 +23692,16 @@
         <v>171</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>84</v>
@@ -23701,10 +23729,10 @@
         <v>226</v>
       </c>
       <c r="Y163" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Z163" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>84</v>
@@ -23722,7 +23750,7 @@
         <v>84</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>82</v>
@@ -23731,7 +23759,7 @@
         <v>94</v>
       </c>
       <c r="AI163" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AJ163" t="s" s="2">
         <v>106</v>
@@ -23746,27 +23774,27 @@
         <v>84</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AO163" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AP163" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AQ163" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR163" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>838</v>
+        <v>845</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -23887,10 +23915,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>839</v>
+        <v>846</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -24013,10 +24041,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>840</v>
+        <v>847</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>841</v>
+        <v>848</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -24039,19 +24067,19 @@
         <v>95</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O166" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>84</v>
@@ -24080,7 +24108,7 @@
       </c>
       <c r="Y166" s="2"/>
       <c r="Z166" t="s" s="2">
-        <v>842</v>
+        <v>849</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>84</v>
@@ -24098,7 +24126,7 @@
         <v>84</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>82</v>
@@ -24113,7 +24141,7 @@
         <v>106</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>843</v>
+        <v>850</v>
       </c>
       <c r="AL166" t="s" s="2">
         <v>84</v>
@@ -24125,10 +24153,10 @@
         <v>84</v>
       </c>
       <c r="AO166" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AP166" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AQ166" t="s" s="2">
         <v>84</v>
@@ -24139,10 +24167,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>844</v>
+        <v>851</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>845</v>
+        <v>852</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -24168,16 +24196,16 @@
         <v>208</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>84</v>
@@ -24226,7 +24254,7 @@
         <v>84</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>82</v>
@@ -24253,10 +24281,10 @@
         <v>84</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP167" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AQ167" t="s" s="2">
         <v>84</v>
@@ -24267,10 +24295,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>846</v>
+        <v>853</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -24296,16 +24324,16 @@
         <v>171</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>84</v>
@@ -24333,10 +24361,10 @@
         <v>226</v>
       </c>
       <c r="Y168" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="Z168" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>84</v>
@@ -24354,7 +24382,7 @@
         <v>84</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>82</v>
@@ -24363,7 +24391,7 @@
         <v>94</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AJ168" t="s" s="2">
         <v>106</v>
@@ -24384,7 +24412,7 @@
         <v>137</v>
       </c>
       <c r="AP168" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AQ168" t="s" s="2">
         <v>84</v>
@@ -24395,14 +24423,14 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>847</v>
+        <v>854</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
@@ -24424,16 +24452,16 @@
         <v>171</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>84</v>
@@ -24461,10 +24489,10 @@
         <v>226</v>
       </c>
       <c r="Y169" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z169" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>84</v>
@@ -24482,7 +24510,7 @@
         <v>84</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>82</v>
@@ -24506,27 +24534,27 @@
         <v>84</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AO169" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AP169" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AQ169" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR169" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>848</v>
+        <v>855</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -24552,16 +24580,16 @@
         <v>85</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="O170" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>84</v>
@@ -24610,7 +24638,7 @@
         <v>84</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>82</v>
@@ -24637,10 +24665,10 @@
         <v>84</v>
       </c>
       <c r="AO170" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AP170" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AQ170" t="s" s="2">
         <v>84</v>
@@ -24651,13 +24679,13 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>849</v>
+        <v>856</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>850</v>
+        <v>857</v>
       </c>
       <c r="D171" t="s" s="2">
         <v>84</v>
@@ -24679,19 +24707,19 @@
         <v>95</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="O171" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>84</v>
@@ -24740,7 +24768,7 @@
         <v>84</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>82</v>
@@ -24752,7 +24780,7 @@
         <v>84</v>
       </c>
       <c r="AJ171" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AK171" t="s" s="2">
         <v>84</v>
@@ -24767,10 +24795,10 @@
         <v>84</v>
       </c>
       <c r="AO171" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AP171" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AQ171" t="s" s="2">
         <v>84</v>
@@ -24781,10 +24809,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>851</v>
+        <v>858</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -24905,10 +24933,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>852</v>
+        <v>859</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -25031,14 +25059,14 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>853</v>
+        <v>860</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E174" s="2"/>
       <c r="F174" t="s" s="2">
@@ -25060,10 +25088,10 @@
         <v>139</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="N174" t="s" s="2">
         <v>195</v>
@@ -25118,7 +25146,7 @@
         <v>84</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>82</v>
@@ -25159,10 +25187,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>854</v>
+        <v>861</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -25188,16 +25216,16 @@
         <v>171</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="O175" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>84</v>
@@ -25207,7 +25235,7 @@
         <v>84</v>
       </c>
       <c r="S175" t="s" s="2">
-        <v>855</v>
+        <v>862</v>
       </c>
       <c r="T175" t="s" s="2">
         <v>84</v>
@@ -25225,10 +25253,10 @@
         <v>226</v>
       </c>
       <c r="Y175" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Z175" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AA175" t="s" s="2">
         <v>84</v>
@@ -25246,7 +25274,7 @@
         <v>84</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>94</v>
@@ -25261,7 +25289,7 @@
         <v>106</v>
       </c>
       <c r="AK175" t="s" s="2">
-        <v>856</v>
+        <v>863</v>
       </c>
       <c r="AL175" t="s" s="2">
         <v>84</v>
@@ -25270,16 +25298,16 @@
         <v>84</v>
       </c>
       <c r="AN175" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AO175" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AP175" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AQ175" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AR175" t="s" s="2">
         <v>84</v>
@@ -25287,10 +25315,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>857</v>
+        <v>864</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -25313,19 +25341,19 @@
         <v>95</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="O176" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>84</v>
@@ -25353,16 +25381,16 @@
         <v>226</v>
       </c>
       <c r="Y176" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Z176" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB176" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AC176" s="2"/>
       <c r="AD176" t="s" s="2">
@@ -25372,7 +25400,7 @@
         <v>143</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>82</v>
@@ -25381,7 +25409,7 @@
         <v>94</v>
       </c>
       <c r="AI176" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AJ176" t="s" s="2">
         <v>106</v>
@@ -25396,30 +25424,30 @@
         <v>84</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AO176" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AP176" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AQ176" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR176" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>858</v>
+        <v>865</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>837</v>
+        <v>844</v>
       </c>
       <c r="D177" t="s" s="2">
         <v>84</v>
@@ -25444,16 +25472,16 @@
         <v>171</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="O177" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>84</v>
@@ -25481,10 +25509,10 @@
         <v>226</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>84</v>
@@ -25502,7 +25530,7 @@
         <v>84</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>82</v>
@@ -25511,7 +25539,7 @@
         <v>94</v>
       </c>
       <c r="AI177" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AJ177" t="s" s="2">
         <v>106</v>
@@ -25526,27 +25554,27 @@
         <v>84</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AO177" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AP177" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AQ177" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR177" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>859</v>
+        <v>866</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -25667,10 +25695,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>860</v>
+        <v>867</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -25793,10 +25821,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>861</v>
+        <v>868</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>841</v>
+        <v>848</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -25819,19 +25847,19 @@
         <v>95</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O180" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>84</v>
@@ -25860,7 +25888,7 @@
       </c>
       <c r="Y180" s="2"/>
       <c r="Z180" t="s" s="2">
-        <v>862</v>
+        <v>869</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>84</v>
@@ -25878,7 +25906,7 @@
         <v>84</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>82</v>
@@ -25893,7 +25921,7 @@
         <v>106</v>
       </c>
       <c r="AK180" t="s" s="2">
-        <v>863</v>
+        <v>870</v>
       </c>
       <c r="AL180" t="s" s="2">
         <v>84</v>
@@ -25905,10 +25933,10 @@
         <v>84</v>
       </c>
       <c r="AO180" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AP180" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AQ180" t="s" s="2">
         <v>84</v>
@@ -25919,10 +25947,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>864</v>
+        <v>871</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>845</v>
+        <v>852</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -25948,16 +25976,16 @@
         <v>208</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O181" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>84</v>
@@ -26006,7 +26034,7 @@
         <v>84</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>82</v>
@@ -26033,10 +26061,10 @@
         <v>84</v>
       </c>
       <c r="AO181" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP181" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AQ181" t="s" s="2">
         <v>84</v>
@@ -26047,10 +26075,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>865</v>
+        <v>872</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -26076,16 +26104,16 @@
         <v>171</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="O182" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>84</v>
@@ -26113,10 +26141,10 @@
         <v>226</v>
       </c>
       <c r="Y182" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="Z182" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AA182" t="s" s="2">
         <v>84</v>
@@ -26134,7 +26162,7 @@
         <v>84</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>82</v>
@@ -26143,7 +26171,7 @@
         <v>94</v>
       </c>
       <c r="AI182" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AJ182" t="s" s="2">
         <v>106</v>
@@ -26164,7 +26192,7 @@
         <v>137</v>
       </c>
       <c r="AP182" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AQ182" t="s" s="2">
         <v>84</v>
@@ -26175,14 +26203,14 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>866</v>
+        <v>873</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
@@ -26204,16 +26232,16 @@
         <v>171</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>84</v>
@@ -26241,10 +26269,10 @@
         <v>226</v>
       </c>
       <c r="Y183" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z183" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AA183" t="s" s="2">
         <v>84</v>
@@ -26262,7 +26290,7 @@
         <v>84</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>82</v>
@@ -26286,27 +26314,27 @@
         <v>84</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AO183" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AP183" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AQ183" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR183" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>867</v>
+        <v>874</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -26332,16 +26360,16 @@
         <v>85</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="O184" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>84</v>
@@ -26390,7 +26418,7 @@
         <v>84</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>82</v>
@@ -26417,10 +26445,10 @@
         <v>84</v>
       </c>
       <c r="AO184" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AP184" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AQ184" t="s" s="2">
         <v>84</v>
@@ -26431,13 +26459,13 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>868</v>
+        <v>875</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>869</v>
+        <v>876</v>
       </c>
       <c r="D185" t="s" s="2">
         <v>84</v>
@@ -26459,19 +26487,19 @@
         <v>95</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="O185" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>84</v>
@@ -26520,7 +26548,7 @@
         <v>84</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>82</v>
@@ -26532,7 +26560,7 @@
         <v>84</v>
       </c>
       <c r="AJ185" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AK185" t="s" s="2">
         <v>84</v>
@@ -26547,10 +26575,10 @@
         <v>84</v>
       </c>
       <c r="AO185" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AP185" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AQ185" t="s" s="2">
         <v>84</v>
@@ -26561,10 +26589,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>870</v>
+        <v>877</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -26685,10 +26713,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>871</v>
+        <v>878</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -26811,14 +26839,14 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E188" s="2"/>
       <c r="F188" t="s" s="2">
@@ -26840,10 +26868,10 @@
         <v>139</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="N188" t="s" s="2">
         <v>195</v>
@@ -26898,7 +26926,7 @@
         <v>84</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>82</v>
@@ -26939,10 +26967,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>873</v>
+        <v>880</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -26968,16 +26996,16 @@
         <v>171</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="N189" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="O189" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="P189" t="s" s="2">
         <v>84</v>
@@ -26987,7 +27015,7 @@
         <v>84</v>
       </c>
       <c r="S189" t="s" s="2">
-        <v>855</v>
+        <v>862</v>
       </c>
       <c r="T189" t="s" s="2">
         <v>84</v>
@@ -27005,10 +27033,10 @@
         <v>226</v>
       </c>
       <c r="Y189" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Z189" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AA189" t="s" s="2">
         <v>84</v>
@@ -27026,7 +27054,7 @@
         <v>84</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>94</v>
@@ -27041,7 +27069,7 @@
         <v>106</v>
       </c>
       <c r="AK189" t="s" s="2">
-        <v>874</v>
+        <v>881</v>
       </c>
       <c r="AL189" t="s" s="2">
         <v>84</v>
@@ -27050,16 +27078,16 @@
         <v>84</v>
       </c>
       <c r="AN189" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AO189" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AP189" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AQ189" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AR189" t="s" s="2">
         <v>84</v>
@@ -27067,10 +27095,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>875</v>
+        <v>882</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -27093,19 +27121,19 @@
         <v>95</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="O190" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P190" t="s" s="2">
         <v>84</v>
@@ -27133,16 +27161,16 @@
         <v>226</v>
       </c>
       <c r="Y190" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Z190" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AA190" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB190" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AC190" s="2"/>
       <c r="AD190" t="s" s="2">
@@ -27152,7 +27180,7 @@
         <v>143</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>82</v>
@@ -27161,7 +27189,7 @@
         <v>94</v>
       </c>
       <c r="AI190" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AJ190" t="s" s="2">
         <v>106</v>
@@ -27176,30 +27204,30 @@
         <v>84</v>
       </c>
       <c r="AN190" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AO190" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AP190" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AQ190" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR190" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>876</v>
+        <v>883</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>837</v>
+        <v>844</v>
       </c>
       <c r="D191" t="s" s="2">
         <v>84</v>
@@ -27224,16 +27252,16 @@
         <v>171</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="O191" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>84</v>
@@ -27261,10 +27289,10 @@
         <v>226</v>
       </c>
       <c r="Y191" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Z191" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AA191" t="s" s="2">
         <v>84</v>
@@ -27282,7 +27310,7 @@
         <v>84</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>82</v>
@@ -27291,7 +27319,7 @@
         <v>94</v>
       </c>
       <c r="AI191" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AJ191" t="s" s="2">
         <v>106</v>
@@ -27306,27 +27334,27 @@
         <v>84</v>
       </c>
       <c r="AN191" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AO191" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AP191" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AQ191" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR191" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>877</v>
+        <v>884</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -27447,10 +27475,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>878</v>
+        <v>885</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -27573,10 +27601,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>879</v>
+        <v>886</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>841</v>
+        <v>848</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -27599,19 +27627,19 @@
         <v>95</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O194" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P194" t="s" s="2">
         <v>84</v>
@@ -27640,7 +27668,7 @@
       </c>
       <c r="Y194" s="2"/>
       <c r="Z194" t="s" s="2">
-        <v>880</v>
+        <v>887</v>
       </c>
       <c r="AA194" t="s" s="2">
         <v>84</v>
@@ -27658,7 +27686,7 @@
         <v>84</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>82</v>
@@ -27673,7 +27701,7 @@
         <v>106</v>
       </c>
       <c r="AK194" t="s" s="2">
-        <v>881</v>
+        <v>888</v>
       </c>
       <c r="AL194" t="s" s="2">
         <v>84</v>
@@ -27685,10 +27713,10 @@
         <v>84</v>
       </c>
       <c r="AO194" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AP194" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AQ194" t="s" s="2">
         <v>84</v>
@@ -27699,10 +27727,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>882</v>
+        <v>889</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>845</v>
+        <v>852</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -27728,16 +27756,16 @@
         <v>208</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N195" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O195" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P195" t="s" s="2">
         <v>84</v>
@@ -27786,7 +27814,7 @@
         <v>84</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>82</v>
@@ -27813,10 +27841,10 @@
         <v>84</v>
       </c>
       <c r="AO195" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP195" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AQ195" t="s" s="2">
         <v>84</v>
@@ -27827,10 +27855,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>883</v>
+        <v>890</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -27856,16 +27884,16 @@
         <v>171</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="O196" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="P196" t="s" s="2">
         <v>84</v>
@@ -27893,10 +27921,10 @@
         <v>226</v>
       </c>
       <c r="Y196" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="Z196" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AA196" t="s" s="2">
         <v>84</v>
@@ -27914,7 +27942,7 @@
         <v>84</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>82</v>
@@ -27923,7 +27951,7 @@
         <v>94</v>
       </c>
       <c r="AI196" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AJ196" t="s" s="2">
         <v>106</v>
@@ -27944,7 +27972,7 @@
         <v>137</v>
       </c>
       <c r="AP196" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AQ196" t="s" s="2">
         <v>84</v>
@@ -27955,14 +27983,14 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>884</v>
+        <v>891</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E197" s="2"/>
       <c r="F197" t="s" s="2">
@@ -27984,16 +28012,16 @@
         <v>171</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="O197" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="P197" t="s" s="2">
         <v>84</v>
@@ -28021,10 +28049,10 @@
         <v>226</v>
       </c>
       <c r="Y197" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z197" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AA197" t="s" s="2">
         <v>84</v>
@@ -28042,7 +28070,7 @@
         <v>84</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>82</v>
@@ -28066,27 +28094,27 @@
         <v>84</v>
       </c>
       <c r="AN197" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AO197" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AP197" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AQ197" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR197" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>885</v>
+        <v>892</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -28112,16 +28140,16 @@
         <v>85</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N198" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="O198" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="P198" t="s" s="2">
         <v>84</v>
@@ -28170,7 +28198,7 @@
         <v>84</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>82</v>
@@ -28197,10 +28225,10 @@
         <v>84</v>
       </c>
       <c r="AO198" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AP198" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AQ198" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -919,7 +919,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-VitalSignsBP-655:if null then fixed value #final {null}VitalSignsBP-656:if not null then fixed value #entered-in-error {null}</t>
+vsbp-12-655:120.5-4: if null then #final {null}vsbp-12-656:120.5-4: if not null then #entered-in-error {null}</t>
   </si>
   <si>
     <t>656: fixed value = #entered-in-error when GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (120.5-4) case not null</t>
@@ -2393,7 +2393,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-VitalSignsBP-666-2:if VUID = 4500634 then fixed value http://loinc.org {null}</t>
+vsbp-12-666-2:undefined: if VUID = 4500634 then http://loinc.org {null}</t>
   </si>
   <si>
     <t>666-2: fixed value = http://loinc.org case VUID = 4500634</t>
@@ -2412,7 +2412,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-VitalSignsBP-666-3:if VUID = 4500634 then fixed value 8480-6 {null}</t>
+vsbp-12-666-3:undefined: if VUID = 4500634 then 8480-6 {null}</t>
   </si>
   <si>
     <t>666-3: fixed value = 8480-6 case VUID = 4500634</t>
@@ -2491,7 +2491,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-VitalSignsBP-666-1:if VUID = 4500634 then fixed value mm[Hg] {null}</t>
+vsbp-12-666-1:undefined: if VUID = 4500634 then mm[Hg] {null}</t>
   </si>
   <si>
     <t>666-1: fixed value = mm[Hg] case VUID = 4500634</t>
@@ -2557,7 +2557,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-VitalSignsBP-667-2:if VUID = 4500634 then fixed value http://loinc.org {null}</t>
+vsbp-12-667-2:undefined: if VUID = 4500634 then http://loinc.org {null}</t>
   </si>
   <si>
     <t>667-2: fixed value = http://loinc.org case VUID = 4500634</t>
@@ -2570,7 +2570,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-VitalSignsBP-667-3:if VUID = 4500634 then fixed value 8462-4 {null}</t>
+vsbp-12-667-3:undefined: if VUID = 4500634 then 8462-4 {null}</t>
   </si>
   <si>
     <t>667-3: fixed value = 8462-4 case VUID = 4500634</t>
@@ -2613,7 +2613,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-VitalSignsBP-667-1:if VUID = 4500634 then fixed value mm[Hg] {null}</t>
+vsbp-12-667-1:undefined: if VUID = 4500634 then mm[Hg] {null}</t>
   </si>
   <si>
     <t>667-1: fixed value = mm[Hg] case VUID = 4500634</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -243,7 +243,7 @@
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
+    <t>Mapping: Summary Document Architecure (SDA)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -577,6 +577,9 @@
     <t>663: terminologyMaps using VF_VitalsMeasurementDevice on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
   </si>
   <si>
+    <t>Observation.ObservationMethods</t>
+  </si>
+  <si>
     <t>Observation.extension:observation-bodyPosition</t>
   </si>
   <si>
@@ -928,7 +931,7 @@
     <t>656: fixed value = #entered-in-error when GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (120.5-4) case not null</t>
   </si>
   <si>
-    <t>vital.removed [m]</t>
+    <t>Observation.ObservationExtension.Removed</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -1281,7 +1284,7 @@
     <t>Vital.VitalSign.VitalTypeIEN</t>
   </si>
   <si>
-    <t>vital.vuid,vital.name,vital.high,vital.low,vital.bmi</t>
+    <t>Observation.ObservationCode,Observation.ObservationExtension.BMI</t>
   </si>
   <si>
     <t>Observation.code.text</t>
@@ -1441,7 +1444,7 @@
     <t>Vital.VitalSign.VitalSignTakenDateTime,Vital.VitalSignQualifier.VitalSignTakenDateTime</t>
   </si>
   <si>
-    <t>vital.taken</t>
+    <t>Observation.Observation.Description,Observation.ObservationMethod.Description</t>
   </si>
   <si>
     <t>Observation.issued</t>
@@ -1466,9 +1469,6 @@
     <t>Vital.VitalSign.VitalSignEnteredDateTime</t>
   </si>
   <si>
-    <t>vital.entered</t>
-  </si>
-  <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
   </si>
   <si>
@@ -1500,7 +1500,7 @@
     <t>Vital.VitalSign.LocationIEN</t>
   </si>
   <si>
-    <t>vital.facility,vital.location</t>
+    <t>Observation.EnteredAt,Observation.ObservationExtension.Location</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1609,7 +1609,7 @@
     <t>Vital.VitalSign.Diastolic,Vital.VitalSign.Systolic,Vital.VitalSign.VitalResult,Vital.VitalSign.VitalResultNumeric</t>
   </si>
   <si>
-    <t>vital.value,vital.units,vital.metricvalue,vital.metricUnits,vital.bmi</t>
+    <t>Observation.ObservationValue,Observation.ObservationExtension.BMI</t>
   </si>
   <si>
     <t>SN.2  / CQ - N/A</t>
@@ -3192,7 +3192,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="150.6015625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="98.75" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="60.49609375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="76.37109375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="247.40625" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>
@@ -4980,7 +4980,7 @@
         <v>85</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>85</v>
@@ -5003,13 +5003,13 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>139</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>85</v>
@@ -5031,13 +5031,13 @@
         <v>85</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -5132,7 +5132,7 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>153</v>
@@ -5259,7 +5259,7 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>160</v>
@@ -5386,7 +5386,7 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B18" t="s" s="2">
         <v>164</v>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>85</v>
@@ -5515,7 +5515,7 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B19" t="s" s="2">
         <v>171</v>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>85</v>
@@ -5611,13 +5611,13 @@
         <v>107</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>85</v>
@@ -5640,14 +5640,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -5669,16 +5669,16 @@
         <v>140</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>85</v>
@@ -5727,7 +5727,7 @@
         <v>85</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>83</v>
@@ -5771,10 +5771,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5797,17 +5797,17 @@
         <v>96</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>85</v>
@@ -5856,7 +5856,7 @@
         <v>85</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>83</v>
@@ -5880,19 +5880,19 @@
         <v>85</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AS21" t="s" s="2">
         <v>85</v>
@@ -5900,10 +5900,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5926,7 +5926,7 @@
         <v>85</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>154</v>
@@ -6027,14 +6027,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -6056,13 +6056,13 @@
         <v>140</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -6156,10 +6156,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -6185,16 +6185,16 @@
         <v>115</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>85</v>
@@ -6222,10 +6222,10 @@
         <v>175</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>85</v>
@@ -6243,7 +6243,7 @@
         <v>85</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>83</v>
@@ -6276,7 +6276,7 @@
         <v>138</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>85</v>
@@ -6287,10 +6287,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -6316,16 +6316,16 @@
         <v>172</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>85</v>
@@ -6350,13 +6350,13 @@
         <v>85</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>85</v>
@@ -6374,7 +6374,7 @@
         <v>85</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>83</v>
@@ -6404,10 +6404,10 @@
         <v>85</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AR25" t="s" s="2">
         <v>85</v>
@@ -6418,10 +6418,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -6447,16 +6447,16 @@
         <v>109</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>85</v>
@@ -6466,10 +6466,10 @@
         <v>85</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>85</v>
@@ -6505,7 +6505,7 @@
         <v>85</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>83</v>
@@ -6520,7 +6520,7 @@
         <v>107</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>85</v>
@@ -6535,10 +6535,10 @@
         <v>85</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AR26" t="s" s="2">
         <v>85</v>
@@ -6549,10 +6549,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -6575,16 +6575,16 @@
         <v>96</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -6598,7 +6598,7 @@
         <v>85</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>85</v>
@@ -6634,7 +6634,7 @@
         <v>85</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>83</v>
@@ -6649,7 +6649,7 @@
         <v>107</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>85</v>
@@ -6664,10 +6664,10 @@
         <v>85</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AR27" t="s" s="2">
         <v>85</v>
@@ -6678,10 +6678,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6704,13 +6704,13 @@
         <v>96</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -6761,7 +6761,7 @@
         <v>85</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>83</v>
@@ -6791,10 +6791,10 @@
         <v>85</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>85</v>
@@ -6805,10 +6805,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6831,16 +6831,16 @@
         <v>96</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6890,7 +6890,7 @@
         <v>85</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>83</v>
@@ -6920,10 +6920,10 @@
         <v>85</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AR29" t="s" s="2">
         <v>85</v>
@@ -6934,14 +6934,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -6960,17 +6960,17 @@
         <v>96</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>85</v>
@@ -7019,7 +7019,7 @@
         <v>85</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>83</v>
@@ -7043,16 +7043,16 @@
         <v>85</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>85</v>
@@ -7063,14 +7063,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -7089,16 +7089,16 @@
         <v>96</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -7148,7 +7148,7 @@
         <v>85</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>83</v>
@@ -7172,16 +7172,16 @@
         <v>85</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>85</v>
@@ -7192,10 +7192,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -7221,16 +7221,16 @@
         <v>115</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>85</v>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>85</v>
@@ -7277,7 +7277,7 @@
         <v>85</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>95</v>
@@ -7289,31 +7289,31 @@
         <v>85</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AR32" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AS32" t="s" s="2">
         <v>85</v>
@@ -7321,10 +7321,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -7350,16 +7350,16 @@
         <v>172</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>85</v>
@@ -7369,7 +7369,7 @@
         <v>85</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>85</v>
@@ -7387,16 +7387,16 @@
         <v>119</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
@@ -7406,7 +7406,7 @@
         <v>144</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>83</v>
@@ -7421,7 +7421,7 @@
         <v>107</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>85</v>
@@ -7439,10 +7439,10 @@
         <v>85</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AR33" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AS33" t="s" s="2">
         <v>85</v>
@@ -7450,13 +7450,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>85</v>
@@ -7481,16 +7481,16 @@
         <v>172</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>85</v>
@@ -7518,10 +7518,10 @@
         <v>119</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>85</v>
@@ -7539,7 +7539,7 @@
         <v>85</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>83</v>
@@ -7572,10 +7572,10 @@
         <v>85</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AS34" t="s" s="2">
         <v>85</v>
@@ -7583,10 +7583,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7609,7 +7609,7 @@
         <v>85</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>154</v>
@@ -7710,14 +7710,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -7739,13 +7739,13 @@
         <v>140</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -7839,10 +7839,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7865,19 +7865,19 @@
         <v>96</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>85</v>
@@ -7926,7 +7926,7 @@
         <v>85</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>83</v>
@@ -7956,10 +7956,10 @@
         <v>85</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>85</v>
@@ -7970,10 +7970,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7996,7 +7996,7 @@
         <v>85</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>154</v>
@@ -8097,14 +8097,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -8126,13 +8126,13 @@
         <v>140</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -8226,10 +8226,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -8255,23 +8255,23 @@
         <v>109</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>85</v>
@@ -8313,7 +8313,7 @@
         <v>85</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>83</v>
@@ -8343,10 +8343,10 @@
         <v>85</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>85</v>
@@ -8357,10 +8357,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -8383,16 +8383,16 @@
         <v>96</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -8442,7 +8442,7 @@
         <v>85</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>83</v>
@@ -8472,10 +8472,10 @@
         <v>85</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>85</v>
@@ -8486,10 +8486,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -8515,21 +8515,21 @@
         <v>115</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>85</v>
@@ -8571,7 +8571,7 @@
         <v>85</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>83</v>
@@ -8601,10 +8601,10 @@
         <v>85</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>85</v>
@@ -8615,10 +8615,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8641,17 +8641,17 @@
         <v>96</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>85</v>
@@ -8700,7 +8700,7 @@
         <v>85</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -8730,10 +8730,10 @@
         <v>85</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>85</v>
@@ -8744,10 +8744,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8770,19 +8770,19 @@
         <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>85</v>
@@ -8831,7 +8831,7 @@
         <v>85</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
@@ -8861,10 +8861,10 @@
         <v>85</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AR44" t="s" s="2">
         <v>85</v>
@@ -8875,10 +8875,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8901,19 +8901,19 @@
         <v>96</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>85</v>
@@ -8962,7 +8962,7 @@
         <v>85</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
@@ -8992,10 +8992,10 @@
         <v>85</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AR45" t="s" s="2">
         <v>85</v>
@@ -9006,14 +9006,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -9035,16 +9035,16 @@
         <v>172</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>85</v>
@@ -9054,7 +9054,7 @@
         <v>85</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>85</v>
@@ -9069,13 +9069,13 @@
         <v>85</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>85</v>
@@ -9093,7 +9093,7 @@
         <v>85</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>95</v>
@@ -9117,30 +9117,30 @@
         <v>85</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AS46" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -9163,7 +9163,7 @@
         <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L47" t="s" s="2">
         <v>154</v>
@@ -9264,14 +9264,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -9293,13 +9293,13 @@
         <v>140</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -9393,10 +9393,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -9419,19 +9419,19 @@
         <v>96</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>85</v>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>85</v>
@@ -9478,7 +9478,7 @@
         <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -9493,13 +9493,13 @@
         <v>107</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>85</v>
@@ -9508,10 +9508,10 @@
         <v>85</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>85</v>
@@ -9522,10 +9522,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9548,19 +9548,19 @@
         <v>96</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>85</v>
@@ -9609,7 +9609,7 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -9639,10 +9639,10 @@
         <v>85</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>85</v>
@@ -9653,10 +9653,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9679,19 +9679,19 @@
         <v>96</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>85</v>
@@ -9740,7 +9740,7 @@
         <v>85</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -9755,28 +9755,28 @@
         <v>107</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AS51" t="s" s="2">
         <v>85</v>
@@ -9784,10 +9784,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9810,16 +9810,16 @@
         <v>96</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -9869,7 +9869,7 @@
         <v>85</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
@@ -9899,13 +9899,13 @@
         <v>85</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AS52" t="s" s="2">
         <v>85</v>
@@ -9913,14 +9913,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -9939,19 +9939,19 @@
         <v>96</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>85</v>
@@ -10000,7 +10000,7 @@
         <v>85</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -10024,19 +10024,19 @@
         <v>85</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AR53" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AS53" t="s" s="2">
         <v>85</v>
@@ -10044,14 +10044,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -10070,19 +10070,19 @@
         <v>96</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>85</v>
@@ -10119,7 +10119,7 @@
         <v>85</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AC54" s="2"/>
       <c r="AD54" t="s" s="2">
@@ -10129,7 +10129,7 @@
         <v>144</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -10138,10 +10138,10 @@
         <v>95</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>85</v>
@@ -10153,19 +10153,19 @@
         <v>85</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AS54" t="s" s="2">
         <v>85</v>
@@ -10173,16 +10173,16 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -10201,19 +10201,19 @@
         <v>96</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>85</v>
@@ -10262,7 +10262,7 @@
         <v>85</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -10271,34 +10271,34 @@
         <v>95</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AR55" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AS55" t="s" s="2">
         <v>85</v>
@@ -10306,10 +10306,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -10332,16 +10332,16 @@
         <v>96</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -10391,7 +10391,7 @@
         <v>85</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -10406,13 +10406,13 @@
         <v>107</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>464</v>
+        <v>85</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>85</v>
@@ -10627,7 +10627,7 @@
         <v>85</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y58" t="s" s="2">
         <v>486</v>
@@ -10639,7 +10639,7 @@
         <v>85</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
@@ -10758,7 +10758,7 @@
         <v>85</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y59" t="s" s="2">
         <v>486</v>
@@ -10852,7 +10852,7 @@
         <v>85</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L60" t="s" s="2">
         <v>154</v>
@@ -10960,7 +10960,7 @@
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -10982,13 +10982,13 @@
         <v>140</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -11370,7 +11370,7 @@
         <v>96</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L64" t="s" s="2">
         <v>526</v>
@@ -11707,10 +11707,10 @@
         <v>547</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>85</v>
@@ -11759,7 +11759,7 @@
         <v>85</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L67" t="s" s="2">
         <v>551</v>
@@ -12652,7 +12652,7 @@
         <v>85</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L74" t="s" s="2">
         <v>574</v>
@@ -12816,7 +12816,7 @@
         <v>85</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y75" t="s" s="2">
         <v>581</v>
@@ -12947,7 +12947,7 @@
         <v>85</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y76" t="s" s="2">
         <v>592</v>
@@ -13250,7 +13250,7 @@
         <v>85</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>85</v>
@@ -13379,7 +13379,7 @@
         <v>85</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>85</v>
@@ -13817,7 +13817,7 @@
         <v>85</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L83" t="s" s="2">
         <v>154</v>
@@ -13925,7 +13925,7 @@
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -13947,13 +13947,13 @@
         <v>140</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -14082,10 +14082,10 @@
         <v>657</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>85</v>
@@ -14849,7 +14849,7 @@
         <v>85</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L91" t="s" s="2">
         <v>694</v>
@@ -15363,7 +15363,7 @@
         <v>85</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L95" t="s" s="2">
         <v>154</v>
@@ -15471,7 +15471,7 @@
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -15493,13 +15493,13 @@
         <v>140</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -15628,10 +15628,10 @@
         <v>657</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>85</v>
@@ -15787,13 +15787,13 @@
         <v>85</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>85</v>
@@ -15841,13 +15841,13 @@
         <v>728</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AQ98" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AR98" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AS98" t="s" s="2">
         <v>85</v>
@@ -15918,7 +15918,7 @@
         <v>85</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y99" t="s" s="2">
         <v>486</v>
@@ -16049,7 +16049,7 @@
         <v>85</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y100" t="s" s="2">
         <v>581</v>
@@ -16180,7 +16180,7 @@
         <v>85</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y101" t="s" s="2">
         <v>592</v>
@@ -16538,7 +16538,7 @@
         <v>85</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L104" t="s" s="2">
         <v>154</v>
@@ -16646,7 +16646,7 @@
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -16668,13 +16668,13 @@
         <v>140</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -16803,10 +16803,10 @@
         <v>657</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>85</v>
@@ -16962,13 +16962,13 @@
         <v>85</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>85</v>
@@ -17016,13 +17016,13 @@
         <v>728</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AQ107" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AR107" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AS107" t="s" s="2">
         <v>85</v>
@@ -17056,7 +17056,7 @@
         <v>85</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L108" t="s" s="2">
         <v>154</v>
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -17186,13 +17186,13 @@
         <v>140</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -17312,19 +17312,19 @@
         <v>96</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>85</v>
@@ -17373,7 +17373,7 @@
         <v>85</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>83</v>
@@ -17403,10 +17403,10 @@
         <v>85</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AQ110" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AR110" t="s" s="2">
         <v>85</v>
@@ -17443,7 +17443,7 @@
         <v>85</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L111" t="s" s="2">
         <v>154</v>
@@ -17551,7 +17551,7 @@
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -17573,13 +17573,13 @@
         <v>140</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -17702,16 +17702,16 @@
         <v>109</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>85</v>
@@ -17760,7 +17760,7 @@
         <v>85</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>83</v>
@@ -17790,10 +17790,10 @@
         <v>85</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AQ113" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AR113" t="s" s="2">
         <v>85</v>
@@ -17830,16 +17830,16 @@
         <v>96</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -17889,7 +17889,7 @@
         <v>85</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>83</v>
@@ -17919,10 +17919,10 @@
         <v>85</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AQ114" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AR114" t="s" s="2">
         <v>85</v>
@@ -17962,14 +17962,14 @@
         <v>115</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>85</v>
@@ -18018,7 +18018,7 @@
         <v>85</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>83</v>
@@ -18048,10 +18048,10 @@
         <v>85</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AQ115" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AR115" t="s" s="2">
         <v>85</v>
@@ -18088,17 +18088,17 @@
         <v>96</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>85</v>
@@ -18147,7 +18147,7 @@
         <v>85</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>83</v>
@@ -18177,10 +18177,10 @@
         <v>85</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AQ116" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AR116" t="s" s="2">
         <v>85</v>
@@ -18217,19 +18217,19 @@
         <v>96</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>85</v>
@@ -18278,7 +18278,7 @@
         <v>85</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>83</v>
@@ -18308,10 +18308,10 @@
         <v>85</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AQ117" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AR117" t="s" s="2">
         <v>85</v>
@@ -18348,19 +18348,19 @@
         <v>96</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>85</v>
@@ -18409,7 +18409,7 @@
         <v>85</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>83</v>
@@ -18439,10 +18439,10 @@
         <v>85</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AQ118" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AR118" t="s" s="2">
         <v>85</v>
@@ -18516,7 +18516,7 @@
         <v>85</v>
       </c>
       <c r="X119" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y119" t="s" s="2">
         <v>486</v>
@@ -18610,7 +18610,7 @@
         <v>85</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L120" t="s" s="2">
         <v>154</v>
@@ -18718,7 +18718,7 @@
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
@@ -18740,13 +18740,13 @@
         <v>140</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -19128,7 +19128,7 @@
         <v>96</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L124" t="s" s="2">
         <v>526</v>
@@ -19554,7 +19554,7 @@
         <v>85</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y127" t="s" s="2">
         <v>581</v>
@@ -19685,7 +19685,7 @@
         <v>85</v>
       </c>
       <c r="X128" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y128" t="s" s="2">
         <v>592</v>
@@ -20043,7 +20043,7 @@
         <v>85</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L131" t="s" s="2">
         <v>154</v>
@@ -20151,7 +20151,7 @@
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
@@ -20173,13 +20173,13 @@
         <v>140</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -20308,10 +20308,10 @@
         <v>657</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>85</v>
@@ -20467,13 +20467,13 @@
         <v>85</v>
       </c>
       <c r="X134" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>85</v>
@@ -20521,13 +20521,13 @@
         <v>728</v>
       </c>
       <c r="AP134" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AQ134" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AR134" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AS134" t="s" s="2">
         <v>85</v>
@@ -20561,7 +20561,7 @@
         <v>85</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L135" t="s" s="2">
         <v>154</v>
@@ -20669,7 +20669,7 @@
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
@@ -20691,13 +20691,13 @@
         <v>140</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -20817,19 +20817,19 @@
         <v>96</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>85</v>
@@ -20878,7 +20878,7 @@
         <v>85</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>83</v>
@@ -20908,10 +20908,10 @@
         <v>85</v>
       </c>
       <c r="AP137" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AQ137" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AR137" t="s" s="2">
         <v>85</v>
@@ -20948,7 +20948,7 @@
         <v>85</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L138" t="s" s="2">
         <v>154</v>
@@ -21056,7 +21056,7 @@
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
@@ -21078,13 +21078,13 @@
         <v>140</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -21207,16 +21207,16 @@
         <v>109</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>85</v>
@@ -21265,7 +21265,7 @@
         <v>85</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>83</v>
@@ -21295,10 +21295,10 @@
         <v>85</v>
       </c>
       <c r="AP140" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AQ140" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AR140" t="s" s="2">
         <v>85</v>
@@ -21335,16 +21335,16 @@
         <v>96</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -21394,7 +21394,7 @@
         <v>85</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>83</v>
@@ -21424,10 +21424,10 @@
         <v>85</v>
       </c>
       <c r="AP141" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AQ141" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AR141" t="s" s="2">
         <v>85</v>
@@ -21467,14 +21467,14 @@
         <v>115</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>85</v>
@@ -21523,7 +21523,7 @@
         <v>85</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>83</v>
@@ -21553,10 +21553,10 @@
         <v>85</v>
       </c>
       <c r="AP142" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AQ142" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AR142" t="s" s="2">
         <v>85</v>
@@ -21593,17 +21593,17 @@
         <v>96</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>85</v>
@@ -21652,7 +21652,7 @@
         <v>85</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>83</v>
@@ -21682,10 +21682,10 @@
         <v>85</v>
       </c>
       <c r="AP143" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AQ143" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AR143" t="s" s="2">
         <v>85</v>
@@ -21722,19 +21722,19 @@
         <v>96</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O144" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>85</v>
@@ -21783,7 +21783,7 @@
         <v>85</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>83</v>
@@ -21813,10 +21813,10 @@
         <v>85</v>
       </c>
       <c r="AP144" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AQ144" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AR144" t="s" s="2">
         <v>85</v>
@@ -21853,19 +21853,19 @@
         <v>96</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>85</v>
@@ -21914,7 +21914,7 @@
         <v>85</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>83</v>
@@ -21944,10 +21944,10 @@
         <v>85</v>
       </c>
       <c r="AP145" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AQ145" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AR145" t="s" s="2">
         <v>85</v>
@@ -22021,7 +22021,7 @@
         <v>85</v>
       </c>
       <c r="X146" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y146" t="s" s="2">
         <v>486</v>
@@ -22115,7 +22115,7 @@
         <v>85</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L147" t="s" s="2">
         <v>154</v>
@@ -22223,7 +22223,7 @@
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
@@ -22245,13 +22245,13 @@
         <v>140</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -22633,7 +22633,7 @@
         <v>96</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L151" t="s" s="2">
         <v>526</v>
@@ -23059,7 +23059,7 @@
         <v>85</v>
       </c>
       <c r="X154" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y154" t="s" s="2">
         <v>581</v>
@@ -23190,7 +23190,7 @@
         <v>85</v>
       </c>
       <c r="X155" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y155" t="s" s="2">
         <v>592</v>
@@ -23548,7 +23548,7 @@
         <v>85</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L158" t="s" s="2">
         <v>154</v>
@@ -23656,7 +23656,7 @@
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
@@ -23678,13 +23678,13 @@
         <v>140</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -23813,10 +23813,10 @@
         <v>657</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O160" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>85</v>
@@ -23972,13 +23972,13 @@
         <v>85</v>
       </c>
       <c r="X161" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y161" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Z161" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AA161" t="s" s="2">
         <v>85</v>
@@ -24026,13 +24026,13 @@
         <v>728</v>
       </c>
       <c r="AP161" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AQ161" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AR161" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AS161" t="s" s="2">
         <v>85</v>
@@ -24103,7 +24103,7 @@
         <v>85</v>
       </c>
       <c r="X162" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y162" t="s" s="2">
         <v>486</v>
@@ -24115,7 +24115,7 @@
         <v>85</v>
       </c>
       <c r="AB162" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AC162" s="2"/>
       <c r="AD162" t="s" s="2">
@@ -24234,7 +24234,7 @@
         <v>85</v>
       </c>
       <c r="X163" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y163" t="s" s="2">
         <v>486</v>
@@ -24328,7 +24328,7 @@
         <v>85</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L164" t="s" s="2">
         <v>154</v>
@@ -24436,7 +24436,7 @@
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E165" s="2"/>
       <c r="F165" t="s" s="2">
@@ -24458,13 +24458,13 @@
         <v>140</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -24584,19 +24584,19 @@
         <v>96</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O166" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>85</v>
@@ -24643,7 +24643,7 @@
         <v>85</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>83</v>
@@ -24664,7 +24664,7 @@
         <v>85</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="AN166" t="s" s="2">
         <v>85</v>
@@ -24673,10 +24673,10 @@
         <v>85</v>
       </c>
       <c r="AP166" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AQ166" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AR166" t="s" s="2">
         <v>85</v>
@@ -24713,19 +24713,19 @@
         <v>96</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>85</v>
@@ -24774,7 +24774,7 @@
         <v>85</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>83</v>
@@ -24804,10 +24804,10 @@
         <v>85</v>
       </c>
       <c r="AP167" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AQ167" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AR167" t="s" s="2">
         <v>85</v>
@@ -24881,7 +24881,7 @@
         <v>85</v>
       </c>
       <c r="X168" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y168" t="s" s="2">
         <v>581</v>
@@ -25012,7 +25012,7 @@
         <v>85</v>
       </c>
       <c r="X169" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y169" t="s" s="2">
         <v>592</v>
@@ -25370,7 +25370,7 @@
         <v>85</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L172" t="s" s="2">
         <v>154</v>
@@ -25478,7 +25478,7 @@
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E173" s="2"/>
       <c r="F173" t="s" s="2">
@@ -25500,13 +25500,13 @@
         <v>140</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
@@ -25635,10 +25635,10 @@
         <v>657</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O174" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>85</v>
@@ -25794,13 +25794,13 @@
         <v>85</v>
       </c>
       <c r="X175" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y175" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Z175" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AA175" t="s" s="2">
         <v>85</v>
@@ -25848,13 +25848,13 @@
         <v>728</v>
       </c>
       <c r="AP175" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AQ175" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AR175" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AS175" t="s" s="2">
         <v>85</v>
@@ -25925,7 +25925,7 @@
         <v>85</v>
       </c>
       <c r="X176" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y176" t="s" s="2">
         <v>486</v>
@@ -25937,7 +25937,7 @@
         <v>85</v>
       </c>
       <c r="AB176" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AC176" s="2"/>
       <c r="AD176" t="s" s="2">
@@ -26056,7 +26056,7 @@
         <v>85</v>
       </c>
       <c r="X177" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y177" t="s" s="2">
         <v>486</v>
@@ -26150,7 +26150,7 @@
         <v>85</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L178" t="s" s="2">
         <v>154</v>
@@ -26258,7 +26258,7 @@
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E179" s="2"/>
       <c r="F179" t="s" s="2">
@@ -26280,13 +26280,13 @@
         <v>140</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O179" s="2"/>
       <c r="P179" t="s" s="2">
@@ -26406,19 +26406,19 @@
         <v>96</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O180" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>85</v>
@@ -26465,7 +26465,7 @@
         <v>85</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>83</v>
@@ -26486,7 +26486,7 @@
         <v>85</v>
       </c>
       <c r="AM180" t="s" s="2">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="AN180" t="s" s="2">
         <v>85</v>
@@ -26495,10 +26495,10 @@
         <v>85</v>
       </c>
       <c r="AP180" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AQ180" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AR180" t="s" s="2">
         <v>85</v>
@@ -26535,19 +26535,19 @@
         <v>96</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O181" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>85</v>
@@ -26596,7 +26596,7 @@
         <v>85</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>83</v>
@@ -26626,10 +26626,10 @@
         <v>85</v>
       </c>
       <c r="AP181" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AQ181" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AR181" t="s" s="2">
         <v>85</v>
@@ -26703,7 +26703,7 @@
         <v>85</v>
       </c>
       <c r="X182" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y182" t="s" s="2">
         <v>581</v>
@@ -26834,7 +26834,7 @@
         <v>85</v>
       </c>
       <c r="X183" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y183" t="s" s="2">
         <v>592</v>
@@ -27192,7 +27192,7 @@
         <v>85</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L186" t="s" s="2">
         <v>154</v>
@@ -27300,7 +27300,7 @@
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E187" s="2"/>
       <c r="F187" t="s" s="2">
@@ -27322,13 +27322,13 @@
         <v>140</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O187" s="2"/>
       <c r="P187" t="s" s="2">
@@ -27457,10 +27457,10 @@
         <v>657</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O188" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>85</v>
@@ -27616,13 +27616,13 @@
         <v>85</v>
       </c>
       <c r="X189" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y189" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Z189" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AA189" t="s" s="2">
         <v>85</v>
@@ -27670,13 +27670,13 @@
         <v>728</v>
       </c>
       <c r="AP189" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AQ189" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AR189" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AS189" t="s" s="2">
         <v>85</v>
@@ -27747,7 +27747,7 @@
         <v>85</v>
       </c>
       <c r="X190" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y190" t="s" s="2">
         <v>486</v>
@@ -27759,7 +27759,7 @@
         <v>85</v>
       </c>
       <c r="AB190" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AC190" s="2"/>
       <c r="AD190" t="s" s="2">
@@ -27878,7 +27878,7 @@
         <v>85</v>
       </c>
       <c r="X191" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y191" t="s" s="2">
         <v>486</v>
@@ -27972,7 +27972,7 @@
         <v>85</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L192" t="s" s="2">
         <v>154</v>
@@ -28080,7 +28080,7 @@
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E193" s="2"/>
       <c r="F193" t="s" s="2">
@@ -28102,13 +28102,13 @@
         <v>140</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
@@ -28228,19 +28228,19 @@
         <v>96</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O194" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P194" t="s" s="2">
         <v>85</v>
@@ -28287,7 +28287,7 @@
         <v>85</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>83</v>
@@ -28308,7 +28308,7 @@
         <v>85</v>
       </c>
       <c r="AM194" t="s" s="2">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="AN194" t="s" s="2">
         <v>85</v>
@@ -28317,10 +28317,10 @@
         <v>85</v>
       </c>
       <c r="AP194" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AQ194" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AR194" t="s" s="2">
         <v>85</v>
@@ -28357,19 +28357,19 @@
         <v>96</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N195" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O195" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P195" t="s" s="2">
         <v>85</v>
@@ -28418,7 +28418,7 @@
         <v>85</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>83</v>
@@ -28448,10 +28448,10 @@
         <v>85</v>
       </c>
       <c r="AP195" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AQ195" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AR195" t="s" s="2">
         <v>85</v>
@@ -28525,7 +28525,7 @@
         <v>85</v>
       </c>
       <c r="X196" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y196" t="s" s="2">
         <v>581</v>
@@ -28656,7 +28656,7 @@
         <v>85</v>
       </c>
       <c r="X197" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y197" t="s" s="2">
         <v>592</v>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -931,7 +931,7 @@
     <t>656: fixed value = #entered-in-error when GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (120.5-4) case not null</t>
   </si>
   <si>
-    <t>Observation.ObservationExtension.Removed</t>
+    <t>Observation.Extension[ObservationExtension].Removed</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -1284,7 +1284,7 @@
     <t>Vital.VitalSign.VitalTypeIEN</t>
   </si>
   <si>
-    <t>Observation.ObservationCode,Observation.ObservationExtension.BMI</t>
+    <t>Observation.ObservationCode,Observation.Extension[ObservationExtension].BMI</t>
   </si>
   <si>
     <t>Observation.code.text</t>
@@ -1444,7 +1444,7 @@
     <t>Vital.VitalSign.VitalSignTakenDateTime,Vital.VitalSignQualifier.VitalSignTakenDateTime</t>
   </si>
   <si>
-    <t>Observation.Observation.Description,Observation.ObservationMethod.Description</t>
+    <t>Observation.ObservationCode[Observation].Description,Observation.ObservationMethods[ObservationMethod].Description</t>
   </si>
   <si>
     <t>Observation.issued</t>
@@ -1500,7 +1500,7 @@
     <t>Vital.VitalSign.LocationIEN</t>
   </si>
   <si>
-    <t>Observation.EnteredAt,Observation.ObservationExtension.Location</t>
+    <t>Observation.EnteredAt,Observation.Extension[ObservationExtension].Location</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1609,7 +1609,7 @@
     <t>Vital.VitalSign.Diastolic,Vital.VitalSign.Systolic,Vital.VitalSign.VitalResult,Vital.VitalSign.VitalResultNumeric</t>
   </si>
   <si>
-    <t>Observation.ObservationValue,Observation.ObservationExtension.BMI</t>
+    <t>Observation.ObservationValue,Observation.Extension[ObservationExtension].BMI</t>
   </si>
   <si>
     <t>SN.2  / CQ - N/A</t>
@@ -3192,7 +3192,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="150.6015625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="98.75" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="76.37109375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="114.0859375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="247.40625" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file GMRV VITAL MEASUREMENT (120.5) to us-core-blood-pressure</t>
+    <t>This StructureDefinition contains the maps for VistA file GMRV VITAL MEASUREMENT (120.5) to us-core-blood-pressure.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$198</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$199</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8210" uniqueCount="900">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8252" uniqueCount="902">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1795,7 +1795,7 @@
 </t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ConceptMap/VitalsUnits</t>
+    <t>http://va.gov/fhir/ConceptMap/VF-VitalsUnits</t>
   </si>
   <si>
     <t>Observation.value[x]:valueQuantity.code.value</t>
@@ -2311,6 +2311,12 @@
   </si>
   <si>
     <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x]:valueQuantity</t>
+  </si>
+  <si>
+    <t>2193: target not supported</t>
   </si>
   <si>
     <t>Observation.component.dataAbsentReason</t>
@@ -3152,7 +3158,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS198"/>
+  <dimension ref="A1:AS199"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="91.8671875" customWidth="true" bestFit="true"/>
@@ -15930,16 +15936,14 @@
         <v>85</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="AC99" s="2"/>
       <c r="AD99" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF99" t="s" s="2">
         <v>729</v>
@@ -15989,9 +15993,11 @@
         <v>735</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="C100" s="2"/>
+        <v>729</v>
+      </c>
+      <c r="C100" t="s" s="2">
+        <v>494</v>
+      </c>
       <c r="D100" t="s" s="2">
         <v>85</v>
       </c>
@@ -16009,22 +16015,22 @@
         <v>85</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>172</v>
+        <v>495</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>580</v>
+        <v>485</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>85</v>
@@ -16052,10 +16058,10 @@
         <v>228</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>581</v>
+        <v>486</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>582</v>
+        <v>487</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>85</v>
@@ -16073,7 +16079,7 @@
         <v>85</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>83</v>
@@ -16082,13 +16088,13 @@
         <v>95</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>85</v>
@@ -16100,41 +16106,41 @@
         <v>85</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>85</v>
+        <v>734</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>138</v>
+        <v>490</v>
       </c>
       <c r="AQ100" t="s" s="2">
-        <v>585</v>
+        <v>491</v>
       </c>
       <c r="AR100" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS100" t="s" s="2">
-        <v>85</v>
+        <v>492</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>587</v>
+        <v>85</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>85</v>
@@ -16146,16 +16152,16 @@
         <v>172</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>588</v>
+        <v>738</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>589</v>
+        <v>739</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>590</v>
+        <v>740</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>591</v>
+        <v>580</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>85</v>
@@ -16183,10 +16189,10 @@
         <v>228</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>592</v>
+        <v>581</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>593</v>
+        <v>582</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>85</v>
@@ -16204,22 +16210,22 @@
         <v>85</v>
       </c>
       <c r="AF101" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI101" t="s" s="2">
         <v>741</v>
-      </c>
-      <c r="AG101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH101" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI101" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>85</v>
+        <v>742</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>85</v>
@@ -16231,31 +16237,31 @@
         <v>85</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>594</v>
+        <v>85</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>595</v>
+        <v>138</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="AR101" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS101" t="s" s="2">
-        <v>597</v>
+        <v>85</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>85</v>
+        <v>587</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -16274,19 +16280,19 @@
         <v>85</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>743</v>
+        <v>588</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>744</v>
+        <v>589</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>647</v>
+        <v>590</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>648</v>
+        <v>591</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>85</v>
@@ -16311,13 +16317,13 @@
         <v>85</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>85</v>
+        <v>592</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>85</v>
+        <v>593</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>85</v>
@@ -16335,7 +16341,7 @@
         <v>85</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>83</v>
@@ -16362,64 +16368,62 @@
         <v>85</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>85</v>
+        <v>594</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>650</v>
+        <v>595</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>651</v>
+        <v>596</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS102" t="s" s="2">
-        <v>85</v>
+        <v>597</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="C103" t="s" s="2">
-        <v>746</v>
-      </c>
+        <v>744</v>
+      </c>
+      <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
         <v>85</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I103" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>644</v>
+        <v>86</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>713</v>
+        <v>746</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>714</v>
+        <v>647</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>715</v>
+        <v>648</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>85</v>
@@ -16468,7 +16472,7 @@
         <v>85</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>710</v>
+        <v>744</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>83</v>
@@ -16480,7 +16484,7 @@
         <v>85</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>717</v>
+        <v>107</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>85</v>
@@ -16498,10 +16502,10 @@
         <v>85</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>718</v>
+        <v>650</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>719</v>
+        <v>651</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>85</v>
@@ -16512,42 +16516,48 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="C104" t="s" s="2">
         <v>748</v>
       </c>
-      <c r="B104" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
         <v>85</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G104" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>210</v>
+        <v>644</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>154</v>
+        <v>749</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N104" s="2"/>
-      <c r="O104" s="2"/>
+        <v>713</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>715</v>
+      </c>
       <c r="P104" t="s" s="2">
         <v>85</v>
       </c>
@@ -16595,19 +16605,19 @@
         <v>85</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>156</v>
+        <v>710</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>85</v>
+        <v>717</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>85</v>
@@ -16625,10 +16635,10 @@
         <v>85</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>85</v>
+        <v>718</v>
       </c>
       <c r="AQ104" t="s" s="2">
-        <v>158</v>
+        <v>719</v>
       </c>
       <c r="AR104" t="s" s="2">
         <v>85</v>
@@ -16639,21 +16649,21 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>85</v>
@@ -16665,17 +16675,15 @@
         <v>85</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N105" s="2"/>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>85</v>
@@ -16724,19 +16732,19 @@
         <v>85</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>85</v>
@@ -16768,14 +16776,14 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>655</v>
+        <v>194</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -16788,26 +16796,24 @@
         <v>85</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K106" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>656</v>
+        <v>212</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>657</v>
+        <v>213</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="O106" t="s" s="2">
-        <v>198</v>
-      </c>
+      <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>85</v>
       </c>
@@ -16855,7 +16861,7 @@
         <v>85</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>658</v>
+        <v>162</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>83</v>
@@ -16888,7 +16894,7 @@
         <v>85</v>
       </c>
       <c r="AQ106" t="s" s="2">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="AR106" t="s" s="2">
         <v>85</v>
@@ -16899,45 +16905,45 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>85</v>
+        <v>655</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H107" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I107" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="I107" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="J107" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>752</v>
+        <v>656</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>725</v>
+        <v>657</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>726</v>
+        <v>197</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>727</v>
+        <v>198</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>85</v>
@@ -16947,7 +16953,7 @@
         <v>85</v>
       </c>
       <c r="S107" t="s" s="2">
-        <v>753</v>
+        <v>85</v>
       </c>
       <c r="T107" t="s" s="2">
         <v>85</v>
@@ -16962,13 +16968,13 @@
         <v>85</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>228</v>
+        <v>85</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>393</v>
+        <v>85</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>394</v>
+        <v>85</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>85</v>
@@ -16986,19 +16992,19 @@
         <v>85</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>723</v>
+        <v>658</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>85</v>
@@ -17013,16 +17019,16 @@
         <v>85</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>728</v>
+        <v>85</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>397</v>
+        <v>85</v>
       </c>
       <c r="AQ107" t="s" s="2">
-        <v>398</v>
+        <v>138</v>
       </c>
       <c r="AR107" t="s" s="2">
-        <v>399</v>
+        <v>85</v>
       </c>
       <c r="AS107" t="s" s="2">
         <v>85</v>
@@ -17030,10 +17036,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>755</v>
+        <v>723</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -17041,31 +17047,35 @@
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G108" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>154</v>
+        <v>754</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N108" s="2"/>
-      <c r="O108" s="2"/>
+        <v>725</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="O108" t="s" s="2">
+        <v>727</v>
+      </c>
       <c r="P108" t="s" s="2">
         <v>85</v>
       </c>
@@ -17074,7 +17084,7 @@
         <v>85</v>
       </c>
       <c r="S108" t="s" s="2">
-        <v>85</v>
+        <v>755</v>
       </c>
       <c r="T108" t="s" s="2">
         <v>85</v>
@@ -17089,13 +17099,13 @@
         <v>85</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>85</v>
+        <v>393</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>85</v>
+        <v>394</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>85</v>
@@ -17113,10 +17123,10 @@
         <v>85</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>156</v>
+        <v>723</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>95</v>
@@ -17125,7 +17135,7 @@
         <v>85</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>85</v>
@@ -17140,16 +17150,16 @@
         <v>85</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>85</v>
+        <v>728</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>85</v>
+        <v>397</v>
       </c>
       <c r="AQ108" t="s" s="2">
-        <v>158</v>
+        <v>398</v>
       </c>
       <c r="AR108" t="s" s="2">
-        <v>85</v>
+        <v>399</v>
       </c>
       <c r="AS108" t="s" s="2">
         <v>85</v>
@@ -17164,14 +17174,14 @@
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>85</v>
@@ -17183,17 +17193,15 @@
         <v>85</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>85</v>
@@ -17230,31 +17238,31 @@
         <v>85</v>
       </c>
       <c r="AB109" t="s" s="2">
-        <v>143</v>
+        <v>85</v>
       </c>
       <c r="AC109" t="s" s="2">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="AD109" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE109" t="s" s="2">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>85</v>
@@ -17293,7 +17301,7 @@
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>85</v>
+        <v>194</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -17309,23 +17317,21 @@
         <v>85</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>320</v>
+        <v>140</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>321</v>
+        <v>212</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>322</v>
+        <v>213</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>85</v>
       </c>
@@ -17361,19 +17367,19 @@
         <v>85</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>85</v>
+        <v>143</v>
       </c>
       <c r="AC110" t="s" s="2">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="AD110" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>325</v>
+        <v>162</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>83</v>
@@ -17385,7 +17391,7 @@
         <v>85</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>85</v>
@@ -17403,10 +17409,10 @@
         <v>85</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>326</v>
+        <v>85</v>
       </c>
       <c r="AQ110" t="s" s="2">
-        <v>327</v>
+        <v>158</v>
       </c>
       <c r="AR110" t="s" s="2">
         <v>85</v>
@@ -17431,7 +17437,7 @@
         <v>83</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>85</v>
@@ -17440,19 +17446,23 @@
         <v>85</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>210</v>
+        <v>320</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>154</v>
+        <v>321</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N111" s="2"/>
-      <c r="O111" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>324</v>
+      </c>
       <c r="P111" t="s" s="2">
         <v>85</v>
       </c>
@@ -17500,19 +17510,19 @@
         <v>85</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>156</v>
+        <v>325</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>85</v>
@@ -17530,10 +17540,10 @@
         <v>85</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>85</v>
+        <v>326</v>
       </c>
       <c r="AQ111" t="s" s="2">
-        <v>158</v>
+        <v>327</v>
       </c>
       <c r="AR111" t="s" s="2">
         <v>85</v>
@@ -17551,14 +17561,14 @@
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>85</v>
@@ -17570,17 +17580,15 @@
         <v>85</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N112" s="2"/>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>85</v>
@@ -17617,31 +17625,31 @@
         <v>85</v>
       </c>
       <c r="AB112" t="s" s="2">
-        <v>143</v>
+        <v>85</v>
       </c>
       <c r="AC112" t="s" s="2">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="AD112" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE112" t="s" s="2">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>85</v>
@@ -17680,39 +17688,37 @@
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>85</v>
+        <v>194</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>334</v>
+        <v>212</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>335</v>
+        <v>213</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>337</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>85</v>
       </c>
@@ -17748,34 +17754,34 @@
         <v>85</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>85</v>
+        <v>143</v>
       </c>
       <c r="AC113" t="s" s="2">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="AD113" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>339</v>
+        <v>162</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>766</v>
+        <v>146</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>767</v>
+        <v>85</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>85</v>
@@ -17790,10 +17796,10 @@
         <v>85</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>340</v>
+        <v>85</v>
       </c>
       <c r="AQ113" t="s" s="2">
-        <v>341</v>
+        <v>158</v>
       </c>
       <c r="AR113" t="s" s="2">
         <v>85</v>
@@ -17804,10 +17810,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17821,7 +17827,7 @@
         <v>95</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>85</v>
@@ -17830,18 +17836,20 @@
         <v>96</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>210</v>
+        <v>109</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="O114" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="O114" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="P114" t="s" s="2">
         <v>85</v>
       </c>
@@ -17889,7 +17897,7 @@
         <v>85</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>83</v>
@@ -17901,10 +17909,10 @@
         <v>85</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>107</v>
+        <v>768</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>85</v>
+        <v>769</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>85</v>
@@ -17919,10 +17927,10 @@
         <v>85</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="AQ114" t="s" s="2">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="AR114" t="s" s="2">
         <v>85</v>
@@ -17950,7 +17958,7 @@
         <v>95</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>85</v>
@@ -17959,18 +17967,18 @@
         <v>96</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>115</v>
+        <v>210</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N115" s="2"/>
-      <c r="O115" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>85</v>
       </c>
@@ -18018,7 +18026,7 @@
         <v>85</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>83</v>
@@ -18030,10 +18038,10 @@
         <v>85</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>772</v>
+        <v>107</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>773</v>
+        <v>85</v>
       </c>
       <c r="AL115" t="s" s="2">
         <v>85</v>
@@ -18048,10 +18056,10 @@
         <v>85</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="AQ115" t="s" s="2">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="AR115" t="s" s="2">
         <v>85</v>
@@ -18062,10 +18070,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -18079,7 +18087,7 @@
         <v>95</v>
       </c>
       <c r="H116" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I116" t="s" s="2">
         <v>85</v>
@@ -18088,17 +18096,17 @@
         <v>96</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>210</v>
+        <v>115</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" t="s" s="2">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>85</v>
@@ -18147,7 +18155,7 @@
         <v>85</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>83</v>
@@ -18159,10 +18167,10 @@
         <v>85</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>107</v>
+        <v>774</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>85</v>
+        <v>775</v>
       </c>
       <c r="AL116" t="s" s="2">
         <v>85</v>
@@ -18177,10 +18185,10 @@
         <v>85</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="AQ116" t="s" s="2">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="AR116" t="s" s="2">
         <v>85</v>
@@ -18217,19 +18225,17 @@
         <v>96</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>369</v>
+        <v>210</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>372</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>85</v>
@@ -18278,7 +18284,7 @@
         <v>85</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>83</v>
@@ -18308,10 +18314,10 @@
         <v>85</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="AQ117" t="s" s="2">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="AR117" t="s" s="2">
         <v>85</v>
@@ -18348,19 +18354,19 @@
         <v>96</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>210</v>
+        <v>369</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>85</v>
@@ -18409,7 +18415,7 @@
         <v>85</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>83</v>
@@ -18439,10 +18445,10 @@
         <v>85</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="AQ118" t="s" s="2">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="AR118" t="s" s="2">
         <v>85</v>
@@ -18456,7 +18462,7 @@
         <v>780</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>729</v>
+        <v>781</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -18470,7 +18476,7 @@
         <v>95</v>
       </c>
       <c r="H119" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I119" t="s" s="2">
         <v>85</v>
@@ -18479,19 +18485,19 @@
         <v>96</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>495</v>
+        <v>210</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>730</v>
+        <v>379</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>731</v>
+        <v>380</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>732</v>
+        <v>381</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>485</v>
+        <v>382</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>85</v>
@@ -18516,13 +18522,13 @@
         <v>85</v>
       </c>
       <c r="X119" t="s" s="2">
-        <v>228</v>
+        <v>85</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>486</v>
+        <v>85</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>487</v>
+        <v>85</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>85</v>
@@ -18540,7 +18546,7 @@
         <v>85</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>729</v>
+        <v>383</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>83</v>
@@ -18549,7 +18555,7 @@
         <v>95</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>733</v>
+        <v>85</v>
       </c>
       <c r="AJ119" t="s" s="2">
         <v>107</v>
@@ -18567,27 +18573,27 @@
         <v>85</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>734</v>
+        <v>85</v>
       </c>
       <c r="AP119" t="s" s="2">
-        <v>490</v>
+        <v>384</v>
       </c>
       <c r="AQ119" t="s" s="2">
-        <v>491</v>
+        <v>385</v>
       </c>
       <c r="AR119" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS119" t="s" s="2">
-        <v>492</v>
+        <v>85</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>782</v>
+        <v>729</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -18601,25 +18607,29 @@
         <v>95</v>
       </c>
       <c r="H120" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I120" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>210</v>
+        <v>495</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>154</v>
+        <v>730</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N120" s="2"/>
-      <c r="O120" s="2"/>
+        <v>731</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="O120" t="s" s="2">
+        <v>485</v>
+      </c>
       <c r="P120" t="s" s="2">
         <v>85</v>
       </c>
@@ -18643,13 +18653,13 @@
         <v>85</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>85</v>
+        <v>486</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>85</v>
+        <v>487</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>85</v>
@@ -18667,7 +18677,7 @@
         <v>85</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>156</v>
+        <v>729</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>83</v>
@@ -18676,10 +18686,10 @@
         <v>95</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>85</v>
+        <v>733</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK120" t="s" s="2">
         <v>85</v>
@@ -18694,19 +18704,19 @@
         <v>85</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>85</v>
+        <v>734</v>
       </c>
       <c r="AP120" t="s" s="2">
-        <v>85</v>
+        <v>490</v>
       </c>
       <c r="AQ120" t="s" s="2">
-        <v>158</v>
+        <v>491</v>
       </c>
       <c r="AR120" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS120" t="s" s="2">
-        <v>85</v>
+        <v>492</v>
       </c>
     </row>
     <row r="121" hidden="true">
@@ -18718,14 +18728,14 @@
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>85</v>
@@ -18737,17 +18747,15 @@
         <v>85</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N121" s="2"/>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>85</v>
@@ -18784,31 +18792,31 @@
         <v>85</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>143</v>
+        <v>85</v>
       </c>
       <c r="AC121" t="s" s="2">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="AD121" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE121" t="s" s="2">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>85</v>
@@ -18847,39 +18855,37 @@
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>85</v>
+        <v>194</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I122" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J122" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>502</v>
+        <v>140</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>503</v>
+        <v>212</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>504</v>
+        <v>213</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="O122" t="s" s="2">
-        <v>506</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
         <v>85</v>
       </c>
@@ -18915,40 +18921,40 @@
         <v>85</v>
       </c>
       <c r="AB122" t="s" s="2">
-        <v>85</v>
+        <v>143</v>
       </c>
       <c r="AC122" t="s" s="2">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="AD122" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE122" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>507</v>
+        <v>162</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>787</v>
+        <v>85</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>509</v>
+        <v>85</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>510</v>
+        <v>85</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>85</v>
@@ -18957,10 +18963,10 @@
         <v>85</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>511</v>
+        <v>85</v>
       </c>
       <c r="AQ122" t="s" s="2">
-        <v>512</v>
+        <v>158</v>
       </c>
       <c r="AR122" t="s" s="2">
         <v>85</v>
@@ -18971,10 +18977,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="B123" t="s" s="2">
         <v>788</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>789</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18982,39 +18988,39 @@
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G123" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H123" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I123" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J123" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>115</v>
+        <v>502</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="N123" s="2"/>
+        <v>504</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>505</v>
+      </c>
       <c r="O123" t="s" s="2">
-        <v>517</v>
+        <v>506</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="Q123" t="s" s="2">
-        <v>518</v>
-      </c>
+      <c r="Q123" s="2"/>
       <c r="R123" t="s" s="2">
         <v>85</v>
       </c>
@@ -19034,13 +19040,13 @@
         <v>85</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>175</v>
+        <v>85</v>
       </c>
       <c r="Y123" t="s" s="2">
-        <v>519</v>
+        <v>85</v>
       </c>
       <c r="Z123" t="s" s="2">
-        <v>520</v>
+        <v>85</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>85</v>
@@ -19058,7 +19064,7 @@
         <v>85</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>521</v>
+        <v>507</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>83</v>
@@ -19073,13 +19079,13 @@
         <v>107</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>85</v>
+        <v>789</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>85</v>
+        <v>509</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>85</v>
+        <v>510</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>85</v>
@@ -19088,10 +19094,10 @@
         <v>85</v>
       </c>
       <c r="AP123" t="s" s="2">
-        <v>522</v>
+        <v>511</v>
       </c>
       <c r="AQ123" t="s" s="2">
-        <v>523</v>
+        <v>512</v>
       </c>
       <c r="AR123" t="s" s="2">
         <v>85</v>
@@ -19113,37 +19119,39 @@
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G124" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H124" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I124" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="I124" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="J124" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>210</v>
+        <v>115</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>526</v>
+        <v>515</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>527</v>
+        <v>516</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="Q124" s="2"/>
+      <c r="Q124" t="s" s="2">
+        <v>518</v>
+      </c>
       <c r="R124" t="s" s="2">
         <v>85</v>
       </c>
@@ -19163,13 +19171,13 @@
         <v>85</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>85</v>
+        <v>175</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>85</v>
+        <v>519</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>85</v>
+        <v>520</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>85</v>
@@ -19187,7 +19195,7 @@
         <v>85</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>83</v>
@@ -19217,10 +19225,10 @@
         <v>85</v>
       </c>
       <c r="AP124" t="s" s="2">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="AQ124" t="s" s="2">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="AR124" t="s" s="2">
         <v>85</v>
@@ -19257,24 +19265,24 @@
         <v>96</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>109</v>
+        <v>210</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" t="s" s="2">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q125" s="2"/>
       <c r="R125" t="s" s="2">
-        <v>794</v>
+        <v>85</v>
       </c>
       <c r="S125" t="s" s="2">
         <v>85</v>
@@ -19316,7 +19324,7 @@
         <v>85</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>83</v>
@@ -19325,7 +19333,7 @@
         <v>95</v>
       </c>
       <c r="AI125" t="s" s="2">
-        <v>538</v>
+        <v>85</v>
       </c>
       <c r="AJ125" t="s" s="2">
         <v>107</v>
@@ -19349,7 +19357,7 @@
         <v>530</v>
       </c>
       <c r="AQ125" t="s" s="2">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="AR125" t="s" s="2">
         <v>85</v>
@@ -19360,10 +19368,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="B126" t="s" s="2">
         <v>795</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>796</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -19386,26 +19394,24 @@
         <v>96</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>544</v>
-      </c>
+        <v>535</v>
+      </c>
+      <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
-        <v>545</v>
+        <v>536</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q126" s="2"/>
       <c r="R126" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="S126" t="s" s="2">
         <v>85</v>
@@ -19447,7 +19453,7 @@
         <v>85</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>83</v>
@@ -19456,13 +19462,13 @@
         <v>95</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>85</v>
+        <v>538</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>798</v>
+        <v>107</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>799</v>
+        <v>85</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>85</v>
@@ -19480,7 +19486,7 @@
         <v>530</v>
       </c>
       <c r="AQ126" t="s" s="2">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="AR126" t="s" s="2">
         <v>85</v>
@@ -19491,10 +19497,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>735</v>
+        <v>798</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -19502,7 +19508,7 @@
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G127" t="s" s="2">
         <v>95</v>
@@ -19514,29 +19520,29 @@
         <v>85</v>
       </c>
       <c r="J127" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>172</v>
+        <v>115</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>736</v>
+        <v>542</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>737</v>
+        <v>543</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>738</v>
+        <v>544</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>580</v>
+        <v>545</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q127" s="2"/>
       <c r="R127" t="s" s="2">
-        <v>85</v>
+        <v>799</v>
       </c>
       <c r="S127" t="s" s="2">
         <v>85</v>
@@ -19554,13 +19560,13 @@
         <v>85</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>228</v>
+        <v>85</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>581</v>
+        <v>85</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>582</v>
+        <v>85</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>85</v>
@@ -19578,7 +19584,7 @@
         <v>85</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>735</v>
+        <v>546</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>83</v>
@@ -19587,13 +19593,13 @@
         <v>95</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>739</v>
+        <v>85</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>107</v>
+        <v>800</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>85</v>
+        <v>801</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>85</v>
@@ -19608,10 +19614,10 @@
         <v>85</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>138</v>
+        <v>530</v>
       </c>
       <c r="AQ127" t="s" s="2">
-        <v>585</v>
+        <v>548</v>
       </c>
       <c r="AR127" t="s" s="2">
         <v>85</v>
@@ -19622,24 +19628,24 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>587</v>
+        <v>85</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H128" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I128" t="s" s="2">
         <v>85</v>
@@ -19651,16 +19657,16 @@
         <v>172</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>588</v>
+        <v>738</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>589</v>
+        <v>739</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>590</v>
+        <v>740</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>591</v>
+        <v>580</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>85</v>
@@ -19688,10 +19694,10 @@
         <v>228</v>
       </c>
       <c r="Y128" t="s" s="2">
-        <v>592</v>
+        <v>581</v>
       </c>
       <c r="Z128" t="s" s="2">
-        <v>593</v>
+        <v>582</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>85</v>
@@ -19709,16 +19715,16 @@
         <v>85</v>
       </c>
       <c r="AF128" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI128" t="s" s="2">
         <v>741</v>
-      </c>
-      <c r="AG128" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI128" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="AJ128" t="s" s="2">
         <v>107</v>
@@ -19736,31 +19742,31 @@
         <v>85</v>
       </c>
       <c r="AO128" t="s" s="2">
-        <v>594</v>
+        <v>85</v>
       </c>
       <c r="AP128" t="s" s="2">
-        <v>595</v>
+        <v>138</v>
       </c>
       <c r="AQ128" t="s" s="2">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="AR128" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS128" t="s" s="2">
-        <v>597</v>
+        <v>85</v>
       </c>
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>85</v>
+        <v>587</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
@@ -19779,19 +19785,19 @@
         <v>85</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>743</v>
+        <v>588</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>744</v>
+        <v>589</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>647</v>
+        <v>590</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>648</v>
+        <v>591</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>85</v>
@@ -19816,13 +19822,13 @@
         <v>85</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>85</v>
+        <v>592</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>85</v>
+        <v>593</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>85</v>
@@ -19840,7 +19846,7 @@
         <v>85</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>83</v>
@@ -19867,64 +19873,62 @@
         <v>85</v>
       </c>
       <c r="AO129" t="s" s="2">
-        <v>85</v>
+        <v>594</v>
       </c>
       <c r="AP129" t="s" s="2">
-        <v>650</v>
+        <v>595</v>
       </c>
       <c r="AQ129" t="s" s="2">
-        <v>651</v>
+        <v>596</v>
       </c>
       <c r="AR129" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS129" t="s" s="2">
-        <v>85</v>
+        <v>597</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="C130" t="s" s="2">
-        <v>804</v>
-      </c>
+        <v>744</v>
+      </c>
+      <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
         <v>85</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H130" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I130" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J130" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>644</v>
+        <v>86</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>805</v>
+        <v>745</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>713</v>
+        <v>746</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>714</v>
+        <v>647</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>715</v>
+        <v>648</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>85</v>
@@ -19973,7 +19977,7 @@
         <v>85</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>710</v>
+        <v>744</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>83</v>
@@ -19985,7 +19989,7 @@
         <v>85</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>717</v>
+        <v>107</v>
       </c>
       <c r="AK130" t="s" s="2">
         <v>85</v>
@@ -20003,10 +20007,10 @@
         <v>85</v>
       </c>
       <c r="AP130" t="s" s="2">
-        <v>718</v>
+        <v>650</v>
       </c>
       <c r="AQ130" t="s" s="2">
-        <v>719</v>
+        <v>651</v>
       </c>
       <c r="AR130" t="s" s="2">
         <v>85</v>
@@ -20017,42 +20021,48 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
+        <v>805</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="C131" t="s" s="2">
         <v>806</v>
       </c>
-      <c r="B131" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
         <v>85</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G131" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H131" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I131" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>210</v>
+        <v>644</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>154</v>
+        <v>807</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N131" s="2"/>
-      <c r="O131" s="2"/>
+        <v>713</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="O131" t="s" s="2">
+        <v>715</v>
+      </c>
       <c r="P131" t="s" s="2">
         <v>85</v>
       </c>
@@ -20100,19 +20110,19 @@
         <v>85</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>156</v>
+        <v>710</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>85</v>
+        <v>717</v>
       </c>
       <c r="AK131" t="s" s="2">
         <v>85</v>
@@ -20130,10 +20140,10 @@
         <v>85</v>
       </c>
       <c r="AP131" t="s" s="2">
-        <v>85</v>
+        <v>718</v>
       </c>
       <c r="AQ131" t="s" s="2">
-        <v>158</v>
+        <v>719</v>
       </c>
       <c r="AR131" t="s" s="2">
         <v>85</v>
@@ -20144,21 +20154,21 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>85</v>
@@ -20170,17 +20180,15 @@
         <v>85</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N132" s="2"/>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>85</v>
@@ -20229,19 +20237,19 @@
         <v>85</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK132" t="s" s="2">
         <v>85</v>
@@ -20273,14 +20281,14 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>655</v>
+        <v>194</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -20293,26 +20301,24 @@
         <v>85</v>
       </c>
       <c r="I133" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J133" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K133" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>656</v>
+        <v>212</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>657</v>
+        <v>213</v>
       </c>
       <c r="N133" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="O133" t="s" s="2">
-        <v>198</v>
-      </c>
+      <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>85</v>
       </c>
@@ -20360,7 +20366,7 @@
         <v>85</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>658</v>
+        <v>162</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>83</v>
@@ -20393,7 +20399,7 @@
         <v>85</v>
       </c>
       <c r="AQ133" t="s" s="2">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="AR133" t="s" s="2">
         <v>85</v>
@@ -20404,45 +20410,45 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>85</v>
+        <v>655</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H134" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I134" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="I134" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="J134" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>810</v>
+        <v>656</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>725</v>
+        <v>657</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>726</v>
+        <v>197</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>727</v>
+        <v>198</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>85</v>
@@ -20452,7 +20458,7 @@
         <v>85</v>
       </c>
       <c r="S134" t="s" s="2">
-        <v>811</v>
+        <v>85</v>
       </c>
       <c r="T134" t="s" s="2">
         <v>85</v>
@@ -20467,13 +20473,13 @@
         <v>85</v>
       </c>
       <c r="X134" t="s" s="2">
-        <v>228</v>
+        <v>85</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>393</v>
+        <v>85</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>394</v>
+        <v>85</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>85</v>
@@ -20491,19 +20497,19 @@
         <v>85</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>723</v>
+        <v>658</v>
       </c>
       <c r="AG134" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK134" t="s" s="2">
         <v>85</v>
@@ -20518,16 +20524,16 @@
         <v>85</v>
       </c>
       <c r="AO134" t="s" s="2">
-        <v>728</v>
+        <v>85</v>
       </c>
       <c r="AP134" t="s" s="2">
-        <v>397</v>
+        <v>85</v>
       </c>
       <c r="AQ134" t="s" s="2">
-        <v>398</v>
+        <v>138</v>
       </c>
       <c r="AR134" t="s" s="2">
-        <v>399</v>
+        <v>85</v>
       </c>
       <c r="AS134" t="s" s="2">
         <v>85</v>
@@ -20535,10 +20541,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>755</v>
+        <v>723</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -20546,31 +20552,35 @@
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G135" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H135" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I135" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J135" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>154</v>
+        <v>812</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N135" s="2"/>
-      <c r="O135" s="2"/>
+        <v>725</v>
+      </c>
+      <c r="N135" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="O135" t="s" s="2">
+        <v>727</v>
+      </c>
       <c r="P135" t="s" s="2">
         <v>85</v>
       </c>
@@ -20579,7 +20589,7 @@
         <v>85</v>
       </c>
       <c r="S135" t="s" s="2">
-        <v>85</v>
+        <v>813</v>
       </c>
       <c r="T135" t="s" s="2">
         <v>85</v>
@@ -20594,13 +20604,13 @@
         <v>85</v>
       </c>
       <c r="X135" t="s" s="2">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="Y135" t="s" s="2">
-        <v>85</v>
+        <v>393</v>
       </c>
       <c r="Z135" t="s" s="2">
-        <v>85</v>
+        <v>394</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>85</v>
@@ -20618,10 +20628,10 @@
         <v>85</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>156</v>
+        <v>723</v>
       </c>
       <c r="AG135" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH135" t="s" s="2">
         <v>95</v>
@@ -20630,7 +20640,7 @@
         <v>85</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK135" t="s" s="2">
         <v>85</v>
@@ -20645,16 +20655,16 @@
         <v>85</v>
       </c>
       <c r="AO135" t="s" s="2">
-        <v>85</v>
+        <v>728</v>
       </c>
       <c r="AP135" t="s" s="2">
-        <v>85</v>
+        <v>397</v>
       </c>
       <c r="AQ135" t="s" s="2">
-        <v>158</v>
+        <v>398</v>
       </c>
       <c r="AR135" t="s" s="2">
-        <v>85</v>
+        <v>399</v>
       </c>
       <c r="AS135" t="s" s="2">
         <v>85</v>
@@ -20662,21 +20672,21 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>757</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H136" t="s" s="2">
         <v>85</v>
@@ -20688,17 +20698,15 @@
         <v>85</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N136" s="2"/>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
         <v>85</v>
@@ -20735,31 +20743,31 @@
         <v>85</v>
       </c>
       <c r="AB136" t="s" s="2">
-        <v>143</v>
+        <v>85</v>
       </c>
       <c r="AC136" t="s" s="2">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="AD136" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE136" t="s" s="2">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK136" t="s" s="2">
         <v>85</v>
@@ -20791,14 +20799,14 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>759</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
-        <v>85</v>
+        <v>194</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
@@ -20814,23 +20822,21 @@
         <v>85</v>
       </c>
       <c r="J137" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>320</v>
+        <v>140</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>321</v>
+        <v>212</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>322</v>
+        <v>213</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
         <v>85</v>
       </c>
@@ -20866,19 +20872,19 @@
         <v>85</v>
       </c>
       <c r="AB137" t="s" s="2">
-        <v>85</v>
+        <v>143</v>
       </c>
       <c r="AC137" t="s" s="2">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="AD137" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE137" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>325</v>
+        <v>162</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>83</v>
@@ -20890,7 +20896,7 @@
         <v>85</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK137" t="s" s="2">
         <v>85</v>
@@ -20908,10 +20914,10 @@
         <v>85</v>
       </c>
       <c r="AP137" t="s" s="2">
-        <v>326</v>
+        <v>85</v>
       </c>
       <c r="AQ137" t="s" s="2">
-        <v>327</v>
+        <v>158</v>
       </c>
       <c r="AR137" t="s" s="2">
         <v>85</v>
@@ -20922,7 +20928,7 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>761</v>
@@ -20936,7 +20942,7 @@
         <v>83</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>85</v>
@@ -20945,19 +20951,23 @@
         <v>85</v>
       </c>
       <c r="J138" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>210</v>
+        <v>320</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>154</v>
+        <v>321</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N138" s="2"/>
-      <c r="O138" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="N138" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="O138" t="s" s="2">
+        <v>324</v>
+      </c>
       <c r="P138" t="s" s="2">
         <v>85</v>
       </c>
@@ -21005,19 +21015,19 @@
         <v>85</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>156</v>
+        <v>325</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI138" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>85</v>
@@ -21035,10 +21045,10 @@
         <v>85</v>
       </c>
       <c r="AP138" t="s" s="2">
-        <v>85</v>
+        <v>326</v>
       </c>
       <c r="AQ138" t="s" s="2">
-        <v>158</v>
+        <v>327</v>
       </c>
       <c r="AR138" t="s" s="2">
         <v>85</v>
@@ -21049,21 +21059,21 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>763</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>85</v>
@@ -21075,17 +21085,15 @@
         <v>85</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N139" s="2"/>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
         <v>85</v>
@@ -21122,31 +21130,31 @@
         <v>85</v>
       </c>
       <c r="AB139" t="s" s="2">
-        <v>143</v>
+        <v>85</v>
       </c>
       <c r="AC139" t="s" s="2">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="AD139" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE139" t="s" s="2">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI139" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK139" t="s" s="2">
         <v>85</v>
@@ -21178,46 +21186,44 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>765</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>85</v>
+        <v>194</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H140" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I140" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J140" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>334</v>
+        <v>212</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>335</v>
+        <v>213</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="O140" t="s" s="2">
-        <v>337</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
         <v>85</v>
       </c>
@@ -21253,34 +21259,34 @@
         <v>85</v>
       </c>
       <c r="AB140" t="s" s="2">
-        <v>85</v>
+        <v>143</v>
       </c>
       <c r="AC140" t="s" s="2">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="AD140" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE140" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>339</v>
+        <v>162</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI140" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>818</v>
+        <v>146</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>819</v>
+        <v>85</v>
       </c>
       <c r="AL140" t="s" s="2">
         <v>85</v>
@@ -21295,10 +21301,10 @@
         <v>85</v>
       </c>
       <c r="AP140" t="s" s="2">
-        <v>340</v>
+        <v>85</v>
       </c>
       <c r="AQ140" t="s" s="2">
-        <v>341</v>
+        <v>158</v>
       </c>
       <c r="AR140" t="s" s="2">
         <v>85</v>
@@ -21309,10 +21315,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -21326,7 +21332,7 @@
         <v>95</v>
       </c>
       <c r="H141" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I141" t="s" s="2">
         <v>85</v>
@@ -21335,18 +21341,20 @@
         <v>96</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>210</v>
+        <v>109</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="O141" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="O141" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="P141" t="s" s="2">
         <v>85</v>
       </c>
@@ -21394,7 +21402,7 @@
         <v>85</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>83</v>
@@ -21406,10 +21414,10 @@
         <v>85</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>107</v>
+        <v>820</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>85</v>
+        <v>821</v>
       </c>
       <c r="AL141" t="s" s="2">
         <v>85</v>
@@ -21424,10 +21432,10 @@
         <v>85</v>
       </c>
       <c r="AP141" t="s" s="2">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="AQ141" t="s" s="2">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="AR141" t="s" s="2">
         <v>85</v>
@@ -21438,7 +21446,7 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B142" t="s" s="2">
         <v>771</v>
@@ -21455,7 +21463,7 @@
         <v>95</v>
       </c>
       <c r="H142" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I142" t="s" s="2">
         <v>85</v>
@@ -21464,18 +21472,18 @@
         <v>96</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>115</v>
+        <v>210</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N142" s="2"/>
-      <c r="O142" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="N142" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
         <v>85</v>
       </c>
@@ -21523,7 +21531,7 @@
         <v>85</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>83</v>
@@ -21535,10 +21543,10 @@
         <v>85</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>822</v>
+        <v>107</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>823</v>
+        <v>85</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>85</v>
@@ -21553,10 +21561,10 @@
         <v>85</v>
       </c>
       <c r="AP142" t="s" s="2">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="AQ142" t="s" s="2">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="AR142" t="s" s="2">
         <v>85</v>
@@ -21567,10 +21575,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -21584,7 +21592,7 @@
         <v>95</v>
       </c>
       <c r="H143" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I143" t="s" s="2">
         <v>85</v>
@@ -21593,17 +21601,17 @@
         <v>96</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>210</v>
+        <v>115</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" t="s" s="2">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>85</v>
@@ -21652,7 +21660,7 @@
         <v>85</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>83</v>
@@ -21664,10 +21672,10 @@
         <v>85</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>107</v>
+        <v>824</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>85</v>
+        <v>825</v>
       </c>
       <c r="AL143" t="s" s="2">
         <v>85</v>
@@ -21682,10 +21690,10 @@
         <v>85</v>
       </c>
       <c r="AP143" t="s" s="2">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="AQ143" t="s" s="2">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="AR143" t="s" s="2">
         <v>85</v>
@@ -21696,7 +21704,7 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>777</v>
@@ -21722,19 +21730,17 @@
         <v>96</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>369</v>
+        <v>210</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N144" t="s" s="2">
-        <v>372</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="N144" s="2"/>
       <c r="O144" t="s" s="2">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>85</v>
@@ -21783,7 +21789,7 @@
         <v>85</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>83</v>
@@ -21813,10 +21819,10 @@
         <v>85</v>
       </c>
       <c r="AP144" t="s" s="2">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="AQ144" t="s" s="2">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="AR144" t="s" s="2">
         <v>85</v>
@@ -21827,7 +21833,7 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>779</v>
@@ -21853,19 +21859,19 @@
         <v>96</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>210</v>
+        <v>369</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>85</v>
@@ -21914,7 +21920,7 @@
         <v>85</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>83</v>
@@ -21944,10 +21950,10 @@
         <v>85</v>
       </c>
       <c r="AP145" t="s" s="2">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="AQ145" t="s" s="2">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="AR145" t="s" s="2">
         <v>85</v>
@@ -21958,10 +21964,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>729</v>
+        <v>781</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -21975,7 +21981,7 @@
         <v>95</v>
       </c>
       <c r="H146" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I146" t="s" s="2">
         <v>85</v>
@@ -21984,19 +21990,19 @@
         <v>96</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>495</v>
+        <v>210</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>730</v>
+        <v>379</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>731</v>
+        <v>380</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>732</v>
+        <v>381</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>485</v>
+        <v>382</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>85</v>
@@ -22021,13 +22027,13 @@
         <v>85</v>
       </c>
       <c r="X146" t="s" s="2">
-        <v>228</v>
+        <v>85</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>486</v>
+        <v>85</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>487</v>
+        <v>85</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>85</v>
@@ -22045,7 +22051,7 @@
         <v>85</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>729</v>
+        <v>383</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>83</v>
@@ -22054,7 +22060,7 @@
         <v>95</v>
       </c>
       <c r="AI146" t="s" s="2">
-        <v>733</v>
+        <v>85</v>
       </c>
       <c r="AJ146" t="s" s="2">
         <v>107</v>
@@ -22072,27 +22078,27 @@
         <v>85</v>
       </c>
       <c r="AO146" t="s" s="2">
-        <v>734</v>
+        <v>85</v>
       </c>
       <c r="AP146" t="s" s="2">
-        <v>490</v>
+        <v>384</v>
       </c>
       <c r="AQ146" t="s" s="2">
-        <v>491</v>
+        <v>385</v>
       </c>
       <c r="AR146" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS146" t="s" s="2">
-        <v>492</v>
+        <v>85</v>
       </c>
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>782</v>
+        <v>729</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -22106,25 +22112,29 @@
         <v>95</v>
       </c>
       <c r="H147" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I147" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J147" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>210</v>
+        <v>495</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>154</v>
+        <v>730</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N147" s="2"/>
-      <c r="O147" s="2"/>
+        <v>731</v>
+      </c>
+      <c r="N147" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="O147" t="s" s="2">
+        <v>485</v>
+      </c>
       <c r="P147" t="s" s="2">
         <v>85</v>
       </c>
@@ -22148,13 +22158,13 @@
         <v>85</v>
       </c>
       <c r="X147" t="s" s="2">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="Y147" t="s" s="2">
-        <v>85</v>
+        <v>486</v>
       </c>
       <c r="Z147" t="s" s="2">
-        <v>85</v>
+        <v>487</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>85</v>
@@ -22172,7 +22182,7 @@
         <v>85</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>156</v>
+        <v>729</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>83</v>
@@ -22181,10 +22191,10 @@
         <v>95</v>
       </c>
       <c r="AI147" t="s" s="2">
-        <v>85</v>
+        <v>733</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK147" t="s" s="2">
         <v>85</v>
@@ -22199,38 +22209,38 @@
         <v>85</v>
       </c>
       <c r="AO147" t="s" s="2">
-        <v>85</v>
+        <v>734</v>
       </c>
       <c r="AP147" t="s" s="2">
-        <v>85</v>
+        <v>490</v>
       </c>
       <c r="AQ147" t="s" s="2">
-        <v>158</v>
+        <v>491</v>
       </c>
       <c r="AR147" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS147" t="s" s="2">
-        <v>85</v>
+        <v>492</v>
       </c>
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B148" t="s" s="2">
         <v>784</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G148" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H148" t="s" s="2">
         <v>85</v>
@@ -22242,17 +22252,15 @@
         <v>85</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N148" s="2"/>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
         <v>85</v>
@@ -22289,31 +22297,31 @@
         <v>85</v>
       </c>
       <c r="AB148" t="s" s="2">
-        <v>143</v>
+        <v>85</v>
       </c>
       <c r="AC148" t="s" s="2">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="AD148" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE148" t="s" s="2">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH148" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI148" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ148" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK148" t="s" s="2">
         <v>85</v>
@@ -22345,46 +22353,44 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B149" t="s" s="2">
         <v>786</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
-        <v>85</v>
+        <v>194</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G149" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H149" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I149" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J149" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>502</v>
+        <v>140</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>503</v>
+        <v>212</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>504</v>
+        <v>213</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="O149" t="s" s="2">
-        <v>506</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
         <v>85</v>
       </c>
@@ -22420,40 +22426,40 @@
         <v>85</v>
       </c>
       <c r="AB149" t="s" s="2">
-        <v>85</v>
+        <v>143</v>
       </c>
       <c r="AC149" t="s" s="2">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="AD149" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE149" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>507</v>
+        <v>162</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH149" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI149" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ149" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>831</v>
+        <v>85</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>509</v>
+        <v>85</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>510</v>
+        <v>85</v>
       </c>
       <c r="AN149" t="s" s="2">
         <v>85</v>
@@ -22462,10 +22468,10 @@
         <v>85</v>
       </c>
       <c r="AP149" t="s" s="2">
-        <v>511</v>
+        <v>85</v>
       </c>
       <c r="AQ149" t="s" s="2">
-        <v>512</v>
+        <v>158</v>
       </c>
       <c r="AR149" t="s" s="2">
         <v>85</v>
@@ -22479,7 +22485,7 @@
         <v>832</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -22487,39 +22493,39 @@
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G150" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H150" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I150" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J150" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>115</v>
+        <v>502</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="N150" s="2"/>
+        <v>504</v>
+      </c>
+      <c r="N150" t="s" s="2">
+        <v>505</v>
+      </c>
       <c r="O150" t="s" s="2">
-        <v>517</v>
+        <v>506</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="Q150" t="s" s="2">
-        <v>518</v>
-      </c>
+      <c r="Q150" s="2"/>
       <c r="R150" t="s" s="2">
         <v>85</v>
       </c>
@@ -22539,13 +22545,13 @@
         <v>85</v>
       </c>
       <c r="X150" t="s" s="2">
-        <v>175</v>
+        <v>85</v>
       </c>
       <c r="Y150" t="s" s="2">
-        <v>519</v>
+        <v>85</v>
       </c>
       <c r="Z150" t="s" s="2">
-        <v>520</v>
+        <v>85</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>85</v>
@@ -22563,7 +22569,7 @@
         <v>85</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>521</v>
+        <v>507</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>83</v>
@@ -22578,13 +22584,13 @@
         <v>107</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>85</v>
+        <v>833</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>85</v>
+        <v>509</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>85</v>
+        <v>510</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>85</v>
@@ -22593,10 +22599,10 @@
         <v>85</v>
       </c>
       <c r="AP150" t="s" s="2">
-        <v>522</v>
+        <v>511</v>
       </c>
       <c r="AQ150" t="s" s="2">
-        <v>523</v>
+        <v>512</v>
       </c>
       <c r="AR150" t="s" s="2">
         <v>85</v>
@@ -22607,7 +22613,7 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>791</v>
@@ -22618,37 +22624,39 @@
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G151" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H151" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I151" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="I151" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="J151" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>210</v>
+        <v>115</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>526</v>
+        <v>515</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>527</v>
+        <v>516</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" t="s" s="2">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="Q151" s="2"/>
+      <c r="Q151" t="s" s="2">
+        <v>518</v>
+      </c>
       <c r="R151" t="s" s="2">
         <v>85</v>
       </c>
@@ -22668,13 +22676,13 @@
         <v>85</v>
       </c>
       <c r="X151" t="s" s="2">
-        <v>85</v>
+        <v>175</v>
       </c>
       <c r="Y151" t="s" s="2">
-        <v>85</v>
+        <v>519</v>
       </c>
       <c r="Z151" t="s" s="2">
-        <v>85</v>
+        <v>520</v>
       </c>
       <c r="AA151" t="s" s="2">
         <v>85</v>
@@ -22692,7 +22700,7 @@
         <v>85</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>83</v>
@@ -22722,10 +22730,10 @@
         <v>85</v>
       </c>
       <c r="AP151" t="s" s="2">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="AQ151" t="s" s="2">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="AR151" t="s" s="2">
         <v>85</v>
@@ -22736,7 +22744,7 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B152" t="s" s="2">
         <v>793</v>
@@ -22762,24 +22770,24 @@
         <v>96</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>109</v>
+        <v>210</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" t="s" s="2">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q152" s="2"/>
       <c r="R152" t="s" s="2">
-        <v>794</v>
+        <v>85</v>
       </c>
       <c r="S152" t="s" s="2">
         <v>85</v>
@@ -22821,7 +22829,7 @@
         <v>85</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>83</v>
@@ -22830,7 +22838,7 @@
         <v>95</v>
       </c>
       <c r="AI152" t="s" s="2">
-        <v>538</v>
+        <v>85</v>
       </c>
       <c r="AJ152" t="s" s="2">
         <v>107</v>
@@ -22854,7 +22862,7 @@
         <v>530</v>
       </c>
       <c r="AQ152" t="s" s="2">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="AR152" t="s" s="2">
         <v>85</v>
@@ -22865,10 +22873,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -22891,26 +22899,24 @@
         <v>96</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>544</v>
-      </c>
+        <v>535</v>
+      </c>
+      <c r="N153" s="2"/>
       <c r="O153" t="s" s="2">
-        <v>545</v>
+        <v>536</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q153" s="2"/>
       <c r="R153" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="S153" t="s" s="2">
         <v>85</v>
@@ -22952,7 +22958,7 @@
         <v>85</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>83</v>
@@ -22961,13 +22967,13 @@
         <v>95</v>
       </c>
       <c r="AI153" t="s" s="2">
-        <v>85</v>
+        <v>538</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>836</v>
+        <v>107</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>837</v>
+        <v>85</v>
       </c>
       <c r="AL153" t="s" s="2">
         <v>85</v>
@@ -22985,7 +22991,7 @@
         <v>530</v>
       </c>
       <c r="AQ153" t="s" s="2">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="AR153" t="s" s="2">
         <v>85</v>
@@ -22996,10 +23002,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>735</v>
+        <v>798</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -23007,7 +23013,7 @@
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G154" t="s" s="2">
         <v>95</v>
@@ -23019,29 +23025,29 @@
         <v>85</v>
       </c>
       <c r="J154" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>172</v>
+        <v>115</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>736</v>
+        <v>542</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>737</v>
+        <v>543</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>738</v>
+        <v>544</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>580</v>
+        <v>545</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q154" s="2"/>
       <c r="R154" t="s" s="2">
-        <v>85</v>
+        <v>799</v>
       </c>
       <c r="S154" t="s" s="2">
         <v>85</v>
@@ -23059,13 +23065,13 @@
         <v>85</v>
       </c>
       <c r="X154" t="s" s="2">
-        <v>228</v>
+        <v>85</v>
       </c>
       <c r="Y154" t="s" s="2">
-        <v>581</v>
+        <v>85</v>
       </c>
       <c r="Z154" t="s" s="2">
-        <v>582</v>
+        <v>85</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>85</v>
@@ -23083,7 +23089,7 @@
         <v>85</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>735</v>
+        <v>546</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>83</v>
@@ -23092,13 +23098,13 @@
         <v>95</v>
       </c>
       <c r="AI154" t="s" s="2">
-        <v>739</v>
+        <v>85</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>107</v>
+        <v>838</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>85</v>
+        <v>839</v>
       </c>
       <c r="AL154" t="s" s="2">
         <v>85</v>
@@ -23113,10 +23119,10 @@
         <v>85</v>
       </c>
       <c r="AP154" t="s" s="2">
-        <v>138</v>
+        <v>530</v>
       </c>
       <c r="AQ154" t="s" s="2">
-        <v>585</v>
+        <v>548</v>
       </c>
       <c r="AR154" t="s" s="2">
         <v>85</v>
@@ -23127,24 +23133,24 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
-        <v>587</v>
+        <v>85</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G155" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H155" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I155" t="s" s="2">
         <v>85</v>
@@ -23156,16 +23162,16 @@
         <v>172</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>588</v>
+        <v>738</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>589</v>
+        <v>739</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>590</v>
+        <v>740</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>591</v>
+        <v>580</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>85</v>
@@ -23193,10 +23199,10 @@
         <v>228</v>
       </c>
       <c r="Y155" t="s" s="2">
-        <v>592</v>
+        <v>581</v>
       </c>
       <c r="Z155" t="s" s="2">
-        <v>593</v>
+        <v>582</v>
       </c>
       <c r="AA155" t="s" s="2">
         <v>85</v>
@@ -23214,16 +23220,16 @@
         <v>85</v>
       </c>
       <c r="AF155" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="AG155" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH155" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI155" t="s" s="2">
         <v>741</v>
-      </c>
-      <c r="AG155" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH155" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI155" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="AJ155" t="s" s="2">
         <v>107</v>
@@ -23241,31 +23247,31 @@
         <v>85</v>
       </c>
       <c r="AO155" t="s" s="2">
-        <v>594</v>
+        <v>85</v>
       </c>
       <c r="AP155" t="s" s="2">
-        <v>595</v>
+        <v>138</v>
       </c>
       <c r="AQ155" t="s" s="2">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="AR155" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS155" t="s" s="2">
-        <v>597</v>
+        <v>85</v>
       </c>
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>85</v>
+        <v>587</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
@@ -23284,19 +23290,19 @@
         <v>85</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>743</v>
+        <v>588</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>744</v>
+        <v>589</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>647</v>
+        <v>590</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>648</v>
+        <v>591</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>85</v>
@@ -23321,13 +23327,13 @@
         <v>85</v>
       </c>
       <c r="X156" t="s" s="2">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="Y156" t="s" s="2">
-        <v>85</v>
+        <v>592</v>
       </c>
       <c r="Z156" t="s" s="2">
-        <v>85</v>
+        <v>593</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>85</v>
@@ -23345,7 +23351,7 @@
         <v>85</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>83</v>
@@ -23372,31 +23378,29 @@
         <v>85</v>
       </c>
       <c r="AO156" t="s" s="2">
-        <v>85</v>
+        <v>594</v>
       </c>
       <c r="AP156" t="s" s="2">
-        <v>650</v>
+        <v>595</v>
       </c>
       <c r="AQ156" t="s" s="2">
-        <v>651</v>
+        <v>596</v>
       </c>
       <c r="AR156" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS156" t="s" s="2">
-        <v>85</v>
+        <v>597</v>
       </c>
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="C157" t="s" s="2">
-        <v>842</v>
-      </c>
+        <v>744</v>
+      </c>
+      <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
         <v>85</v>
       </c>
@@ -23405,31 +23409,31 @@
         <v>83</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H157" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I157" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J157" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>644</v>
+        <v>86</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>712</v>
+        <v>745</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>713</v>
+        <v>746</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>714</v>
+        <v>647</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>715</v>
+        <v>648</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>85</v>
@@ -23478,7 +23482,7 @@
         <v>85</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>710</v>
+        <v>744</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>83</v>
@@ -23490,7 +23494,7 @@
         <v>85</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>717</v>
+        <v>107</v>
       </c>
       <c r="AK157" t="s" s="2">
         <v>85</v>
@@ -23508,10 +23512,10 @@
         <v>85</v>
       </c>
       <c r="AP157" t="s" s="2">
-        <v>718</v>
+        <v>650</v>
       </c>
       <c r="AQ157" t="s" s="2">
-        <v>719</v>
+        <v>651</v>
       </c>
       <c r="AR157" t="s" s="2">
         <v>85</v>
@@ -23525,9 +23529,11 @@
         <v>843</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="C158" s="2"/>
+        <v>710</v>
+      </c>
+      <c r="C158" t="s" s="2">
+        <v>844</v>
+      </c>
       <c r="D158" t="s" s="2">
         <v>85</v>
       </c>
@@ -23539,25 +23545,29 @@
         <v>95</v>
       </c>
       <c r="H158" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I158" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J158" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>210</v>
+        <v>644</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>154</v>
+        <v>712</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N158" s="2"/>
-      <c r="O158" s="2"/>
+        <v>713</v>
+      </c>
+      <c r="N158" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="O158" t="s" s="2">
+        <v>715</v>
+      </c>
       <c r="P158" t="s" s="2">
         <v>85</v>
       </c>
@@ -23605,19 +23615,19 @@
         <v>85</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>156</v>
+        <v>710</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH158" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI158" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ158" t="s" s="2">
-        <v>85</v>
+        <v>717</v>
       </c>
       <c r="AK158" t="s" s="2">
         <v>85</v>
@@ -23635,10 +23645,10 @@
         <v>85</v>
       </c>
       <c r="AP158" t="s" s="2">
-        <v>85</v>
+        <v>718</v>
       </c>
       <c r="AQ158" t="s" s="2">
-        <v>158</v>
+        <v>719</v>
       </c>
       <c r="AR158" t="s" s="2">
         <v>85</v>
@@ -23649,21 +23659,21 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G159" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H159" t="s" s="2">
         <v>85</v>
@@ -23675,17 +23685,15 @@
         <v>85</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N159" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N159" s="2"/>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
         <v>85</v>
@@ -23734,19 +23742,19 @@
         <v>85</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH159" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI159" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ159" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK159" t="s" s="2">
         <v>85</v>
@@ -23778,14 +23786,14 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
-        <v>655</v>
+        <v>194</v>
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
@@ -23798,26 +23806,24 @@
         <v>85</v>
       </c>
       <c r="I160" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J160" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K160" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>656</v>
+        <v>212</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>657</v>
+        <v>213</v>
       </c>
       <c r="N160" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="O160" t="s" s="2">
-        <v>198</v>
-      </c>
+      <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
         <v>85</v>
       </c>
@@ -23865,7 +23871,7 @@
         <v>85</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>658</v>
+        <v>162</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>83</v>
@@ -23898,7 +23904,7 @@
         <v>85</v>
       </c>
       <c r="AQ160" t="s" s="2">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="AR160" t="s" s="2">
         <v>85</v>
@@ -23909,45 +23915,45 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
-        <v>85</v>
+        <v>655</v>
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G161" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H161" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I161" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="I161" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="J161" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>724</v>
+        <v>656</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>725</v>
+        <v>657</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>726</v>
+        <v>197</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>727</v>
+        <v>198</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>85</v>
@@ -23957,7 +23963,7 @@
         <v>85</v>
       </c>
       <c r="S161" t="s" s="2">
-        <v>847</v>
+        <v>85</v>
       </c>
       <c r="T161" t="s" s="2">
         <v>85</v>
@@ -23972,13 +23978,13 @@
         <v>85</v>
       </c>
       <c r="X161" t="s" s="2">
-        <v>228</v>
+        <v>85</v>
       </c>
       <c r="Y161" t="s" s="2">
-        <v>393</v>
+        <v>85</v>
       </c>
       <c r="Z161" t="s" s="2">
-        <v>394</v>
+        <v>85</v>
       </c>
       <c r="AA161" t="s" s="2">
         <v>85</v>
@@ -23996,22 +24002,22 @@
         <v>85</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>723</v>
+        <v>658</v>
       </c>
       <c r="AG161" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH161" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI161" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ161" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK161" t="s" s="2">
-        <v>848</v>
+        <v>85</v>
       </c>
       <c r="AL161" t="s" s="2">
         <v>85</v>
@@ -24023,16 +24029,16 @@
         <v>85</v>
       </c>
       <c r="AO161" t="s" s="2">
-        <v>728</v>
+        <v>85</v>
       </c>
       <c r="AP161" t="s" s="2">
-        <v>397</v>
+        <v>85</v>
       </c>
       <c r="AQ161" t="s" s="2">
-        <v>398</v>
+        <v>138</v>
       </c>
       <c r="AR161" t="s" s="2">
-        <v>399</v>
+        <v>85</v>
       </c>
       <c r="AS161" t="s" s="2">
         <v>85</v>
@@ -24040,10 +24046,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -24051,7 +24057,7 @@
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G162" t="s" s="2">
         <v>95</v>
@@ -24066,19 +24072,19 @@
         <v>96</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>481</v>
+        <v>172</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="O162" t="s" s="2">
-        <v>485</v>
+        <v>727</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>85</v>
@@ -24088,7 +24094,7 @@
         <v>85</v>
       </c>
       <c r="S162" t="s" s="2">
-        <v>85</v>
+        <v>849</v>
       </c>
       <c r="T162" t="s" s="2">
         <v>85</v>
@@ -24106,41 +24112,43 @@
         <v>228</v>
       </c>
       <c r="Y162" t="s" s="2">
-        <v>486</v>
+        <v>393</v>
       </c>
       <c r="Z162" t="s" s="2">
-        <v>487</v>
+        <v>394</v>
       </c>
       <c r="AA162" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB162" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AC162" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="AC162" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="AD162" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE162" t="s" s="2">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="AG162" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH162" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AI162" t="s" s="2">
-        <v>733</v>
+        <v>85</v>
       </c>
       <c r="AJ162" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>85</v>
+        <v>850</v>
       </c>
       <c r="AL162" t="s" s="2">
         <v>85</v>
@@ -24152,31 +24160,29 @@
         <v>85</v>
       </c>
       <c r="AO162" t="s" s="2">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="AP162" t="s" s="2">
-        <v>490</v>
+        <v>397</v>
       </c>
       <c r="AQ162" t="s" s="2">
-        <v>491</v>
+        <v>398</v>
       </c>
       <c r="AR162" t="s" s="2">
-        <v>85</v>
+        <v>399</v>
       </c>
       <c r="AS162" t="s" s="2">
-        <v>492</v>
+        <v>85</v>
       </c>
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B163" t="s" s="2">
         <v>729</v>
       </c>
-      <c r="C163" t="s" s="2">
-        <v>851</v>
-      </c>
+      <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
         <v>85</v>
       </c>
@@ -24197,7 +24203,7 @@
         <v>96</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>172</v>
+        <v>481</v>
       </c>
       <c r="L163" t="s" s="2">
         <v>730</v>
@@ -24246,16 +24252,14 @@
         <v>85</v>
       </c>
       <c r="AB163" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC163" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="AC163" s="2"/>
       <c r="AD163" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE163" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF163" t="s" s="2">
         <v>729</v>
@@ -24305,9 +24309,11 @@
         <v>852</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>782</v>
-      </c>
-      <c r="C164" s="2"/>
+        <v>729</v>
+      </c>
+      <c r="C164" t="s" s="2">
+        <v>853</v>
+      </c>
       <c r="D164" t="s" s="2">
         <v>85</v>
       </c>
@@ -24319,25 +24325,29 @@
         <v>95</v>
       </c>
       <c r="H164" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I164" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J164" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>154</v>
+        <v>730</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N164" s="2"/>
-      <c r="O164" s="2"/>
+        <v>731</v>
+      </c>
+      <c r="N164" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="O164" t="s" s="2">
+        <v>485</v>
+      </c>
       <c r="P164" t="s" s="2">
         <v>85</v>
       </c>
@@ -24361,13 +24371,13 @@
         <v>85</v>
       </c>
       <c r="X164" t="s" s="2">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="Y164" t="s" s="2">
-        <v>85</v>
+        <v>486</v>
       </c>
       <c r="Z164" t="s" s="2">
-        <v>85</v>
+        <v>487</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>85</v>
@@ -24385,7 +24395,7 @@
         <v>85</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>156</v>
+        <v>729</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>83</v>
@@ -24394,10 +24404,10 @@
         <v>95</v>
       </c>
       <c r="AI164" t="s" s="2">
-        <v>85</v>
+        <v>733</v>
       </c>
       <c r="AJ164" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK164" t="s" s="2">
         <v>85</v>
@@ -24412,38 +24422,38 @@
         <v>85</v>
       </c>
       <c r="AO164" t="s" s="2">
-        <v>85</v>
+        <v>734</v>
       </c>
       <c r="AP164" t="s" s="2">
-        <v>85</v>
+        <v>490</v>
       </c>
       <c r="AQ164" t="s" s="2">
-        <v>158</v>
+        <v>491</v>
       </c>
       <c r="AR164" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS164" t="s" s="2">
-        <v>85</v>
+        <v>492</v>
       </c>
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B165" t="s" s="2">
         <v>784</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="E165" s="2"/>
       <c r="F165" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G165" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H165" t="s" s="2">
         <v>85</v>
@@ -24455,17 +24465,15 @@
         <v>85</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N165" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N165" s="2"/>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
         <v>85</v>
@@ -24502,31 +24510,31 @@
         <v>85</v>
       </c>
       <c r="AB165" t="s" s="2">
-        <v>143</v>
+        <v>85</v>
       </c>
       <c r="AC165" t="s" s="2">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="AD165" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE165" t="s" s="2">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH165" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI165" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ165" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK165" t="s" s="2">
         <v>85</v>
@@ -24558,14 +24566,14 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>855</v>
+        <v>786</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
-        <v>85</v>
+        <v>194</v>
       </c>
       <c r="E166" s="2"/>
       <c r="F166" t="s" s="2">
@@ -24575,29 +24583,27 @@
         <v>84</v>
       </c>
       <c r="H166" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I166" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J166" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>320</v>
+        <v>140</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>321</v>
+        <v>212</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>322</v>
+        <v>213</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="O166" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
         <v>85</v>
       </c>
@@ -24621,29 +24627,31 @@
         <v>85</v>
       </c>
       <c r="X166" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="Y166" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="Y166" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="Z166" t="s" s="2">
-        <v>856</v>
+        <v>85</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB166" t="s" s="2">
-        <v>85</v>
+        <v>143</v>
       </c>
       <c r="AC166" t="s" s="2">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="AD166" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE166" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>325</v>
+        <v>162</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>83</v>
@@ -24655,16 +24663,16 @@
         <v>85</v>
       </c>
       <c r="AJ166" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>857</v>
+        <v>85</v>
       </c>
       <c r="AL166" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>180</v>
+        <v>85</v>
       </c>
       <c r="AN166" t="s" s="2">
         <v>85</v>
@@ -24673,10 +24681,10 @@
         <v>85</v>
       </c>
       <c r="AP166" t="s" s="2">
-        <v>326</v>
+        <v>85</v>
       </c>
       <c r="AQ166" t="s" s="2">
-        <v>327</v>
+        <v>158</v>
       </c>
       <c r="AR166" t="s" s="2">
         <v>85</v>
@@ -24687,10 +24695,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -24701,10 +24709,10 @@
         <v>83</v>
       </c>
       <c r="G167" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H167" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I167" t="s" s="2">
         <v>85</v>
@@ -24713,19 +24721,19 @@
         <v>96</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>210</v>
+        <v>320</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>379</v>
+        <v>321</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>380</v>
+        <v>322</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>381</v>
+        <v>323</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>382</v>
+        <v>324</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>85</v>
@@ -24750,13 +24758,11 @@
         <v>85</v>
       </c>
       <c r="X167" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y167" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="Y167" s="2"/>
       <c r="Z167" t="s" s="2">
-        <v>85</v>
+        <v>858</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>85</v>
@@ -24774,13 +24780,13 @@
         <v>85</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>383</v>
+        <v>325</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH167" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI167" t="s" s="2">
         <v>85</v>
@@ -24789,13 +24795,13 @@
         <v>107</v>
       </c>
       <c r="AK167" t="s" s="2">
-        <v>85</v>
+        <v>859</v>
       </c>
       <c r="AL167" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="AN167" t="s" s="2">
         <v>85</v>
@@ -24804,10 +24810,10 @@
         <v>85</v>
       </c>
       <c r="AP167" t="s" s="2">
-        <v>384</v>
+        <v>326</v>
       </c>
       <c r="AQ167" t="s" s="2">
-        <v>385</v>
+        <v>327</v>
       </c>
       <c r="AR167" t="s" s="2">
         <v>85</v>
@@ -24821,7 +24827,7 @@
         <v>860</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>735</v>
+        <v>861</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -24835,28 +24841,28 @@
         <v>95</v>
       </c>
       <c r="H168" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I168" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J168" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="I168" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J168" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="K168" t="s" s="2">
-        <v>172</v>
+        <v>210</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>736</v>
+        <v>379</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>737</v>
+        <v>380</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>738</v>
+        <v>381</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>580</v>
+        <v>382</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>85</v>
@@ -24881,13 +24887,13 @@
         <v>85</v>
       </c>
       <c r="X168" t="s" s="2">
-        <v>228</v>
+        <v>85</v>
       </c>
       <c r="Y168" t="s" s="2">
-        <v>581</v>
+        <v>85</v>
       </c>
       <c r="Z168" t="s" s="2">
-        <v>582</v>
+        <v>85</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>85</v>
@@ -24905,7 +24911,7 @@
         <v>85</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>735</v>
+        <v>383</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>83</v>
@@ -24914,7 +24920,7 @@
         <v>95</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>739</v>
+        <v>85</v>
       </c>
       <c r="AJ168" t="s" s="2">
         <v>107</v>
@@ -24935,10 +24941,10 @@
         <v>85</v>
       </c>
       <c r="AP168" t="s" s="2">
-        <v>138</v>
+        <v>384</v>
       </c>
       <c r="AQ168" t="s" s="2">
-        <v>585</v>
+        <v>385</v>
       </c>
       <c r="AR168" t="s" s="2">
         <v>85</v>
@@ -24949,24 +24955,24 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
-        <v>587</v>
+        <v>85</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G169" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H169" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I169" t="s" s="2">
         <v>85</v>
@@ -24978,16 +24984,16 @@
         <v>172</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>588</v>
+        <v>738</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>589</v>
+        <v>739</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>590</v>
+        <v>740</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>591</v>
+        <v>580</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>85</v>
@@ -25015,10 +25021,10 @@
         <v>228</v>
       </c>
       <c r="Y169" t="s" s="2">
-        <v>592</v>
+        <v>581</v>
       </c>
       <c r="Z169" t="s" s="2">
-        <v>593</v>
+        <v>582</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>85</v>
@@ -25036,16 +25042,16 @@
         <v>85</v>
       </c>
       <c r="AF169" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="AG169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH169" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI169" t="s" s="2">
         <v>741</v>
-      </c>
-      <c r="AG169" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH169" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI169" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="AJ169" t="s" s="2">
         <v>107</v>
@@ -25063,31 +25069,31 @@
         <v>85</v>
       </c>
       <c r="AO169" t="s" s="2">
-        <v>594</v>
+        <v>85</v>
       </c>
       <c r="AP169" t="s" s="2">
-        <v>595</v>
+        <v>138</v>
       </c>
       <c r="AQ169" t="s" s="2">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="AR169" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS169" t="s" s="2">
-        <v>597</v>
+        <v>85</v>
       </c>
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
-        <v>85</v>
+        <v>587</v>
       </c>
       <c r="E170" s="2"/>
       <c r="F170" t="s" s="2">
@@ -25106,19 +25112,19 @@
         <v>85</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>743</v>
+        <v>588</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>744</v>
+        <v>589</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>647</v>
+        <v>590</v>
       </c>
       <c r="O170" t="s" s="2">
-        <v>648</v>
+        <v>591</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>85</v>
@@ -25143,13 +25149,13 @@
         <v>85</v>
       </c>
       <c r="X170" t="s" s="2">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="Y170" t="s" s="2">
-        <v>85</v>
+        <v>592</v>
       </c>
       <c r="Z170" t="s" s="2">
-        <v>85</v>
+        <v>593</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>85</v>
@@ -25167,7 +25173,7 @@
         <v>85</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>83</v>
@@ -25194,31 +25200,29 @@
         <v>85</v>
       </c>
       <c r="AO170" t="s" s="2">
-        <v>85</v>
+        <v>594</v>
       </c>
       <c r="AP170" t="s" s="2">
-        <v>650</v>
+        <v>595</v>
       </c>
       <c r="AQ170" t="s" s="2">
-        <v>651</v>
+        <v>596</v>
       </c>
       <c r="AR170" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS170" t="s" s="2">
-        <v>85</v>
+        <v>597</v>
       </c>
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="C171" t="s" s="2">
-        <v>864</v>
-      </c>
+        <v>744</v>
+      </c>
+      <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
         <v>85</v>
       </c>
@@ -25227,31 +25231,31 @@
         <v>83</v>
       </c>
       <c r="G171" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H171" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I171" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J171" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>644</v>
+        <v>86</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>712</v>
+        <v>745</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>713</v>
+        <v>746</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>714</v>
+        <v>647</v>
       </c>
       <c r="O171" t="s" s="2">
-        <v>715</v>
+        <v>648</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>85</v>
@@ -25300,7 +25304,7 @@
         <v>85</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>710</v>
+        <v>744</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>83</v>
@@ -25312,7 +25316,7 @@
         <v>85</v>
       </c>
       <c r="AJ171" t="s" s="2">
-        <v>717</v>
+        <v>107</v>
       </c>
       <c r="AK171" t="s" s="2">
         <v>85</v>
@@ -25330,10 +25334,10 @@
         <v>85</v>
       </c>
       <c r="AP171" t="s" s="2">
-        <v>718</v>
+        <v>650</v>
       </c>
       <c r="AQ171" t="s" s="2">
-        <v>719</v>
+        <v>651</v>
       </c>
       <c r="AR171" t="s" s="2">
         <v>85</v>
@@ -25347,9 +25351,11 @@
         <v>865</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="C172" s="2"/>
+        <v>710</v>
+      </c>
+      <c r="C172" t="s" s="2">
+        <v>866</v>
+      </c>
       <c r="D172" t="s" s="2">
         <v>85</v>
       </c>
@@ -25361,25 +25367,29 @@
         <v>95</v>
       </c>
       <c r="H172" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I172" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J172" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>210</v>
+        <v>644</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>154</v>
+        <v>712</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N172" s="2"/>
-      <c r="O172" s="2"/>
+        <v>713</v>
+      </c>
+      <c r="N172" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="O172" t="s" s="2">
+        <v>715</v>
+      </c>
       <c r="P172" t="s" s="2">
         <v>85</v>
       </c>
@@ -25427,19 +25437,19 @@
         <v>85</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>156</v>
+        <v>710</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH172" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI172" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ172" t="s" s="2">
-        <v>85</v>
+        <v>717</v>
       </c>
       <c r="AK172" t="s" s="2">
         <v>85</v>
@@ -25457,10 +25467,10 @@
         <v>85</v>
       </c>
       <c r="AP172" t="s" s="2">
-        <v>85</v>
+        <v>718</v>
       </c>
       <c r="AQ172" t="s" s="2">
-        <v>158</v>
+        <v>719</v>
       </c>
       <c r="AR172" t="s" s="2">
         <v>85</v>
@@ -25471,21 +25481,21 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="E173" s="2"/>
       <c r="F173" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G173" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H173" t="s" s="2">
         <v>85</v>
@@ -25497,17 +25507,15 @@
         <v>85</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N173" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N173" s="2"/>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
         <v>85</v>
@@ -25556,19 +25564,19 @@
         <v>85</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH173" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI173" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ173" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK173" t="s" s="2">
         <v>85</v>
@@ -25600,14 +25608,14 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
-        <v>655</v>
+        <v>194</v>
       </c>
       <c r="E174" s="2"/>
       <c r="F174" t="s" s="2">
@@ -25620,26 +25628,24 @@
         <v>85</v>
       </c>
       <c r="I174" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J174" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K174" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>656</v>
+        <v>212</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>657</v>
+        <v>213</v>
       </c>
       <c r="N174" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="O174" t="s" s="2">
-        <v>198</v>
-      </c>
+      <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
         <v>85</v>
       </c>
@@ -25687,7 +25693,7 @@
         <v>85</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>658</v>
+        <v>162</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>83</v>
@@ -25720,7 +25726,7 @@
         <v>85</v>
       </c>
       <c r="AQ174" t="s" s="2">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="AR174" t="s" s="2">
         <v>85</v>
@@ -25731,45 +25737,45 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
-        <v>85</v>
+        <v>655</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G175" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H175" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I175" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="I175" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="J175" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>724</v>
+        <v>656</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>725</v>
+        <v>657</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>726</v>
+        <v>197</v>
       </c>
       <c r="O175" t="s" s="2">
-        <v>727</v>
+        <v>198</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>85</v>
@@ -25779,7 +25785,7 @@
         <v>85</v>
       </c>
       <c r="S175" t="s" s="2">
-        <v>869</v>
+        <v>85</v>
       </c>
       <c r="T175" t="s" s="2">
         <v>85</v>
@@ -25794,13 +25800,13 @@
         <v>85</v>
       </c>
       <c r="X175" t="s" s="2">
-        <v>228</v>
+        <v>85</v>
       </c>
       <c r="Y175" t="s" s="2">
-        <v>393</v>
+        <v>85</v>
       </c>
       <c r="Z175" t="s" s="2">
-        <v>394</v>
+        <v>85</v>
       </c>
       <c r="AA175" t="s" s="2">
         <v>85</v>
@@ -25818,22 +25824,22 @@
         <v>85</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>723</v>
+        <v>658</v>
       </c>
       <c r="AG175" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH175" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI175" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ175" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK175" t="s" s="2">
-        <v>870</v>
+        <v>85</v>
       </c>
       <c r="AL175" t="s" s="2">
         <v>85</v>
@@ -25845,16 +25851,16 @@
         <v>85</v>
       </c>
       <c r="AO175" t="s" s="2">
-        <v>728</v>
+        <v>85</v>
       </c>
       <c r="AP175" t="s" s="2">
-        <v>397</v>
+        <v>85</v>
       </c>
       <c r="AQ175" t="s" s="2">
-        <v>398</v>
+        <v>138</v>
       </c>
       <c r="AR175" t="s" s="2">
-        <v>399</v>
+        <v>85</v>
       </c>
       <c r="AS175" t="s" s="2">
         <v>85</v>
@@ -25862,10 +25868,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -25873,7 +25879,7 @@
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G176" t="s" s="2">
         <v>95</v>
@@ -25888,19 +25894,19 @@
         <v>96</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>481</v>
+        <v>172</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="O176" t="s" s="2">
-        <v>485</v>
+        <v>727</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>85</v>
@@ -25910,7 +25916,7 @@
         <v>85</v>
       </c>
       <c r="S176" t="s" s="2">
-        <v>85</v>
+        <v>871</v>
       </c>
       <c r="T176" t="s" s="2">
         <v>85</v>
@@ -25928,41 +25934,43 @@
         <v>228</v>
       </c>
       <c r="Y176" t="s" s="2">
-        <v>486</v>
+        <v>393</v>
       </c>
       <c r="Z176" t="s" s="2">
-        <v>487</v>
+        <v>394</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB176" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AC176" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="AC176" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="AD176" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE176" t="s" s="2">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="AG176" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH176" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AI176" t="s" s="2">
-        <v>733</v>
+        <v>85</v>
       </c>
       <c r="AJ176" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK176" t="s" s="2">
-        <v>85</v>
+        <v>872</v>
       </c>
       <c r="AL176" t="s" s="2">
         <v>85</v>
@@ -25974,31 +25982,29 @@
         <v>85</v>
       </c>
       <c r="AO176" t="s" s="2">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="AP176" t="s" s="2">
-        <v>490</v>
+        <v>397</v>
       </c>
       <c r="AQ176" t="s" s="2">
-        <v>491</v>
+        <v>398</v>
       </c>
       <c r="AR176" t="s" s="2">
-        <v>85</v>
+        <v>399</v>
       </c>
       <c r="AS176" t="s" s="2">
-        <v>492</v>
+        <v>85</v>
       </c>
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B177" t="s" s="2">
         <v>729</v>
       </c>
-      <c r="C177" t="s" s="2">
-        <v>851</v>
-      </c>
+      <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
         <v>85</v>
       </c>
@@ -26019,7 +26025,7 @@
         <v>96</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>172</v>
+        <v>481</v>
       </c>
       <c r="L177" t="s" s="2">
         <v>730</v>
@@ -26068,16 +26074,14 @@
         <v>85</v>
       </c>
       <c r="AB177" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC177" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="AC177" s="2"/>
       <c r="AD177" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE177" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF177" t="s" s="2">
         <v>729</v>
@@ -26124,12 +26128,14 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>782</v>
-      </c>
-      <c r="C178" s="2"/>
+        <v>729</v>
+      </c>
+      <c r="C178" t="s" s="2">
+        <v>853</v>
+      </c>
       <c r="D178" t="s" s="2">
         <v>85</v>
       </c>
@@ -26141,25 +26147,29 @@
         <v>95</v>
       </c>
       <c r="H178" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I178" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J178" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>154</v>
+        <v>730</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N178" s="2"/>
-      <c r="O178" s="2"/>
+        <v>731</v>
+      </c>
+      <c r="N178" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="O178" t="s" s="2">
+        <v>485</v>
+      </c>
       <c r="P178" t="s" s="2">
         <v>85</v>
       </c>
@@ -26183,13 +26193,13 @@
         <v>85</v>
       </c>
       <c r="X178" t="s" s="2">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="Y178" t="s" s="2">
-        <v>85</v>
+        <v>486</v>
       </c>
       <c r="Z178" t="s" s="2">
-        <v>85</v>
+        <v>487</v>
       </c>
       <c r="AA178" t="s" s="2">
         <v>85</v>
@@ -26207,7 +26217,7 @@
         <v>85</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>156</v>
+        <v>729</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>83</v>
@@ -26216,10 +26226,10 @@
         <v>95</v>
       </c>
       <c r="AI178" t="s" s="2">
-        <v>85</v>
+        <v>733</v>
       </c>
       <c r="AJ178" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK178" t="s" s="2">
         <v>85</v>
@@ -26234,38 +26244,38 @@
         <v>85</v>
       </c>
       <c r="AO178" t="s" s="2">
-        <v>85</v>
+        <v>734</v>
       </c>
       <c r="AP178" t="s" s="2">
-        <v>85</v>
+        <v>490</v>
       </c>
       <c r="AQ178" t="s" s="2">
-        <v>158</v>
+        <v>491</v>
       </c>
       <c r="AR178" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS178" t="s" s="2">
-        <v>85</v>
+        <v>492</v>
       </c>
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B179" t="s" s="2">
         <v>784</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="E179" s="2"/>
       <c r="F179" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G179" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H179" t="s" s="2">
         <v>85</v>
@@ -26277,17 +26287,15 @@
         <v>85</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N179" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N179" s="2"/>
       <c r="O179" s="2"/>
       <c r="P179" t="s" s="2">
         <v>85</v>
@@ -26324,31 +26332,31 @@
         <v>85</v>
       </c>
       <c r="AB179" t="s" s="2">
-        <v>143</v>
+        <v>85</v>
       </c>
       <c r="AC179" t="s" s="2">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="AD179" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE179" t="s" s="2">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH179" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI179" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ179" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK179" t="s" s="2">
         <v>85</v>
@@ -26380,14 +26388,14 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>855</v>
+        <v>786</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
-        <v>85</v>
+        <v>194</v>
       </c>
       <c r="E180" s="2"/>
       <c r="F180" t="s" s="2">
@@ -26397,29 +26405,27 @@
         <v>84</v>
       </c>
       <c r="H180" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I180" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J180" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>320</v>
+        <v>140</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>321</v>
+        <v>212</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>322</v>
+        <v>213</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="O180" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="O180" s="2"/>
       <c r="P180" t="s" s="2">
         <v>85</v>
       </c>
@@ -26443,29 +26449,31 @@
         <v>85</v>
       </c>
       <c r="X180" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="Y180" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="Y180" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="Z180" t="s" s="2">
-        <v>876</v>
+        <v>85</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB180" t="s" s="2">
-        <v>85</v>
+        <v>143</v>
       </c>
       <c r="AC180" t="s" s="2">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="AD180" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE180" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>325</v>
+        <v>162</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>83</v>
@@ -26477,16 +26485,16 @@
         <v>85</v>
       </c>
       <c r="AJ180" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK180" t="s" s="2">
-        <v>877</v>
+        <v>85</v>
       </c>
       <c r="AL180" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AM180" t="s" s="2">
-        <v>180</v>
+        <v>85</v>
       </c>
       <c r="AN180" t="s" s="2">
         <v>85</v>
@@ -26495,10 +26503,10 @@
         <v>85</v>
       </c>
       <c r="AP180" t="s" s="2">
-        <v>326</v>
+        <v>85</v>
       </c>
       <c r="AQ180" t="s" s="2">
-        <v>327</v>
+        <v>158</v>
       </c>
       <c r="AR180" t="s" s="2">
         <v>85</v>
@@ -26509,10 +26517,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -26523,10 +26531,10 @@
         <v>83</v>
       </c>
       <c r="G181" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H181" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I181" t="s" s="2">
         <v>85</v>
@@ -26535,19 +26543,19 @@
         <v>96</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>210</v>
+        <v>320</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>379</v>
+        <v>321</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>380</v>
+        <v>322</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>381</v>
+        <v>323</v>
       </c>
       <c r="O181" t="s" s="2">
-        <v>382</v>
+        <v>324</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>85</v>
@@ -26572,13 +26580,11 @@
         <v>85</v>
       </c>
       <c r="X181" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y181" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="Y181" s="2"/>
       <c r="Z181" t="s" s="2">
-        <v>85</v>
+        <v>878</v>
       </c>
       <c r="AA181" t="s" s="2">
         <v>85</v>
@@ -26596,13 +26602,13 @@
         <v>85</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>383</v>
+        <v>325</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH181" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI181" t="s" s="2">
         <v>85</v>
@@ -26611,13 +26617,13 @@
         <v>107</v>
       </c>
       <c r="AK181" t="s" s="2">
-        <v>85</v>
+        <v>879</v>
       </c>
       <c r="AL181" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AM181" t="s" s="2">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="AN181" t="s" s="2">
         <v>85</v>
@@ -26626,10 +26632,10 @@
         <v>85</v>
       </c>
       <c r="AP181" t="s" s="2">
-        <v>384</v>
+        <v>326</v>
       </c>
       <c r="AQ181" t="s" s="2">
-        <v>385</v>
+        <v>327</v>
       </c>
       <c r="AR181" t="s" s="2">
         <v>85</v>
@@ -26640,10 +26646,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>735</v>
+        <v>861</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -26657,28 +26663,28 @@
         <v>95</v>
       </c>
       <c r="H182" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I182" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J182" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="I182" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J182" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="K182" t="s" s="2">
-        <v>172</v>
+        <v>210</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>736</v>
+        <v>379</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>737</v>
+        <v>380</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>738</v>
+        <v>381</v>
       </c>
       <c r="O182" t="s" s="2">
-        <v>580</v>
+        <v>382</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>85</v>
@@ -26703,13 +26709,13 @@
         <v>85</v>
       </c>
       <c r="X182" t="s" s="2">
-        <v>228</v>
+        <v>85</v>
       </c>
       <c r="Y182" t="s" s="2">
-        <v>581</v>
+        <v>85</v>
       </c>
       <c r="Z182" t="s" s="2">
-        <v>582</v>
+        <v>85</v>
       </c>
       <c r="AA182" t="s" s="2">
         <v>85</v>
@@ -26727,7 +26733,7 @@
         <v>85</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>735</v>
+        <v>383</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>83</v>
@@ -26736,7 +26742,7 @@
         <v>95</v>
       </c>
       <c r="AI182" t="s" s="2">
-        <v>739</v>
+        <v>85</v>
       </c>
       <c r="AJ182" t="s" s="2">
         <v>107</v>
@@ -26757,10 +26763,10 @@
         <v>85</v>
       </c>
       <c r="AP182" t="s" s="2">
-        <v>138</v>
+        <v>384</v>
       </c>
       <c r="AQ182" t="s" s="2">
-        <v>585</v>
+        <v>385</v>
       </c>
       <c r="AR182" t="s" s="2">
         <v>85</v>
@@ -26771,24 +26777,24 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
-        <v>587</v>
+        <v>85</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G183" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H183" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I183" t="s" s="2">
         <v>85</v>
@@ -26800,16 +26806,16 @@
         <v>172</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>588</v>
+        <v>738</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>589</v>
+        <v>739</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>590</v>
+        <v>740</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>591</v>
+        <v>580</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>85</v>
@@ -26837,10 +26843,10 @@
         <v>228</v>
       </c>
       <c r="Y183" t="s" s="2">
-        <v>592</v>
+        <v>581</v>
       </c>
       <c r="Z183" t="s" s="2">
-        <v>593</v>
+        <v>582</v>
       </c>
       <c r="AA183" t="s" s="2">
         <v>85</v>
@@ -26858,16 +26864,16 @@
         <v>85</v>
       </c>
       <c r="AF183" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="AG183" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH183" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI183" t="s" s="2">
         <v>741</v>
-      </c>
-      <c r="AG183" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH183" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI183" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="AJ183" t="s" s="2">
         <v>107</v>
@@ -26885,31 +26891,31 @@
         <v>85</v>
       </c>
       <c r="AO183" t="s" s="2">
-        <v>594</v>
+        <v>85</v>
       </c>
       <c r="AP183" t="s" s="2">
-        <v>595</v>
+        <v>138</v>
       </c>
       <c r="AQ183" t="s" s="2">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="AR183" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS183" t="s" s="2">
-        <v>597</v>
+        <v>85</v>
       </c>
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
-        <v>85</v>
+        <v>587</v>
       </c>
       <c r="E184" s="2"/>
       <c r="F184" t="s" s="2">
@@ -26928,19 +26934,19 @@
         <v>85</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>743</v>
+        <v>588</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>744</v>
+        <v>589</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>647</v>
+        <v>590</v>
       </c>
       <c r="O184" t="s" s="2">
-        <v>648</v>
+        <v>591</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>85</v>
@@ -26965,13 +26971,13 @@
         <v>85</v>
       </c>
       <c r="X184" t="s" s="2">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="Y184" t="s" s="2">
-        <v>85</v>
+        <v>592</v>
       </c>
       <c r="Z184" t="s" s="2">
-        <v>85</v>
+        <v>593</v>
       </c>
       <c r="AA184" t="s" s="2">
         <v>85</v>
@@ -26989,7 +26995,7 @@
         <v>85</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>83</v>
@@ -27016,31 +27022,29 @@
         <v>85</v>
       </c>
       <c r="AO184" t="s" s="2">
-        <v>85</v>
+        <v>594</v>
       </c>
       <c r="AP184" t="s" s="2">
-        <v>650</v>
+        <v>595</v>
       </c>
       <c r="AQ184" t="s" s="2">
-        <v>651</v>
+        <v>596</v>
       </c>
       <c r="AR184" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS184" t="s" s="2">
-        <v>85</v>
+        <v>597</v>
       </c>
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="C185" t="s" s="2">
-        <v>883</v>
-      </c>
+        <v>744</v>
+      </c>
+      <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
         <v>85</v>
       </c>
@@ -27049,31 +27053,31 @@
         <v>83</v>
       </c>
       <c r="G185" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H185" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I185" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J185" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>644</v>
+        <v>86</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>712</v>
+        <v>745</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>713</v>
+        <v>746</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>714</v>
+        <v>647</v>
       </c>
       <c r="O185" t="s" s="2">
-        <v>715</v>
+        <v>648</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>85</v>
@@ -27122,7 +27126,7 @@
         <v>85</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>710</v>
+        <v>744</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>83</v>
@@ -27134,7 +27138,7 @@
         <v>85</v>
       </c>
       <c r="AJ185" t="s" s="2">
-        <v>717</v>
+        <v>107</v>
       </c>
       <c r="AK185" t="s" s="2">
         <v>85</v>
@@ -27152,10 +27156,10 @@
         <v>85</v>
       </c>
       <c r="AP185" t="s" s="2">
-        <v>718</v>
+        <v>650</v>
       </c>
       <c r="AQ185" t="s" s="2">
-        <v>719</v>
+        <v>651</v>
       </c>
       <c r="AR185" t="s" s="2">
         <v>85</v>
@@ -27169,9 +27173,11 @@
         <v>884</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="C186" s="2"/>
+        <v>710</v>
+      </c>
+      <c r="C186" t="s" s="2">
+        <v>885</v>
+      </c>
       <c r="D186" t="s" s="2">
         <v>85</v>
       </c>
@@ -27183,25 +27189,29 @@
         <v>95</v>
       </c>
       <c r="H186" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I186" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J186" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>210</v>
+        <v>644</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>154</v>
+        <v>712</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N186" s="2"/>
-      <c r="O186" s="2"/>
+        <v>713</v>
+      </c>
+      <c r="N186" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="O186" t="s" s="2">
+        <v>715</v>
+      </c>
       <c r="P186" t="s" s="2">
         <v>85</v>
       </c>
@@ -27249,19 +27259,19 @@
         <v>85</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>156</v>
+        <v>710</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH186" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI186" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ186" t="s" s="2">
-        <v>85</v>
+        <v>717</v>
       </c>
       <c r="AK186" t="s" s="2">
         <v>85</v>
@@ -27279,10 +27289,10 @@
         <v>85</v>
       </c>
       <c r="AP186" t="s" s="2">
-        <v>85</v>
+        <v>718</v>
       </c>
       <c r="AQ186" t="s" s="2">
-        <v>158</v>
+        <v>719</v>
       </c>
       <c r="AR186" t="s" s="2">
         <v>85</v>
@@ -27293,21 +27303,21 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="E187" s="2"/>
       <c r="F187" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G187" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H187" t="s" s="2">
         <v>85</v>
@@ -27319,17 +27329,15 @@
         <v>85</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N187" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N187" s="2"/>
       <c r="O187" s="2"/>
       <c r="P187" t="s" s="2">
         <v>85</v>
@@ -27378,19 +27386,19 @@
         <v>85</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH187" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI187" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ187" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK187" t="s" s="2">
         <v>85</v>
@@ -27422,14 +27430,14 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
-        <v>655</v>
+        <v>194</v>
       </c>
       <c r="E188" s="2"/>
       <c r="F188" t="s" s="2">
@@ -27442,26 +27450,24 @@
         <v>85</v>
       </c>
       <c r="I188" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J188" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K188" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>656</v>
+        <v>212</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>657</v>
+        <v>213</v>
       </c>
       <c r="N188" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="O188" t="s" s="2">
-        <v>198</v>
-      </c>
+      <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
         <v>85</v>
       </c>
@@ -27509,7 +27515,7 @@
         <v>85</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>658</v>
+        <v>162</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>83</v>
@@ -27542,7 +27548,7 @@
         <v>85</v>
       </c>
       <c r="AQ188" t="s" s="2">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="AR188" t="s" s="2">
         <v>85</v>
@@ -27553,45 +27559,45 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
-        <v>85</v>
+        <v>655</v>
       </c>
       <c r="E189" s="2"/>
       <c r="F189" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G189" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H189" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I189" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="I189" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="J189" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>724</v>
+        <v>656</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>725</v>
+        <v>657</v>
       </c>
       <c r="N189" t="s" s="2">
-        <v>726</v>
+        <v>197</v>
       </c>
       <c r="O189" t="s" s="2">
-        <v>727</v>
+        <v>198</v>
       </c>
       <c r="P189" t="s" s="2">
         <v>85</v>
@@ -27601,7 +27607,7 @@
         <v>85</v>
       </c>
       <c r="S189" t="s" s="2">
-        <v>869</v>
+        <v>85</v>
       </c>
       <c r="T189" t="s" s="2">
         <v>85</v>
@@ -27616,13 +27622,13 @@
         <v>85</v>
       </c>
       <c r="X189" t="s" s="2">
-        <v>228</v>
+        <v>85</v>
       </c>
       <c r="Y189" t="s" s="2">
-        <v>393</v>
+        <v>85</v>
       </c>
       <c r="Z189" t="s" s="2">
-        <v>394</v>
+        <v>85</v>
       </c>
       <c r="AA189" t="s" s="2">
         <v>85</v>
@@ -27640,22 +27646,22 @@
         <v>85</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>723</v>
+        <v>658</v>
       </c>
       <c r="AG189" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH189" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI189" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ189" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK189" t="s" s="2">
-        <v>888</v>
+        <v>85</v>
       </c>
       <c r="AL189" t="s" s="2">
         <v>85</v>
@@ -27667,16 +27673,16 @@
         <v>85</v>
       </c>
       <c r="AO189" t="s" s="2">
-        <v>728</v>
+        <v>85</v>
       </c>
       <c r="AP189" t="s" s="2">
-        <v>397</v>
+        <v>85</v>
       </c>
       <c r="AQ189" t="s" s="2">
-        <v>398</v>
+        <v>138</v>
       </c>
       <c r="AR189" t="s" s="2">
-        <v>399</v>
+        <v>85</v>
       </c>
       <c r="AS189" t="s" s="2">
         <v>85</v>
@@ -27687,7 +27693,7 @@
         <v>889</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -27695,7 +27701,7 @@
       </c>
       <c r="E190" s="2"/>
       <c r="F190" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G190" t="s" s="2">
         <v>95</v>
@@ -27710,19 +27716,19 @@
         <v>96</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>481</v>
+        <v>172</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="O190" t="s" s="2">
-        <v>485</v>
+        <v>727</v>
       </c>
       <c r="P190" t="s" s="2">
         <v>85</v>
@@ -27732,7 +27738,7 @@
         <v>85</v>
       </c>
       <c r="S190" t="s" s="2">
-        <v>85</v>
+        <v>871</v>
       </c>
       <c r="T190" t="s" s="2">
         <v>85</v>
@@ -27750,41 +27756,43 @@
         <v>228</v>
       </c>
       <c r="Y190" t="s" s="2">
-        <v>486</v>
+        <v>393</v>
       </c>
       <c r="Z190" t="s" s="2">
-        <v>487</v>
+        <v>394</v>
       </c>
       <c r="AA190" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB190" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AC190" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="AC190" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="AD190" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE190" t="s" s="2">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="AG190" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH190" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AI190" t="s" s="2">
-        <v>733</v>
+        <v>85</v>
       </c>
       <c r="AJ190" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK190" t="s" s="2">
-        <v>85</v>
+        <v>890</v>
       </c>
       <c r="AL190" t="s" s="2">
         <v>85</v>
@@ -27796,31 +27804,29 @@
         <v>85</v>
       </c>
       <c r="AO190" t="s" s="2">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="AP190" t="s" s="2">
-        <v>490</v>
+        <v>397</v>
       </c>
       <c r="AQ190" t="s" s="2">
-        <v>491</v>
+        <v>398</v>
       </c>
       <c r="AR190" t="s" s="2">
-        <v>85</v>
+        <v>399</v>
       </c>
       <c r="AS190" t="s" s="2">
-        <v>492</v>
+        <v>85</v>
       </c>
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B191" t="s" s="2">
         <v>729</v>
       </c>
-      <c r="C191" t="s" s="2">
-        <v>851</v>
-      </c>
+      <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
         <v>85</v>
       </c>
@@ -27841,7 +27847,7 @@
         <v>96</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>172</v>
+        <v>481</v>
       </c>
       <c r="L191" t="s" s="2">
         <v>730</v>
@@ -27890,16 +27896,14 @@
         <v>85</v>
       </c>
       <c r="AB191" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC191" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="AC191" s="2"/>
       <c r="AD191" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE191" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF191" t="s" s="2">
         <v>729</v>
@@ -27946,12 +27950,14 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>782</v>
-      </c>
-      <c r="C192" s="2"/>
+        <v>729</v>
+      </c>
+      <c r="C192" t="s" s="2">
+        <v>853</v>
+      </c>
       <c r="D192" t="s" s="2">
         <v>85</v>
       </c>
@@ -27963,25 +27969,29 @@
         <v>95</v>
       </c>
       <c r="H192" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I192" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J192" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>154</v>
+        <v>730</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N192" s="2"/>
-      <c r="O192" s="2"/>
+        <v>731</v>
+      </c>
+      <c r="N192" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="O192" t="s" s="2">
+        <v>485</v>
+      </c>
       <c r="P192" t="s" s="2">
         <v>85</v>
       </c>
@@ -28005,13 +28015,13 @@
         <v>85</v>
       </c>
       <c r="X192" t="s" s="2">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="Y192" t="s" s="2">
-        <v>85</v>
+        <v>486</v>
       </c>
       <c r="Z192" t="s" s="2">
-        <v>85</v>
+        <v>487</v>
       </c>
       <c r="AA192" t="s" s="2">
         <v>85</v>
@@ -28029,7 +28039,7 @@
         <v>85</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>156</v>
+        <v>729</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>83</v>
@@ -28038,10 +28048,10 @@
         <v>95</v>
       </c>
       <c r="AI192" t="s" s="2">
-        <v>85</v>
+        <v>733</v>
       </c>
       <c r="AJ192" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK192" t="s" s="2">
         <v>85</v>
@@ -28056,38 +28066,38 @@
         <v>85</v>
       </c>
       <c r="AO192" t="s" s="2">
-        <v>85</v>
+        <v>734</v>
       </c>
       <c r="AP192" t="s" s="2">
-        <v>85</v>
+        <v>490</v>
       </c>
       <c r="AQ192" t="s" s="2">
-        <v>158</v>
+        <v>491</v>
       </c>
       <c r="AR192" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS192" t="s" s="2">
-        <v>85</v>
+        <v>492</v>
       </c>
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B193" t="s" s="2">
         <v>784</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="E193" s="2"/>
       <c r="F193" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G193" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H193" t="s" s="2">
         <v>85</v>
@@ -28099,17 +28109,15 @@
         <v>85</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N193" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N193" s="2"/>
       <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
         <v>85</v>
@@ -28146,31 +28154,31 @@
         <v>85</v>
       </c>
       <c r="AB193" t="s" s="2">
-        <v>143</v>
+        <v>85</v>
       </c>
       <c r="AC193" t="s" s="2">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="AD193" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE193" t="s" s="2">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH193" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI193" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ193" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK193" t="s" s="2">
         <v>85</v>
@@ -28202,14 +28210,14 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>855</v>
+        <v>786</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
-        <v>85</v>
+        <v>194</v>
       </c>
       <c r="E194" s="2"/>
       <c r="F194" t="s" s="2">
@@ -28219,29 +28227,27 @@
         <v>84</v>
       </c>
       <c r="H194" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I194" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J194" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>320</v>
+        <v>140</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>321</v>
+        <v>212</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>322</v>
+        <v>213</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="O194" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="O194" s="2"/>
       <c r="P194" t="s" s="2">
         <v>85</v>
       </c>
@@ -28265,29 +28271,31 @@
         <v>85</v>
       </c>
       <c r="X194" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="Y194" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="Y194" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="Z194" t="s" s="2">
-        <v>894</v>
+        <v>85</v>
       </c>
       <c r="AA194" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB194" t="s" s="2">
-        <v>85</v>
+        <v>143</v>
       </c>
       <c r="AC194" t="s" s="2">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="AD194" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE194" t="s" s="2">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>325</v>
+        <v>162</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>83</v>
@@ -28299,16 +28307,16 @@
         <v>85</v>
       </c>
       <c r="AJ194" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK194" t="s" s="2">
-        <v>895</v>
+        <v>85</v>
       </c>
       <c r="AL194" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AM194" t="s" s="2">
-        <v>180</v>
+        <v>85</v>
       </c>
       <c r="AN194" t="s" s="2">
         <v>85</v>
@@ -28317,10 +28325,10 @@
         <v>85</v>
       </c>
       <c r="AP194" t="s" s="2">
-        <v>326</v>
+        <v>85</v>
       </c>
       <c r="AQ194" t="s" s="2">
-        <v>327</v>
+        <v>158</v>
       </c>
       <c r="AR194" t="s" s="2">
         <v>85</v>
@@ -28331,10 +28339,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -28345,10 +28353,10 @@
         <v>83</v>
       </c>
       <c r="G195" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H195" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I195" t="s" s="2">
         <v>85</v>
@@ -28357,19 +28365,19 @@
         <v>96</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>210</v>
+        <v>320</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>379</v>
+        <v>321</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>380</v>
+        <v>322</v>
       </c>
       <c r="N195" t="s" s="2">
-        <v>381</v>
+        <v>323</v>
       </c>
       <c r="O195" t="s" s="2">
-        <v>382</v>
+        <v>324</v>
       </c>
       <c r="P195" t="s" s="2">
         <v>85</v>
@@ -28394,13 +28402,11 @@
         <v>85</v>
       </c>
       <c r="X195" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y195" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="Y195" s="2"/>
       <c r="Z195" t="s" s="2">
-        <v>85</v>
+        <v>896</v>
       </c>
       <c r="AA195" t="s" s="2">
         <v>85</v>
@@ -28418,13 +28424,13 @@
         <v>85</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>383</v>
+        <v>325</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH195" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI195" t="s" s="2">
         <v>85</v>
@@ -28433,13 +28439,13 @@
         <v>107</v>
       </c>
       <c r="AK195" t="s" s="2">
-        <v>85</v>
+        <v>897</v>
       </c>
       <c r="AL195" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AM195" t="s" s="2">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="AN195" t="s" s="2">
         <v>85</v>
@@ -28448,10 +28454,10 @@
         <v>85</v>
       </c>
       <c r="AP195" t="s" s="2">
-        <v>384</v>
+        <v>326</v>
       </c>
       <c r="AQ195" t="s" s="2">
-        <v>385</v>
+        <v>327</v>
       </c>
       <c r="AR195" t="s" s="2">
         <v>85</v>
@@ -28462,10 +28468,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>735</v>
+        <v>861</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -28479,28 +28485,28 @@
         <v>95</v>
       </c>
       <c r="H196" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I196" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J196" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="I196" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J196" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="K196" t="s" s="2">
-        <v>172</v>
+        <v>210</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>736</v>
+        <v>379</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>737</v>
+        <v>380</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>738</v>
+        <v>381</v>
       </c>
       <c r="O196" t="s" s="2">
-        <v>580</v>
+        <v>382</v>
       </c>
       <c r="P196" t="s" s="2">
         <v>85</v>
@@ -28525,13 +28531,13 @@
         <v>85</v>
       </c>
       <c r="X196" t="s" s="2">
-        <v>228</v>
+        <v>85</v>
       </c>
       <c r="Y196" t="s" s="2">
-        <v>581</v>
+        <v>85</v>
       </c>
       <c r="Z196" t="s" s="2">
-        <v>582</v>
+        <v>85</v>
       </c>
       <c r="AA196" t="s" s="2">
         <v>85</v>
@@ -28549,7 +28555,7 @@
         <v>85</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>735</v>
+        <v>383</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>83</v>
@@ -28558,7 +28564,7 @@
         <v>95</v>
       </c>
       <c r="AI196" t="s" s="2">
-        <v>739</v>
+        <v>85</v>
       </c>
       <c r="AJ196" t="s" s="2">
         <v>107</v>
@@ -28579,10 +28585,10 @@
         <v>85</v>
       </c>
       <c r="AP196" t="s" s="2">
-        <v>138</v>
+        <v>384</v>
       </c>
       <c r="AQ196" t="s" s="2">
-        <v>585</v>
+        <v>385</v>
       </c>
       <c r="AR196" t="s" s="2">
         <v>85</v>
@@ -28593,24 +28599,24 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
-        <v>587</v>
+        <v>85</v>
       </c>
       <c r="E197" s="2"/>
       <c r="F197" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G197" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H197" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I197" t="s" s="2">
         <v>85</v>
@@ -28622,16 +28628,16 @@
         <v>172</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>588</v>
+        <v>738</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>589</v>
+        <v>739</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>590</v>
+        <v>740</v>
       </c>
       <c r="O197" t="s" s="2">
-        <v>591</v>
+        <v>580</v>
       </c>
       <c r="P197" t="s" s="2">
         <v>85</v>
@@ -28659,10 +28665,10 @@
         <v>228</v>
       </c>
       <c r="Y197" t="s" s="2">
-        <v>592</v>
+        <v>581</v>
       </c>
       <c r="Z197" t="s" s="2">
-        <v>593</v>
+        <v>582</v>
       </c>
       <c r="AA197" t="s" s="2">
         <v>85</v>
@@ -28680,16 +28686,16 @@
         <v>85</v>
       </c>
       <c r="AF197" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="AG197" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH197" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI197" t="s" s="2">
         <v>741</v>
-      </c>
-      <c r="AG197" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH197" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI197" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="AJ197" t="s" s="2">
         <v>107</v>
@@ -28707,31 +28713,31 @@
         <v>85</v>
       </c>
       <c r="AO197" t="s" s="2">
-        <v>594</v>
+        <v>85</v>
       </c>
       <c r="AP197" t="s" s="2">
-        <v>595</v>
+        <v>138</v>
       </c>
       <c r="AQ197" t="s" s="2">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="AR197" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS197" t="s" s="2">
-        <v>597</v>
+        <v>85</v>
       </c>
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
-        <v>85</v>
+        <v>587</v>
       </c>
       <c r="E198" s="2"/>
       <c r="F198" t="s" s="2">
@@ -28750,19 +28756,19 @@
         <v>85</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>743</v>
+        <v>588</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>744</v>
+        <v>589</v>
       </c>
       <c r="N198" t="s" s="2">
-        <v>647</v>
+        <v>590</v>
       </c>
       <c r="O198" t="s" s="2">
-        <v>648</v>
+        <v>591</v>
       </c>
       <c r="P198" t="s" s="2">
         <v>85</v>
@@ -28787,13 +28793,13 @@
         <v>85</v>
       </c>
       <c r="X198" t="s" s="2">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="Y198" t="s" s="2">
-        <v>85</v>
+        <v>592</v>
       </c>
       <c r="Z198" t="s" s="2">
-        <v>85</v>
+        <v>593</v>
       </c>
       <c r="AA198" t="s" s="2">
         <v>85</v>
@@ -28811,7 +28817,7 @@
         <v>85</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>83</v>
@@ -28838,23 +28844,154 @@
         <v>85</v>
       </c>
       <c r="AO198" t="s" s="2">
-        <v>85</v>
+        <v>594</v>
       </c>
       <c r="AP198" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AQ198" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AR198" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS198" t="s" s="2">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="199" hidden="true">
+      <c r="A199" t="s" s="2">
+        <v>901</v>
+      </c>
+      <c r="B199" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="C199" s="2"/>
+      <c r="D199" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E199" s="2"/>
+      <c r="F199" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G199" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H199" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I199" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J199" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K199" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L199" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="M199" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="N199" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="O199" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="P199" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q199" s="2"/>
+      <c r="R199" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S199" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T199" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U199" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V199" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W199" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X199" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y199" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z199" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA199" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB199" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC199" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD199" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE199" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF199" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="AG199" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH199" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI199" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ199" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK199" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL199" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM199" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN199" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO199" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP199" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="AQ198" t="s" s="2">
+      <c r="AQ199" t="s" s="2">
         <v>651</v>
       </c>
-      <c r="AR198" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS198" t="s" s="2">
+      <c r="AR199" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS199" t="s" s="2">
         <v>85</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS198">
+  <autoFilter ref="A1:AS199">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -28864,7 +29001,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI197">
+  <conditionalFormatting sqref="A2:AI198">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8252" uniqueCount="902">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8252" uniqueCount="905">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -792,7 +792,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>660: source value from GMRV VITAL MEASUREMENT - IEN (120.5-.001)</t>
+    <t>660: source value based on GMRV VITAL MEASUREMENT - IEN (120.5-.001)</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -925,10 +925,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vsbp-12-655:120.5-4: if null then #final {null}vsbp-12-656:120.5-4: if not null then #entered-in-error {null}</t>
-  </si>
-  <si>
-    <t>656: fixed value = #entered-in-error when GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (120.5-4) case not null</t>
+vsbp-12-655:If (120.5-4) is null then fixed value #final {null}vsbp-12-656:If (120.5-4) is not null then fixed value #entered-in-error {null}</t>
+  </si>
+  <si>
+    <t>656: fixed value = #entered-in-error when GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (120.5-4) if not null</t>
   </si>
   <si>
     <t>Observation.Extension[ObservationExtension].Removed</t>
@@ -1309,7 +1309,7 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
-    <t>659: reference from GMRV VITAL MEASUREMENT - PATIENT (120.5-.02)</t>
+    <t>659: reference based on GMRV VITAL MEASUREMENT - PATIENT (120.5-.02)</t>
   </si>
   <si>
     <t>Vital.VitalSign.PatientIEN</t>
@@ -1438,7 +1438,7 @@
 </t>
   </si>
   <si>
-    <t>657: source value from GMRV VITAL MEASUREMENT - DATE/TIME VITALS TAKEN (120.5-.01)</t>
+    <t>657: source value based on GMRV VITAL MEASUREMENT - DATE/TIME VITALS TAKEN (120.5-.01)</t>
   </si>
   <si>
     <t>Vital.VitalSign.VitalSignTakenDateTime,Vital.VitalSignQualifier.VitalSignTakenDateTime</t>
@@ -1463,7 +1463,7 @@
     <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
-    <t>652: source value from GMRV VITAL MEASUREMENT - DATE/TIME VITALS ENTERED (120.5-.04)</t>
+    <t>652: source value based on GMRV VITAL MEASUREMENT - DATE/TIME VITALS ENTERED (120.5-.04)</t>
   </si>
   <si>
     <t>Vital.VitalSign.VitalSignEnteredDateTime</t>
@@ -1494,7 +1494,7 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
-    <t>1653: reference from GMRV VITAL MEASUREMENT - HOSPITAL LOCATION (120.5-.05)</t>
+    <t>1653: reference based on GMRV VITAL MEASUREMENT - HOSPITAL LOCATION (120.5-.05)</t>
   </si>
   <si>
     <t>Vital.VitalSign.LocationIEN</t>
@@ -1603,7 +1603,11 @@
     <t>Quantity.value</t>
   </si>
   <si>
-    <t>664: source value from GMRV VITAL MEASUREMENT - RATE (120.5-1.2) case VUID not = 4500634</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+vsbp-12-664:If VUID not = 4500634 then source value from (120.5-1.2) {null}</t>
+  </si>
+  <si>
+    <t>664: source value based on GMRV VITAL MEASUREMENT - RATE (120.5-1.2) if VUID not = 4500634</t>
   </si>
   <si>
     <t>Vital.VitalSign.Diastolic,Vital.VitalSign.Systolic,Vital.VitalSign.VitalResult,Vital.VitalSign.VitalResultNumeric</t>
@@ -2420,10 +2424,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vsbp-12-666-2:undefined: if VUID = 4500634 then http://loinc.org {null}</t>
-  </si>
-  <si>
-    <t>666-2: fixed value = http://loinc.org case VUID = 4500634</t>
+vsbp-12-666-2:If (undefined) is VUID = 4500634 then fixed value http://loinc.org {null}</t>
+  </si>
+  <si>
+    <t>666-2: fixed value = http://loinc.org if VUID = 4500634</t>
   </si>
   <si>
     <t>Observation.component:systolic.code.coding.version</t>
@@ -2439,10 +2443,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vsbp-12-666-3:undefined: if VUID = 4500634 then 8480-6 {null}</t>
-  </si>
-  <si>
-    <t>666-3: fixed value = 8480-6 case VUID = 4500634</t>
+vsbp-12-666-3:If (undefined) is VUID = 4500634 then fixed value 8480-6 {null}</t>
+  </si>
+  <si>
+    <t>666-3: fixed value = 8480-6 if VUID = 4500634</t>
   </si>
   <si>
     <t>Observation.component:systolic.code.coding.display</t>
@@ -2484,7 +2488,11 @@
     <t>Observation.component.value[x].value</t>
   </si>
   <si>
-    <t>666: transform using Split_rate_value.Systolic() on GMRV VITAL MEASUREMENT - RATE (120.5-1.2) case VUID = 4500634</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+vsbp-12-666:If VUID = 4500634 then transform (120.5-1.2) using Split_rate_value.Systolic() {null}</t>
+  </si>
+  <si>
+    <t>666: transform using Split_rate_value.Systolic() on GMRV VITAL MEASUREMENT - RATE (120.5-1.2) if VUID = 4500634</t>
   </si>
   <si>
     <t>Observation.component:systolic.value[x].comparator</t>
@@ -2518,10 +2526,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vsbp-12-666-1:undefined: if VUID = 4500634 then mm[Hg] {null}</t>
-  </si>
-  <si>
-    <t>666-1: fixed value = mm[Hg] case VUID = 4500634</t>
+vsbp-12-666-1:If (undefined) is VUID = 4500634 then fixed value mm[Hg] {null}</t>
+  </si>
+  <si>
+    <t>666-1: fixed value = mm[Hg] if VUID = 4500634</t>
   </si>
   <si>
     <t>Observation.component:systolic.dataAbsentReason</t>
@@ -2584,10 +2592,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vsbp-12-667-2:undefined: if VUID = 4500634 then http://loinc.org {null}</t>
-  </si>
-  <si>
-    <t>667-2: fixed value = http://loinc.org case VUID = 4500634</t>
+vsbp-12-667-2:If (undefined) is VUID = 4500634 then fixed value http://loinc.org {null}</t>
+  </si>
+  <si>
+    <t>667-2: fixed value = http://loinc.org if VUID = 4500634</t>
   </si>
   <si>
     <t>Observation.component:diastolic.code.coding.version</t>
@@ -2597,10 +2605,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vsbp-12-667-3:undefined: if VUID = 4500634 then 8462-4 {null}</t>
-  </si>
-  <si>
-    <t>667-3: fixed value = 8462-4 case VUID = 4500634</t>
+vsbp-12-667-3:If (undefined) is VUID = 4500634 then fixed value 8462-4 {null}</t>
+  </si>
+  <si>
+    <t>667-3: fixed value = 8462-4 if VUID = 4500634</t>
   </si>
   <si>
     <t>Observation.component:diastolic.code.coding.display</t>
@@ -2624,7 +2632,11 @@
     <t>Observation.component:diastolic.value[x].value</t>
   </si>
   <si>
-    <t>667: transform using Split_rate_value.Diastolic() on GMRV VITAL MEASUREMENT - RATE (120.5-1.2) case VUID = 4500634</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+vsbp-12-667:If VUID = 4500634 then transform (120.5-1.2) using Split_rate_value.Diastolic() {null}</t>
+  </si>
+  <si>
+    <t>667: transform using Split_rate_value.Diastolic() on GMRV VITAL MEASUREMENT - RATE (120.5-1.2) if VUID = 4500634</t>
   </si>
   <si>
     <t>Observation.component:diastolic.value[x].comparator</t>
@@ -2640,10 +2652,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-vsbp-12-667-1:undefined: if VUID = 4500634 then mm[Hg] {null}</t>
-  </si>
-  <si>
-    <t>667-1: fixed value = mm[Hg] case VUID = 4500634</t>
+vsbp-12-667-1:If (undefined) is VUID = 4500634 then fixed value mm[Hg] {null}</t>
+  </si>
+  <si>
+    <t>667-1: fixed value = mm[Hg] if VUID = 4500634</t>
   </si>
   <si>
     <t>Observation.component:diastolic.dataAbsentReason</t>
@@ -11187,16 +11199,16 @@
         <v>85</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>107</v>
+        <v>508</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>85</v>
@@ -11205,10 +11217,10 @@
         <v>85</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>85</v>
@@ -11219,10 +11231,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -11248,20 +11260,20 @@
         <v>115</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q63" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="R63" t="s" s="2">
         <v>85</v>
@@ -11285,10 +11297,10 @@
         <v>175</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>85</v>
@@ -11306,7 +11318,7 @@
         <v>85</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -11336,10 +11348,10 @@
         <v>85</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>85</v>
@@ -11350,10 +11362,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -11379,14 +11391,14 @@
         <v>210</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>85</v>
@@ -11435,7 +11447,7 @@
         <v>85</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
@@ -11465,10 +11477,10 @@
         <v>85</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>85</v>
@@ -11479,10 +11491,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -11508,14 +11520,14 @@
         <v>109</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>85</v>
@@ -11564,7 +11576,7 @@
         <v>85</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>83</v>
@@ -11573,7 +11585,7 @@
         <v>95</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>107</v>
@@ -11594,10 +11606,10 @@
         <v>85</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>85</v>
@@ -11608,10 +11620,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11637,16 +11649,16 @@
         <v>115</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>85</v>
@@ -11695,7 +11707,7 @@
         <v>85</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>83</v>
@@ -11710,7 +11722,7 @@
         <v>107</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>406</v>
@@ -11725,10 +11737,10 @@
         <v>85</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AR66" t="s" s="2">
         <v>85</v>
@@ -11739,10 +11751,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11768,10 +11780,10 @@
         <v>210</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -11866,10 +11878,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11991,13 +12003,13 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="B69" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="B69" t="s" s="2">
-        <v>554</v>
-      </c>
       <c r="C69" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>85</v>
@@ -12019,16 +12031,16 @@
         <v>85</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -12122,10 +12134,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -12249,10 +12261,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -12376,10 +12388,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -12419,7 +12431,7 @@
       </c>
       <c r="Q72" s="2"/>
       <c r="R72" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="S72" t="s" s="2">
         <v>85</v>
@@ -12505,10 +12517,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12531,7 +12543,7 @@
         <v>85</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="L73" t="s" s="2">
         <v>173</v>
@@ -12549,7 +12561,7 @@
         <v>85</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="T73" t="s" s="2">
         <v>85</v>
@@ -12632,10 +12644,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12661,10 +12673,10 @@
         <v>210</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -12715,7 +12727,7 @@
         <v>85</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>83</v>
@@ -12759,10 +12771,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12788,16 +12800,16 @@
         <v>172</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>85</v>
@@ -12825,10 +12837,10 @@
         <v>228</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>85</v>
@@ -12846,7 +12858,7 @@
         <v>85</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>83</v>
@@ -12855,13 +12867,13 @@
         <v>95</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>85</v>
@@ -12879,7 +12891,7 @@
         <v>138</v>
       </c>
       <c r="AQ75" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AR75" t="s" s="2">
         <v>85</v>
@@ -12890,14 +12902,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -12919,16 +12931,16 @@
         <v>172</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>85</v>
@@ -12956,10 +12968,10 @@
         <v>228</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>85</v>
@@ -12977,7 +12989,7 @@
         <v>85</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>83</v>
@@ -13004,27 +13016,27 @@
         <v>85</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AQ76" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AR76" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS76" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -13047,19 +13059,19 @@
         <v>85</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>85</v>
@@ -13108,7 +13120,7 @@
         <v>85</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>83</v>
@@ -13138,10 +13150,10 @@
         <v>85</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AQ77" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AR77" t="s" s="2">
         <v>85</v>
@@ -13152,10 +13164,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -13181,13 +13193,13 @@
         <v>172</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -13217,7 +13229,7 @@
       </c>
       <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>85</v>
@@ -13235,7 +13247,7 @@
         <v>85</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>83</v>
@@ -13250,7 +13262,7 @@
         <v>107</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>85</v>
@@ -13262,27 +13274,27 @@
         <v>85</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AQ78" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AR78" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS78" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -13308,16 +13320,16 @@
         <v>172</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>85</v>
@@ -13346,7 +13358,7 @@
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>85</v>
@@ -13364,7 +13376,7 @@
         <v>85</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>83</v>
@@ -13379,7 +13391,7 @@
         <v>107</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>85</v>
@@ -13394,10 +13406,10 @@
         <v>85</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AQ79" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AR79" t="s" s="2">
         <v>85</v>
@@ -13408,10 +13420,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -13434,16 +13446,16 @@
         <v>85</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -13493,7 +13505,7 @@
         <v>85</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>83</v>
@@ -13520,27 +13532,27 @@
         <v>85</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AQ80" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AR80" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS80" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -13563,16 +13575,16 @@
         <v>85</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -13622,7 +13634,7 @@
         <v>85</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>83</v>
@@ -13649,27 +13661,27 @@
         <v>85</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AQ81" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AR81" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS81" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13692,19 +13704,19 @@
         <v>85</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>85</v>
@@ -13753,7 +13765,7 @@
         <v>85</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>83</v>
@@ -13765,7 +13777,7 @@
         <v>85</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>85</v>
@@ -13783,10 +13795,10 @@
         <v>85</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AQ82" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AR82" t="s" s="2">
         <v>85</v>
@@ -13797,10 +13809,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13924,10 +13936,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -14053,14 +14065,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -14082,10 +14094,10 @@
         <v>140</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>197</v>
@@ -14140,7 +14152,7 @@
         <v>85</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>83</v>
@@ -14184,10 +14196,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -14210,13 +14222,13 @@
         <v>85</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -14267,7 +14279,7 @@
         <v>85</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>83</v>
@@ -14276,7 +14288,7 @@
         <v>95</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>107</v>
@@ -14297,10 +14309,10 @@
         <v>85</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AQ86" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AR86" t="s" s="2">
         <v>85</v>
@@ -14311,10 +14323,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -14337,13 +14349,13 @@
         <v>85</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -14394,7 +14406,7 @@
         <v>85</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>83</v>
@@ -14403,7 +14415,7 @@
         <v>95</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>107</v>
@@ -14424,10 +14436,10 @@
         <v>85</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AQ87" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AR87" t="s" s="2">
         <v>85</v>
@@ -14438,10 +14450,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -14467,16 +14479,16 @@
         <v>172</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>85</v>
@@ -14504,10 +14516,10 @@
         <v>119</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>85</v>
@@ -14525,7 +14537,7 @@
         <v>85</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>83</v>
@@ -14552,13 +14564,13 @@
         <v>85</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AQ88" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AR88" t="s" s="2">
         <v>85</v>
@@ -14569,10 +14581,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -14598,16 +14610,16 @@
         <v>172</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>85</v>
@@ -14632,13 +14644,13 @@
         <v>85</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>85</v>
@@ -14656,7 +14668,7 @@
         <v>85</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>83</v>
@@ -14683,13 +14695,13 @@
         <v>85</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AQ89" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AR89" t="s" s="2">
         <v>85</v>
@@ -14700,10 +14712,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14726,17 +14738,17 @@
         <v>85</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>85</v>
@@ -14785,7 +14797,7 @@
         <v>85</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>83</v>
@@ -14818,7 +14830,7 @@
         <v>85</v>
       </c>
       <c r="AQ90" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AR90" t="s" s="2">
         <v>85</v>
@@ -14829,10 +14841,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14858,10 +14870,10 @@
         <v>210</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -14912,7 +14924,7 @@
         <v>85</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>83</v>
@@ -14942,10 +14954,10 @@
         <v>85</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AQ91" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AR91" t="s" s="2">
         <v>85</v>
@@ -14956,10 +14968,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14982,16 +14994,16 @@
         <v>96</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -15041,7 +15053,7 @@
         <v>85</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>83</v>
@@ -15071,10 +15083,10 @@
         <v>85</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AQ92" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AR92" t="s" s="2">
         <v>85</v>
@@ -15085,10 +15097,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -15111,16 +15123,16 @@
         <v>96</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -15170,7 +15182,7 @@
         <v>85</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>83</v>
@@ -15200,10 +15212,10 @@
         <v>85</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AQ93" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AR93" t="s" s="2">
         <v>85</v>
@@ -15214,10 +15226,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -15225,7 +15237,7 @@
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="G94" t="s" s="2">
         <v>84</v>
@@ -15240,19 +15252,19 @@
         <v>96</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>85</v>
@@ -15289,7 +15301,7 @@
         <v>85</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="AC94" s="2"/>
       <c r="AD94" t="s" s="2">
@@ -15299,7 +15311,7 @@
         <v>144</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>83</v>
@@ -15311,7 +15323,7 @@
         <v>85</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>85</v>
@@ -15329,10 +15341,10 @@
         <v>85</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AQ94" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AR94" t="s" s="2">
         <v>85</v>
@@ -15343,10 +15355,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -15470,10 +15482,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -15599,14 +15611,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -15628,10 +15640,10 @@
         <v>140</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>197</v>
@@ -15686,7 +15698,7 @@
         <v>85</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>83</v>
@@ -15730,10 +15742,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15759,16 +15771,16 @@
         <v>172</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>85</v>
@@ -15817,7 +15829,7 @@
         <v>85</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>95</v>
@@ -15844,7 +15856,7 @@
         <v>85</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AP98" t="s" s="2">
         <v>397</v>
@@ -15861,10 +15873,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15890,13 +15902,13 @@
         <v>481</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="O99" t="s" s="2">
         <v>485</v>
@@ -15946,7 +15958,7 @@
         <v>144</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>83</v>
@@ -15955,7 +15967,7 @@
         <v>95</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>107</v>
@@ -15973,7 +15985,7 @@
         <v>85</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AP99" t="s" s="2">
         <v>490</v>
@@ -15990,10 +16002,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C100" t="s" s="2">
         <v>494</v>
@@ -16021,13 +16033,13 @@
         <v>495</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="O100" t="s" s="2">
         <v>485</v>
@@ -16079,7 +16091,7 @@
         <v>85</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>83</v>
@@ -16088,13 +16100,13 @@
         <v>95</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>85</v>
@@ -16106,7 +16118,7 @@
         <v>85</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>490</v>
@@ -16123,10 +16135,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -16152,16 +16164,16 @@
         <v>172</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>85</v>
@@ -16189,10 +16201,10 @@
         <v>228</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>85</v>
@@ -16210,7 +16222,7 @@
         <v>85</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>83</v>
@@ -16219,13 +16231,13 @@
         <v>95</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>85</v>
@@ -16243,7 +16255,7 @@
         <v>138</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AR101" t="s" s="2">
         <v>85</v>
@@ -16254,14 +16266,14 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -16283,16 +16295,16 @@
         <v>172</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>85</v>
@@ -16320,10 +16332,10 @@
         <v>228</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>85</v>
@@ -16341,7 +16353,7 @@
         <v>85</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>83</v>
@@ -16368,27 +16380,27 @@
         <v>85</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS102" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -16414,16 +16426,16 @@
         <v>86</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>85</v>
@@ -16472,7 +16484,7 @@
         <v>85</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>83</v>
@@ -16502,10 +16514,10 @@
         <v>85</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>85</v>
@@ -16516,13 +16528,13 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>85</v>
@@ -16544,19 +16556,19 @@
         <v>96</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>85</v>
@@ -16605,7 +16617,7 @@
         <v>85</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>83</v>
@@ -16617,7 +16629,7 @@
         <v>85</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>85</v>
@@ -16635,10 +16647,10 @@
         <v>85</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AQ104" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AR104" t="s" s="2">
         <v>85</v>
@@ -16649,10 +16661,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -16776,10 +16788,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16905,14 +16917,14 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -16934,10 +16946,10 @@
         <v>140</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="N107" t="s" s="2">
         <v>197</v>
@@ -16992,7 +17004,7 @@
         <v>85</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>83</v>
@@ -17036,10 +17048,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -17065,16 +17077,16 @@
         <v>172</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>85</v>
@@ -17084,7 +17096,7 @@
         <v>85</v>
       </c>
       <c r="S108" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="T108" t="s" s="2">
         <v>85</v>
@@ -17123,7 +17135,7 @@
         <v>85</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>95</v>
@@ -17150,7 +17162,7 @@
         <v>85</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AP108" t="s" s="2">
         <v>397</v>
@@ -17167,10 +17179,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -17294,10 +17306,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -17423,10 +17435,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -17554,10 +17566,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -17681,10 +17693,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17810,10 +17822,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17909,10 +17921,10 @@
         <v>85</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>85</v>
@@ -17941,10 +17953,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -18070,10 +18082,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -18167,10 +18179,10 @@
         <v>85</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="AL116" t="s" s="2">
         <v>85</v>
@@ -18199,10 +18211,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -18328,10 +18340,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -18459,10 +18471,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -18590,10 +18602,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -18619,13 +18631,13 @@
         <v>495</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="O120" t="s" s="2">
         <v>485</v>
@@ -18677,7 +18689,7 @@
         <v>85</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>83</v>
@@ -18686,7 +18698,7 @@
         <v>95</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AJ120" t="s" s="2">
         <v>107</v>
@@ -18704,7 +18716,7 @@
         <v>85</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AP120" t="s" s="2">
         <v>490</v>
@@ -18721,10 +18733,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -18848,10 +18860,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18977,10 +18989,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -19076,16 +19088,16 @@
         <v>85</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>107</v>
+        <v>790</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>85</v>
@@ -19094,10 +19106,10 @@
         <v>85</v>
       </c>
       <c r="AP123" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AQ123" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AR123" t="s" s="2">
         <v>85</v>
@@ -19108,10 +19120,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -19137,20 +19149,20 @@
         <v>115</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q124" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="R124" t="s" s="2">
         <v>85</v>
@@ -19174,10 +19186,10 @@
         <v>175</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>85</v>
@@ -19195,7 +19207,7 @@
         <v>85</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>83</v>
@@ -19225,10 +19237,10 @@
         <v>85</v>
       </c>
       <c r="AP124" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AQ124" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AR124" t="s" s="2">
         <v>85</v>
@@ -19239,10 +19251,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -19268,14 +19280,14 @@
         <v>210</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>85</v>
@@ -19324,7 +19336,7 @@
         <v>85</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>83</v>
@@ -19354,10 +19366,10 @@
         <v>85</v>
       </c>
       <c r="AP125" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AQ125" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AR125" t="s" s="2">
         <v>85</v>
@@ -19368,10 +19380,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -19397,21 +19409,21 @@
         <v>109</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q126" s="2"/>
       <c r="R126" t="s" s="2">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="S126" t="s" s="2">
         <v>85</v>
@@ -19453,7 +19465,7 @@
         <v>85</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>83</v>
@@ -19462,7 +19474,7 @@
         <v>95</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>107</v>
@@ -19483,10 +19495,10 @@
         <v>85</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AQ126" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AR126" t="s" s="2">
         <v>85</v>
@@ -19497,10 +19509,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -19526,23 +19538,23 @@
         <v>115</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q127" s="2"/>
       <c r="R127" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="S127" t="s" s="2">
         <v>85</v>
@@ -19584,7 +19596,7 @@
         <v>85</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>83</v>
@@ -19596,10 +19608,10 @@
         <v>85</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>85</v>
@@ -19614,10 +19626,10 @@
         <v>85</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AQ127" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AR127" t="s" s="2">
         <v>85</v>
@@ -19628,10 +19640,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -19657,16 +19669,16 @@
         <v>172</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>85</v>
@@ -19694,10 +19706,10 @@
         <v>228</v>
       </c>
       <c r="Y128" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="Z128" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>85</v>
@@ -19715,7 +19727,7 @@
         <v>85</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>83</v>
@@ -19724,7 +19736,7 @@
         <v>95</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AJ128" t="s" s="2">
         <v>107</v>
@@ -19748,7 +19760,7 @@
         <v>138</v>
       </c>
       <c r="AQ128" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AR128" t="s" s="2">
         <v>85</v>
@@ -19759,14 +19771,14 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
@@ -19788,16 +19800,16 @@
         <v>172</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>85</v>
@@ -19825,10 +19837,10 @@
         <v>228</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>85</v>
@@ -19846,7 +19858,7 @@
         <v>85</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>83</v>
@@ -19873,27 +19885,27 @@
         <v>85</v>
       </c>
       <c r="AO129" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AP129" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AQ129" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AR129" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS129" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -19919,16 +19931,16 @@
         <v>86</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>85</v>
@@ -19977,7 +19989,7 @@
         <v>85</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>83</v>
@@ -20007,10 +20019,10 @@
         <v>85</v>
       </c>
       <c r="AP130" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AQ130" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AR130" t="s" s="2">
         <v>85</v>
@@ -20021,13 +20033,13 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="D131" t="s" s="2">
         <v>85</v>
@@ -20049,19 +20061,19 @@
         <v>96</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>85</v>
@@ -20110,7 +20122,7 @@
         <v>85</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>83</v>
@@ -20122,7 +20134,7 @@
         <v>85</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AK131" t="s" s="2">
         <v>85</v>
@@ -20140,10 +20152,10 @@
         <v>85</v>
       </c>
       <c r="AP131" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AQ131" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AR131" t="s" s="2">
         <v>85</v>
@@ -20154,10 +20166,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -20281,10 +20293,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -20410,14 +20422,14 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
@@ -20439,10 +20451,10 @@
         <v>140</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="N134" t="s" s="2">
         <v>197</v>
@@ -20497,7 +20509,7 @@
         <v>85</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>83</v>
@@ -20541,10 +20553,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -20570,16 +20582,16 @@
         <v>172</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>85</v>
@@ -20589,7 +20601,7 @@
         <v>85</v>
       </c>
       <c r="S135" t="s" s="2">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="T135" t="s" s="2">
         <v>85</v>
@@ -20628,7 +20640,7 @@
         <v>85</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>95</v>
@@ -20655,7 +20667,7 @@
         <v>85</v>
       </c>
       <c r="AO135" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AP135" t="s" s="2">
         <v>397</v>
@@ -20672,10 +20684,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -20799,10 +20811,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -20928,10 +20940,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -21059,10 +21071,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -21186,10 +21198,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -21315,10 +21327,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -21414,10 +21426,10 @@
         <v>85</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="AL141" t="s" s="2">
         <v>85</v>
@@ -21446,10 +21458,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -21575,10 +21587,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -21672,10 +21684,10 @@
         <v>85</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="AL143" t="s" s="2">
         <v>85</v>
@@ -21704,10 +21716,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -21833,10 +21845,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -21964,10 +21976,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -22095,10 +22107,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -22124,13 +22136,13 @@
         <v>495</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="O147" t="s" s="2">
         <v>485</v>
@@ -22182,7 +22194,7 @@
         <v>85</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>83</v>
@@ -22191,7 +22203,7 @@
         <v>95</v>
       </c>
       <c r="AI147" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AJ147" t="s" s="2">
         <v>107</v>
@@ -22209,7 +22221,7 @@
         <v>85</v>
       </c>
       <c r="AO147" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AP147" t="s" s="2">
         <v>490</v>
@@ -22226,10 +22238,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -22353,10 +22365,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -22482,10 +22494,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -22581,16 +22593,16 @@
         <v>85</v>
       </c>
       <c r="AJ150" t="s" s="2">
-        <v>107</v>
+        <v>835</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>85</v>
@@ -22599,10 +22611,10 @@
         <v>85</v>
       </c>
       <c r="AP150" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AQ150" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AR150" t="s" s="2">
         <v>85</v>
@@ -22613,10 +22625,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -22642,20 +22654,20 @@
         <v>115</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q151" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="R151" t="s" s="2">
         <v>85</v>
@@ -22679,10 +22691,10 @@
         <v>175</v>
       </c>
       <c r="Y151" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="Z151" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AA151" t="s" s="2">
         <v>85</v>
@@ -22700,7 +22712,7 @@
         <v>85</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>83</v>
@@ -22730,10 +22742,10 @@
         <v>85</v>
       </c>
       <c r="AP151" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AQ151" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AR151" t="s" s="2">
         <v>85</v>
@@ -22744,10 +22756,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -22773,14 +22785,14 @@
         <v>210</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>85</v>
@@ -22829,7 +22841,7 @@
         <v>85</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>83</v>
@@ -22859,10 +22871,10 @@
         <v>85</v>
       </c>
       <c r="AP152" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AQ152" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AR152" t="s" s="2">
         <v>85</v>
@@ -22873,10 +22885,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -22902,21 +22914,21 @@
         <v>109</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q153" s="2"/>
       <c r="R153" t="s" s="2">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="S153" t="s" s="2">
         <v>85</v>
@@ -22958,7 +22970,7 @@
         <v>85</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>83</v>
@@ -22967,7 +22979,7 @@
         <v>95</v>
       </c>
       <c r="AI153" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AJ153" t="s" s="2">
         <v>107</v>
@@ -22988,10 +23000,10 @@
         <v>85</v>
       </c>
       <c r="AP153" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AQ153" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AR153" t="s" s="2">
         <v>85</v>
@@ -23002,10 +23014,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -23031,23 +23043,23 @@
         <v>115</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q154" s="2"/>
       <c r="R154" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="S154" t="s" s="2">
         <v>85</v>
@@ -23089,7 +23101,7 @@
         <v>85</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>83</v>
@@ -23101,10 +23113,10 @@
         <v>85</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="AL154" t="s" s="2">
         <v>85</v>
@@ -23119,10 +23131,10 @@
         <v>85</v>
       </c>
       <c r="AP154" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AQ154" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AR154" t="s" s="2">
         <v>85</v>
@@ -23133,10 +23145,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -23162,16 +23174,16 @@
         <v>172</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>85</v>
@@ -23199,10 +23211,10 @@
         <v>228</v>
       </c>
       <c r="Y155" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="Z155" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AA155" t="s" s="2">
         <v>85</v>
@@ -23220,7 +23232,7 @@
         <v>85</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>83</v>
@@ -23229,7 +23241,7 @@
         <v>95</v>
       </c>
       <c r="AI155" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AJ155" t="s" s="2">
         <v>107</v>
@@ -23253,7 +23265,7 @@
         <v>138</v>
       </c>
       <c r="AQ155" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AR155" t="s" s="2">
         <v>85</v>
@@ -23264,14 +23276,14 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
@@ -23293,16 +23305,16 @@
         <v>172</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>85</v>
@@ -23330,10 +23342,10 @@
         <v>228</v>
       </c>
       <c r="Y156" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Z156" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>85</v>
@@ -23351,7 +23363,7 @@
         <v>85</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>83</v>
@@ -23378,27 +23390,27 @@
         <v>85</v>
       </c>
       <c r="AO156" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AP156" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AQ156" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AR156" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS156" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -23424,16 +23436,16 @@
         <v>86</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>85</v>
@@ -23482,7 +23494,7 @@
         <v>85</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>83</v>
@@ -23512,10 +23524,10 @@
         <v>85</v>
       </c>
       <c r="AP157" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AQ157" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AR157" t="s" s="2">
         <v>85</v>
@@ -23526,13 +23538,13 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="D158" t="s" s="2">
         <v>85</v>
@@ -23554,19 +23566,19 @@
         <v>96</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>85</v>
@@ -23615,7 +23627,7 @@
         <v>85</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>83</v>
@@ -23627,7 +23639,7 @@
         <v>85</v>
       </c>
       <c r="AJ158" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AK158" t="s" s="2">
         <v>85</v>
@@ -23645,10 +23657,10 @@
         <v>85</v>
       </c>
       <c r="AP158" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AQ158" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AR158" t="s" s="2">
         <v>85</v>
@@ -23659,10 +23671,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -23786,10 +23798,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -23915,14 +23927,14 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
@@ -23944,10 +23956,10 @@
         <v>140</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="N161" t="s" s="2">
         <v>197</v>
@@ -24002,7 +24014,7 @@
         <v>85</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>83</v>
@@ -24046,10 +24058,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -24075,16 +24087,16 @@
         <v>172</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="O162" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>85</v>
@@ -24094,7 +24106,7 @@
         <v>85</v>
       </c>
       <c r="S162" t="s" s="2">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="T162" t="s" s="2">
         <v>85</v>
@@ -24133,7 +24145,7 @@
         <v>85</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>95</v>
@@ -24148,7 +24160,7 @@
         <v>107</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="AL162" t="s" s="2">
         <v>85</v>
@@ -24160,7 +24172,7 @@
         <v>85</v>
       </c>
       <c r="AO162" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AP162" t="s" s="2">
         <v>397</v>
@@ -24177,10 +24189,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -24206,13 +24218,13 @@
         <v>481</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="O163" t="s" s="2">
         <v>485</v>
@@ -24262,7 +24274,7 @@
         <v>144</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>83</v>
@@ -24271,7 +24283,7 @@
         <v>95</v>
       </c>
       <c r="AI163" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AJ163" t="s" s="2">
         <v>107</v>
@@ -24289,7 +24301,7 @@
         <v>85</v>
       </c>
       <c r="AO163" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AP163" t="s" s="2">
         <v>490</v>
@@ -24306,13 +24318,13 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="D164" t="s" s="2">
         <v>85</v>
@@ -24337,13 +24349,13 @@
         <v>172</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="O164" t="s" s="2">
         <v>485</v>
@@ -24395,7 +24407,7 @@
         <v>85</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>83</v>
@@ -24404,7 +24416,7 @@
         <v>95</v>
       </c>
       <c r="AI164" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AJ164" t="s" s="2">
         <v>107</v>
@@ -24422,7 +24434,7 @@
         <v>85</v>
       </c>
       <c r="AO164" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AP164" t="s" s="2">
         <v>490</v>
@@ -24439,10 +24451,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -24566,10 +24578,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -24695,10 +24707,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -24762,7 +24774,7 @@
       </c>
       <c r="Y167" s="2"/>
       <c r="Z167" t="s" s="2">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>85</v>
@@ -24795,7 +24807,7 @@
         <v>107</v>
       </c>
       <c r="AK167" t="s" s="2">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="AL167" t="s" s="2">
         <v>85</v>
@@ -24824,10 +24836,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -24955,10 +24967,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -24984,16 +24996,16 @@
         <v>172</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>85</v>
@@ -25021,10 +25033,10 @@
         <v>228</v>
       </c>
       <c r="Y169" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="Z169" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>85</v>
@@ -25042,7 +25054,7 @@
         <v>85</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>83</v>
@@ -25051,7 +25063,7 @@
         <v>95</v>
       </c>
       <c r="AI169" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AJ169" t="s" s="2">
         <v>107</v>
@@ -25075,7 +25087,7 @@
         <v>138</v>
       </c>
       <c r="AQ169" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AR169" t="s" s="2">
         <v>85</v>
@@ -25086,14 +25098,14 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E170" s="2"/>
       <c r="F170" t="s" s="2">
@@ -25115,16 +25127,16 @@
         <v>172</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="O170" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>85</v>
@@ -25152,10 +25164,10 @@
         <v>228</v>
       </c>
       <c r="Y170" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Z170" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>85</v>
@@ -25173,7 +25185,7 @@
         <v>85</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>83</v>
@@ -25200,27 +25212,27 @@
         <v>85</v>
       </c>
       <c r="AO170" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AP170" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AQ170" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AR170" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS170" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -25246,16 +25258,16 @@
         <v>86</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="O171" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>85</v>
@@ -25304,7 +25316,7 @@
         <v>85</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>83</v>
@@ -25334,10 +25346,10 @@
         <v>85</v>
       </c>
       <c r="AP171" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AQ171" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AR171" t="s" s="2">
         <v>85</v>
@@ -25348,13 +25360,13 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="D172" t="s" s="2">
         <v>85</v>
@@ -25376,19 +25388,19 @@
         <v>96</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="O172" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>85</v>
@@ -25437,7 +25449,7 @@
         <v>85</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>83</v>
@@ -25449,7 +25461,7 @@
         <v>85</v>
       </c>
       <c r="AJ172" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AK172" t="s" s="2">
         <v>85</v>
@@ -25467,10 +25479,10 @@
         <v>85</v>
       </c>
       <c r="AP172" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AQ172" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AR172" t="s" s="2">
         <v>85</v>
@@ -25481,10 +25493,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -25608,10 +25620,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -25737,14 +25749,14 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
@@ -25766,10 +25778,10 @@
         <v>140</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="N175" t="s" s="2">
         <v>197</v>
@@ -25824,7 +25836,7 @@
         <v>85</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>83</v>
@@ -25868,10 +25880,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -25897,16 +25909,16 @@
         <v>172</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="O176" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>85</v>
@@ -25916,7 +25928,7 @@
         <v>85</v>
       </c>
       <c r="S176" t="s" s="2">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="T176" t="s" s="2">
         <v>85</v>
@@ -25955,7 +25967,7 @@
         <v>85</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>95</v>
@@ -25970,7 +25982,7 @@
         <v>107</v>
       </c>
       <c r="AK176" t="s" s="2">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="AL176" t="s" s="2">
         <v>85</v>
@@ -25982,7 +25994,7 @@
         <v>85</v>
       </c>
       <c r="AO176" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AP176" t="s" s="2">
         <v>397</v>
@@ -25999,10 +26011,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -26028,13 +26040,13 @@
         <v>481</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="O177" t="s" s="2">
         <v>485</v>
@@ -26084,7 +26096,7 @@
         <v>144</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>83</v>
@@ -26093,7 +26105,7 @@
         <v>95</v>
       </c>
       <c r="AI177" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AJ177" t="s" s="2">
         <v>107</v>
@@ -26111,7 +26123,7 @@
         <v>85</v>
       </c>
       <c r="AO177" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AP177" t="s" s="2">
         <v>490</v>
@@ -26128,13 +26140,13 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="D178" t="s" s="2">
         <v>85</v>
@@ -26159,13 +26171,13 @@
         <v>172</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="O178" t="s" s="2">
         <v>485</v>
@@ -26217,7 +26229,7 @@
         <v>85</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>83</v>
@@ -26226,7 +26238,7 @@
         <v>95</v>
       </c>
       <c r="AI178" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AJ178" t="s" s="2">
         <v>107</v>
@@ -26244,7 +26256,7 @@
         <v>85</v>
       </c>
       <c r="AO178" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AP178" t="s" s="2">
         <v>490</v>
@@ -26261,10 +26273,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -26388,10 +26400,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -26517,10 +26529,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -26584,7 +26596,7 @@
       </c>
       <c r="Y181" s="2"/>
       <c r="Z181" t="s" s="2">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="AA181" t="s" s="2">
         <v>85</v>
@@ -26617,7 +26629,7 @@
         <v>107</v>
       </c>
       <c r="AK181" t="s" s="2">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="AL181" t="s" s="2">
         <v>85</v>
@@ -26646,10 +26658,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -26777,10 +26789,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -26806,16 +26818,16 @@
         <v>172</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>85</v>
@@ -26843,10 +26855,10 @@
         <v>228</v>
       </c>
       <c r="Y183" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="Z183" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AA183" t="s" s="2">
         <v>85</v>
@@ -26864,7 +26876,7 @@
         <v>85</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>83</v>
@@ -26873,7 +26885,7 @@
         <v>95</v>
       </c>
       <c r="AI183" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AJ183" t="s" s="2">
         <v>107</v>
@@ -26897,7 +26909,7 @@
         <v>138</v>
       </c>
       <c r="AQ183" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AR183" t="s" s="2">
         <v>85</v>
@@ -26908,14 +26920,14 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E184" s="2"/>
       <c r="F184" t="s" s="2">
@@ -26937,16 +26949,16 @@
         <v>172</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="O184" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>85</v>
@@ -26974,10 +26986,10 @@
         <v>228</v>
       </c>
       <c r="Y184" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Z184" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AA184" t="s" s="2">
         <v>85</v>
@@ -26995,7 +27007,7 @@
         <v>85</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>83</v>
@@ -27022,27 +27034,27 @@
         <v>85</v>
       </c>
       <c r="AO184" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AP184" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AQ184" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AR184" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS184" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -27068,16 +27080,16 @@
         <v>86</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="O185" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>85</v>
@@ -27126,7 +27138,7 @@
         <v>85</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>83</v>
@@ -27156,10 +27168,10 @@
         <v>85</v>
       </c>
       <c r="AP185" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AQ185" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AR185" t="s" s="2">
         <v>85</v>
@@ -27170,13 +27182,13 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="D186" t="s" s="2">
         <v>85</v>
@@ -27198,19 +27210,19 @@
         <v>96</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="O186" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>85</v>
@@ -27259,7 +27271,7 @@
         <v>85</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>83</v>
@@ -27271,7 +27283,7 @@
         <v>85</v>
       </c>
       <c r="AJ186" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AK186" t="s" s="2">
         <v>85</v>
@@ -27289,10 +27301,10 @@
         <v>85</v>
       </c>
       <c r="AP186" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AQ186" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AR186" t="s" s="2">
         <v>85</v>
@@ -27303,10 +27315,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -27430,10 +27442,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -27559,14 +27571,14 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E189" s="2"/>
       <c r="F189" t="s" s="2">
@@ -27588,10 +27600,10 @@
         <v>140</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="N189" t="s" s="2">
         <v>197</v>
@@ -27646,7 +27658,7 @@
         <v>85</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>83</v>
@@ -27690,10 +27702,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -27719,16 +27731,16 @@
         <v>172</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="O190" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="P190" t="s" s="2">
         <v>85</v>
@@ -27738,7 +27750,7 @@
         <v>85</v>
       </c>
       <c r="S190" t="s" s="2">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="T190" t="s" s="2">
         <v>85</v>
@@ -27777,7 +27789,7 @@
         <v>85</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>95</v>
@@ -27792,7 +27804,7 @@
         <v>107</v>
       </c>
       <c r="AK190" t="s" s="2">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="AL190" t="s" s="2">
         <v>85</v>
@@ -27804,7 +27816,7 @@
         <v>85</v>
       </c>
       <c r="AO190" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AP190" t="s" s="2">
         <v>397</v>
@@ -27821,10 +27833,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -27850,13 +27862,13 @@
         <v>481</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="O191" t="s" s="2">
         <v>485</v>
@@ -27906,7 +27918,7 @@
         <v>144</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>83</v>
@@ -27915,7 +27927,7 @@
         <v>95</v>
       </c>
       <c r="AI191" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AJ191" t="s" s="2">
         <v>107</v>
@@ -27933,7 +27945,7 @@
         <v>85</v>
       </c>
       <c r="AO191" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AP191" t="s" s="2">
         <v>490</v>
@@ -27950,13 +27962,13 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="D192" t="s" s="2">
         <v>85</v>
@@ -27981,13 +27993,13 @@
         <v>172</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="O192" t="s" s="2">
         <v>485</v>
@@ -28039,7 +28051,7 @@
         <v>85</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>83</v>
@@ -28048,7 +28060,7 @@
         <v>95</v>
       </c>
       <c r="AI192" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AJ192" t="s" s="2">
         <v>107</v>
@@ -28066,7 +28078,7 @@
         <v>85</v>
       </c>
       <c r="AO192" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AP192" t="s" s="2">
         <v>490</v>
@@ -28083,10 +28095,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -28210,10 +28222,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -28339,10 +28351,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -28406,7 +28418,7 @@
       </c>
       <c r="Y195" s="2"/>
       <c r="Z195" t="s" s="2">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="AA195" t="s" s="2">
         <v>85</v>
@@ -28439,7 +28451,7 @@
         <v>107</v>
       </c>
       <c r="AK195" t="s" s="2">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="AL195" t="s" s="2">
         <v>85</v>
@@ -28468,10 +28480,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -28599,10 +28611,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -28628,16 +28640,16 @@
         <v>172</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="O197" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="P197" t="s" s="2">
         <v>85</v>
@@ -28665,10 +28677,10 @@
         <v>228</v>
       </c>
       <c r="Y197" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="Z197" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AA197" t="s" s="2">
         <v>85</v>
@@ -28686,7 +28698,7 @@
         <v>85</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>83</v>
@@ -28695,7 +28707,7 @@
         <v>95</v>
       </c>
       <c r="AI197" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AJ197" t="s" s="2">
         <v>107</v>
@@ -28719,7 +28731,7 @@
         <v>138</v>
       </c>
       <c r="AQ197" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AR197" t="s" s="2">
         <v>85</v>
@@ -28730,14 +28742,14 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E198" s="2"/>
       <c r="F198" t="s" s="2">
@@ -28759,16 +28771,16 @@
         <v>172</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N198" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="O198" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="P198" t="s" s="2">
         <v>85</v>
@@ -28796,10 +28808,10 @@
         <v>228</v>
       </c>
       <c r="Y198" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Z198" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AA198" t="s" s="2">
         <v>85</v>
@@ -28817,7 +28829,7 @@
         <v>85</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>83</v>
@@ -28844,27 +28856,27 @@
         <v>85</v>
       </c>
       <c r="AO198" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AP198" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AQ198" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AR198" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS198" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -28890,16 +28902,16 @@
         <v>86</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="N199" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="O199" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="P199" t="s" s="2">
         <v>85</v>
@@ -28948,7 +28960,7 @@
         <v>85</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>83</v>
@@ -28978,10 +28990,10 @@
         <v>85</v>
       </c>
       <c r="AP199" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AQ199" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AR199" t="s" s="2">
         <v>85</v>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBP.xlsx
+++ b/docs/StructureDefinition-VitalSignsBP.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
